--- a/research/traditional_assets/database/data/finland/finland_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="hlse_vik1v" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.173</v>
+        <v>-0.0223</v>
       </c>
       <c r="E2">
-        <v>-0.017</v>
+        <v>0.398</v>
       </c>
       <c r="G2">
-        <v>-0.1419491525423729</v>
+        <v>0.04751332149200711</v>
       </c>
       <c r="H2">
-        <v>-0.1419491525423729</v>
+        <v>0.04751332149200711</v>
       </c>
       <c r="I2">
-        <v>-0.06483050847457628</v>
+        <v>0.03818827708703375</v>
       </c>
       <c r="J2">
-        <v>-0.05715669318574888</v>
+        <v>0.03396908840886954</v>
       </c>
       <c r="K2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>0.05508474576271186</v>
+        <v>0.02442273534635879</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>75.5</v>
+        <v>114</v>
       </c>
       <c r="V2">
-        <v>0.3355555555555556</v>
+        <v>0.4918032786885246</v>
       </c>
       <c r="W2">
-        <v>0.05421184320266889</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="X2">
-        <v>0.08129320705149842</v>
+        <v>0.1328270160253025</v>
       </c>
       <c r="Y2">
-        <v>-0.02708136384882953</v>
+        <v>-0.08934875515573729</v>
       </c>
       <c r="Z2">
-        <v>0.6550097141271164</v>
+        <v>1.316959064327485</v>
       </c>
       <c r="AA2">
-        <v>-0.03743818926404868</v>
+        <v>0.04473589888700245</v>
       </c>
       <c r="AB2">
-        <v>0.05598921435457391</v>
+        <v>0.0845997244224112</v>
       </c>
       <c r="AC2">
-        <v>-0.09342740361862259</v>
+        <v>-0.03986382553540876</v>
       </c>
       <c r="AD2">
-        <v>164.5</v>
+        <v>260.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>164.5</v>
+        <v>260.9</v>
       </c>
       <c r="AG2">
-        <v>89</v>
+        <v>146.9</v>
       </c>
       <c r="AH2">
-        <v>0.4223363286264442</v>
+        <v>0.5295311548609701</v>
       </c>
       <c r="AI2">
-        <v>0.3940119760479042</v>
+        <v>0.4895852880465378</v>
       </c>
       <c r="AJ2">
-        <v>0.2834394904458599</v>
+        <v>0.3879059941906522</v>
       </c>
       <c r="AK2">
-        <v>0.260233918128655</v>
+        <v>0.3506803533062783</v>
       </c>
       <c r="AL2">
-        <v>3.59</v>
+        <v>7.84</v>
       </c>
       <c r="AM2">
-        <v>-2.09</v>
+        <v>7.84</v>
       </c>
       <c r="AN2">
-        <v>22.53424657534246</v>
+        <v>6.759067357512953</v>
       </c>
       <c r="AO2">
-        <v>-4.261838440111421</v>
+        <v>2.193877551020408</v>
       </c>
       <c r="AP2">
-        <v>12.19178082191781</v>
+        <v>3.805699481865284</v>
       </c>
       <c r="AQ2">
-        <v>7.320574162679427</v>
+        <v>2.193877551020408</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.173</v>
+        <v>-0.0223</v>
       </c>
       <c r="E3">
-        <v>-0.017</v>
+        <v>0.398</v>
       </c>
       <c r="G3">
-        <v>-0.1419491525423729</v>
+        <v>0.04751332149200711</v>
       </c>
       <c r="H3">
-        <v>-0.1419491525423729</v>
+        <v>0.04751332149200711</v>
       </c>
       <c r="I3">
-        <v>-0.06483050847457628</v>
+        <v>0.03818827708703375</v>
       </c>
       <c r="J3">
-        <v>-0.05715669318574888</v>
+        <v>0.03396908840886954</v>
       </c>
       <c r="K3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>0.05508474576271186</v>
+        <v>0.02442273534635879</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +766,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>75.5</v>
+        <v>114</v>
       </c>
       <c r="V3">
-        <v>0.3355555555555556</v>
+        <v>0.4918032786885246</v>
       </c>
       <c r="W3">
-        <v>0.05421184320266889</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="X3">
-        <v>0.08129320705149842</v>
+        <v>0.1328270160253025</v>
       </c>
       <c r="Y3">
-        <v>-0.02708136384882953</v>
+        <v>-0.08934875515573729</v>
       </c>
       <c r="Z3">
-        <v>0.6550097141271164</v>
+        <v>1.316959064327485</v>
       </c>
       <c r="AA3">
-        <v>-0.03743818926404868</v>
+        <v>0.04473589888700245</v>
       </c>
       <c r="AB3">
-        <v>0.05598921435457391</v>
+        <v>0.0845997244224112</v>
       </c>
       <c r="AC3">
-        <v>-0.09342740361862259</v>
+        <v>-0.03986382553540876</v>
       </c>
       <c r="AD3">
-        <v>164.5</v>
+        <v>260.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>164.5</v>
+        <v>260.9</v>
       </c>
       <c r="AG3">
-        <v>89</v>
+        <v>146.9</v>
       </c>
       <c r="AH3">
-        <v>0.4223363286264442</v>
+        <v>0.5295311548609701</v>
       </c>
       <c r="AI3">
-        <v>0.3940119760479042</v>
+        <v>0.4895852880465378</v>
       </c>
       <c r="AJ3">
-        <v>0.2834394904458599</v>
+        <v>0.3879059941906522</v>
       </c>
       <c r="AK3">
-        <v>0.260233918128655</v>
+        <v>0.3506803533062783</v>
       </c>
       <c r="AL3">
-        <v>3.59</v>
+        <v>7.84</v>
       </c>
       <c r="AM3">
-        <v>-2.09</v>
+        <v>7.84</v>
       </c>
       <c r="AN3">
-        <v>22.53424657534246</v>
+        <v>6.759067357512953</v>
       </c>
       <c r="AO3">
-        <v>-4.261838440111421</v>
+        <v>2.193877551020408</v>
       </c>
       <c r="AP3">
-        <v>12.19178082191781</v>
+        <v>3.805699481865284</v>
       </c>
       <c r="AQ3">
-        <v>7.320574162679427</v>
+        <v>2.193877551020408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Viking Line Abp (HLSE:VIK1V)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HLSE:VIK1V</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.52953115486097</v>
+      </c>
+      <c r="F2">
+        <v>0.06</v>
+      </c>
+      <c r="G2">
+        <v>231.8</v>
+      </c>
+      <c r="H2">
+        <v>439.670598123783</v>
+      </c>
+      <c r="I2">
+        <v>378.7</v>
+      </c>
+      <c r="J2">
+        <v>355.232598123783</v>
+      </c>
+      <c r="K2">
+        <v>260.9</v>
+      </c>
+      <c r="L2">
+        <v>29.562</v>
+      </c>
+      <c r="M2">
+        <v>0.0845997244224112</v>
+      </c>
+      <c r="N2">
+        <v>0.087625349166642</v>
+      </c>
+      <c r="O2">
+        <v>0.0417515596330275</v>
+      </c>
+      <c r="P2">
+        <v>0.03784</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.132827016025303</v>
+      </c>
+      <c r="T2">
+        <v>0.0908031374113213</v>
+      </c>
+      <c r="U2">
+        <v>1.42379789107556</v>
+      </c>
+      <c r="V2">
+        <v>0.787454079746905</v>
+      </c>
+      <c r="W2">
+        <v>10.65592892309466</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>231.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0660395809086869</v>
+      </c>
+      <c r="AC2">
+        <v>0.05218944954128441</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>38.6</v>
+      </c>
+      <c r="AH2">
+        <v>23.7</v>
+      </c>
+      <c r="AI2">
+        <v>167.7</v>
+      </c>
+      <c r="AJ2">
+        <v>260.9</v>
+      </c>
+      <c r="AK2">
+        <v>260.9</v>
+      </c>
+      <c r="AL2">
+        <v>7.84</v>
+      </c>
+      <c r="AM2">
+        <v>260.9</v>
+      </c>
+      <c r="AN2">
+        <v>114</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08827666919700608</v>
+      </c>
+      <c r="C2">
+        <v>464.5562504562587</v>
+      </c>
+      <c r="D2">
+        <v>350.5562504562587</v>
+      </c>
+      <c r="E2">
+        <v>-260.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>114</v>
+      </c>
+      <c r="H2">
+        <v>231.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>38.6</v>
+      </c>
+      <c r="K2">
+        <v>23.7</v>
+      </c>
+      <c r="L2">
+        <v>14.9</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>14.9</v>
+      </c>
+      <c r="O2">
+        <v>2.98</v>
+      </c>
+      <c r="P2">
+        <v>11.92</v>
+      </c>
+      <c r="Q2">
+        <v>35.62</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08827666919700608</v>
+      </c>
+      <c r="T2">
+        <v>0.7491972013786339</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08815531585861208</v>
+      </c>
+      <c r="C3">
+        <v>460.4911874238919</v>
+      </c>
+      <c r="D3">
+        <v>351.4181874238919</v>
+      </c>
+      <c r="E3">
+        <v>-255.973</v>
+      </c>
+      <c r="F3">
+        <v>4.927</v>
+      </c>
+      <c r="G3">
+        <v>114</v>
+      </c>
+      <c r="H3">
+        <v>231.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>38.6</v>
+      </c>
+      <c r="K3">
+        <v>23.7</v>
+      </c>
+      <c r="L3">
+        <v>14.9</v>
+      </c>
+      <c r="M3">
+        <v>0.2251639</v>
+      </c>
+      <c r="N3">
+        <v>14.6748361</v>
+      </c>
+      <c r="O3">
+        <v>2.93496722</v>
+      </c>
+      <c r="P3">
+        <v>11.73986888</v>
+      </c>
+      <c r="Q3">
+        <v>35.43986888000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08867648066526473</v>
+      </c>
+      <c r="T3">
+        <v>0.7552513201776532</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>66.17401812635153</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08803396252021806</v>
+      </c>
+      <c r="C4">
+        <v>456.4303734473864</v>
+      </c>
+      <c r="D4">
+        <v>352.2843734473864</v>
+      </c>
+      <c r="E4">
+        <v>-251.046</v>
+      </c>
+      <c r="F4">
+        <v>9.853999999999999</v>
+      </c>
+      <c r="G4">
+        <v>114</v>
+      </c>
+      <c r="H4">
+        <v>231.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>38.6</v>
+      </c>
+      <c r="K4">
+        <v>23.7</v>
+      </c>
+      <c r="L4">
+        <v>14.9</v>
+      </c>
+      <c r="M4">
+        <v>0.4503278</v>
+      </c>
+      <c r="N4">
+        <v>14.4496722</v>
+      </c>
+      <c r="O4">
+        <v>2.88993444</v>
+      </c>
+      <c r="P4">
+        <v>11.55973776</v>
+      </c>
+      <c r="Q4">
+        <v>35.25973776</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08908445155124292</v>
+      </c>
+      <c r="T4">
+        <v>0.7614289924215504</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>33.08700906317576</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08791260918182404</v>
+      </c>
+      <c r="C5">
+        <v>452.373840023976</v>
+      </c>
+      <c r="D5">
+        <v>353.154840023976</v>
+      </c>
+      <c r="E5">
+        <v>-246.119</v>
+      </c>
+      <c r="F5">
+        <v>14.781</v>
+      </c>
+      <c r="G5">
+        <v>114</v>
+      </c>
+      <c r="H5">
+        <v>231.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>38.6</v>
+      </c>
+      <c r="K5">
+        <v>23.7</v>
+      </c>
+      <c r="L5">
+        <v>14.9</v>
+      </c>
+      <c r="M5">
+        <v>0.6754917</v>
+      </c>
+      <c r="N5">
+        <v>14.2245083</v>
+      </c>
+      <c r="O5">
+        <v>2.84490166</v>
+      </c>
+      <c r="P5">
+        <v>11.37960664</v>
+      </c>
+      <c r="Q5">
+        <v>35.07960664</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08950083420806604</v>
+      </c>
+      <c r="T5">
+        <v>0.7677340393508887</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>22.05800604211717</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08779125584343005</v>
+      </c>
+      <c r="C6">
+        <v>448.3216189629742</v>
+      </c>
+      <c r="D6">
+        <v>354.0296189629742</v>
+      </c>
+      <c r="E6">
+        <v>-241.192</v>
+      </c>
+      <c r="F6">
+        <v>19.708</v>
+      </c>
+      <c r="G6">
+        <v>114</v>
+      </c>
+      <c r="H6">
+        <v>231.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>38.6</v>
+      </c>
+      <c r="K6">
+        <v>23.7</v>
+      </c>
+      <c r="L6">
+        <v>14.9</v>
+      </c>
+      <c r="M6">
+        <v>0.9006556</v>
+      </c>
+      <c r="N6">
+        <v>13.9993444</v>
+      </c>
+      <c r="O6">
+        <v>2.79986888</v>
+      </c>
+      <c r="P6">
+        <v>11.19947552</v>
+      </c>
+      <c r="Q6">
+        <v>34.89947552</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08992589150357297</v>
+      </c>
+      <c r="T6">
+        <v>0.7741704414245885</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>16.54350453158788</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08766990250503602</v>
+      </c>
+      <c r="C7">
+        <v>444.2737423896496</v>
+      </c>
+      <c r="D7">
+        <v>354.9087423896496</v>
+      </c>
+      <c r="E7">
+        <v>-236.265</v>
+      </c>
+      <c r="F7">
+        <v>24.635</v>
+      </c>
+      <c r="G7">
+        <v>114</v>
+      </c>
+      <c r="H7">
+        <v>231.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>38.6</v>
+      </c>
+      <c r="K7">
+        <v>23.7</v>
+      </c>
+      <c r="L7">
+        <v>14.9</v>
+      </c>
+      <c r="M7">
+        <v>1.1258195</v>
+      </c>
+      <c r="N7">
+        <v>13.7741805</v>
+      </c>
+      <c r="O7">
+        <v>2.7548361</v>
+      </c>
+      <c r="P7">
+        <v>11.0193444</v>
+      </c>
+      <c r="Q7">
+        <v>34.7193444</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09035989737372213</v>
+      </c>
+      <c r="T7">
+        <v>0.7807423466998394</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>13.2348036252703</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08762534916664201</v>
+      </c>
+      <c r="C8">
+        <v>439.670598123783</v>
+      </c>
+      <c r="D8">
+        <v>355.232598123783</v>
+      </c>
+      <c r="E8">
+        <v>-231.338</v>
+      </c>
+      <c r="F8">
+        <v>29.562</v>
+      </c>
+      <c r="G8">
+        <v>114</v>
+      </c>
+      <c r="H8">
+        <v>231.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>38.6</v>
+      </c>
+      <c r="K8">
+        <v>23.7</v>
+      </c>
+      <c r="L8">
+        <v>14.9</v>
+      </c>
+      <c r="M8">
+        <v>1.3982826</v>
+      </c>
+      <c r="N8">
+        <v>13.5017174</v>
+      </c>
+      <c r="O8">
+        <v>2.70034348</v>
+      </c>
+      <c r="P8">
+        <v>10.80137392</v>
+      </c>
+      <c r="Q8">
+        <v>34.50137392000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09080313741132129</v>
+      </c>
+      <c r="T8">
+        <v>0.7874540797469046</v>
+      </c>
+      <c r="U8">
+        <v>0.0473</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>10.65592892309466</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08772959582824801</v>
+      </c>
+      <c r="C9">
+        <v>433.9867594084578</v>
+      </c>
+      <c r="D9">
+        <v>354.4757594084579</v>
+      </c>
+      <c r="E9">
+        <v>-226.411</v>
+      </c>
+      <c r="F9">
+        <v>34.489</v>
+      </c>
+      <c r="G9">
+        <v>114</v>
+      </c>
+      <c r="H9">
+        <v>231.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>38.6</v>
+      </c>
+      <c r="K9">
+        <v>23.7</v>
+      </c>
+      <c r="L9">
+        <v>14.9</v>
+      </c>
+      <c r="M9">
+        <v>1.7623879</v>
+      </c>
+      <c r="N9">
+        <v>13.1376121</v>
+      </c>
+      <c r="O9">
+        <v>2.62752242</v>
+      </c>
+      <c r="P9">
+        <v>10.51008968</v>
+      </c>
+      <c r="Q9">
+        <v>34.21008968</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09125590949273979</v>
+      </c>
+      <c r="T9">
+        <v>0.7943101511390678</v>
+      </c>
+      <c r="U9">
+        <v>0.0511</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.04088</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>8.454438435488578</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.087773042489854</v>
+      </c>
+      <c r="C10">
+        <v>428.7452845957129</v>
+      </c>
+      <c r="D10">
+        <v>354.1612845957129</v>
+      </c>
+      <c r="E10">
+        <v>-221.484</v>
+      </c>
+      <c r="F10">
+        <v>39.416</v>
+      </c>
+      <c r="G10">
+        <v>114</v>
+      </c>
+      <c r="H10">
+        <v>231.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>38.6</v>
+      </c>
+      <c r="K10">
+        <v>23.7</v>
+      </c>
+      <c r="L10">
+        <v>14.9</v>
+      </c>
+      <c r="M10">
+        <v>2.089048</v>
+      </c>
+      <c r="N10">
+        <v>12.810952</v>
+      </c>
+      <c r="O10">
+        <v>2.5621904</v>
+      </c>
+      <c r="P10">
+        <v>10.2487616</v>
+      </c>
+      <c r="Q10">
+        <v>33.9487616</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09171852444549347</v>
+      </c>
+      <c r="T10">
+        <v>0.8013152675614954</v>
+      </c>
+      <c r="U10">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>7.132435444278926</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08771008915145999</v>
+      </c>
+      <c r="C11">
+        <v>424.2741340039233</v>
+      </c>
+      <c r="D11">
+        <v>354.6171340039234</v>
+      </c>
+      <c r="E11">
+        <v>-216.557</v>
+      </c>
+      <c r="F11">
+        <v>44.343</v>
+      </c>
+      <c r="G11">
+        <v>114</v>
+      </c>
+      <c r="H11">
+        <v>231.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>38.6</v>
+      </c>
+      <c r="K11">
+        <v>23.7</v>
+      </c>
+      <c r="L11">
+        <v>14.9</v>
+      </c>
+      <c r="M11">
+        <v>2.350179</v>
+      </c>
+      <c r="N11">
+        <v>12.549821</v>
+      </c>
+      <c r="O11">
+        <v>2.5099642</v>
+      </c>
+      <c r="P11">
+        <v>10.0398568</v>
+      </c>
+      <c r="Q11">
+        <v>33.7398568</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09219130675984613</v>
+      </c>
+      <c r="T11">
+        <v>0.8084743425866137</v>
+      </c>
+      <c r="U11">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>6.339942617136822</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08780713581306597</v>
+      </c>
+      <c r="C12">
+        <v>418.6449013916231</v>
+      </c>
+      <c r="D12">
+        <v>353.9149013916231</v>
+      </c>
+      <c r="E12">
+        <v>-211.63</v>
+      </c>
+      <c r="F12">
+        <v>49.27</v>
+      </c>
+      <c r="G12">
+        <v>114</v>
+      </c>
+      <c r="H12">
+        <v>231.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>38.6</v>
+      </c>
+      <c r="K12">
+        <v>23.7</v>
+      </c>
+      <c r="L12">
+        <v>14.9</v>
+      </c>
+      <c r="M12">
+        <v>2.70985</v>
+      </c>
+      <c r="N12">
+        <v>12.19015</v>
+      </c>
+      <c r="O12">
+        <v>2.43803</v>
+      </c>
+      <c r="P12">
+        <v>9.752120000000003</v>
+      </c>
+      <c r="Q12">
+        <v>33.45212</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09267459534785108</v>
+      </c>
+      <c r="T12">
+        <v>0.8157925081678459</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.044</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>5.498459324316845</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08776018247467195</v>
+      </c>
+      <c r="C13">
+        <v>414.057309565527</v>
+      </c>
+      <c r="D13">
+        <v>354.254309565527</v>
+      </c>
+      <c r="E13">
+        <v>-206.703</v>
+      </c>
+      <c r="F13">
+        <v>54.197</v>
+      </c>
+      <c r="G13">
+        <v>114</v>
+      </c>
+      <c r="H13">
+        <v>231.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>38.6</v>
+      </c>
+      <c r="K13">
+        <v>23.7</v>
+      </c>
+      <c r="L13">
+        <v>14.9</v>
+      </c>
+      <c r="M13">
+        <v>2.980835</v>
+      </c>
+      <c r="N13">
+        <v>11.919165</v>
+      </c>
+      <c r="O13">
+        <v>2.383833</v>
+      </c>
+      <c r="P13">
+        <v>9.535332000000004</v>
+      </c>
+      <c r="Q13">
+        <v>33.235332</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09316874435356398</v>
+      </c>
+      <c r="T13">
+        <v>0.8232751269082066</v>
+      </c>
+      <c r="U13">
+        <v>0.055</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.044</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>4.998599385742587</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08771322913627796</v>
+      </c>
+      <c r="C14">
+        <v>409.4703693564726</v>
+      </c>
+      <c r="D14">
+        <v>354.5943693564726</v>
+      </c>
+      <c r="E14">
+        <v>-201.776</v>
+      </c>
+      <c r="F14">
+        <v>59.124</v>
+      </c>
+      <c r="G14">
+        <v>114</v>
+      </c>
+      <c r="H14">
+        <v>231.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>38.6</v>
+      </c>
+      <c r="K14">
+        <v>23.7</v>
+      </c>
+      <c r="L14">
+        <v>14.9</v>
+      </c>
+      <c r="M14">
+        <v>3.25182</v>
+      </c>
+      <c r="N14">
+        <v>11.64818</v>
+      </c>
+      <c r="O14">
+        <v>2.329636</v>
+      </c>
+      <c r="P14">
+        <v>9.318544000000003</v>
+      </c>
+      <c r="Q14">
+        <v>33.01854400000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09367412401849767</v>
+      </c>
+      <c r="T14">
+        <v>0.830927805165394</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.044</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>4.582049436930705</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08849827579788393</v>
+      </c>
+      <c r="C15">
+        <v>398.9421061050134</v>
+      </c>
+      <c r="D15">
+        <v>348.9931061050133</v>
+      </c>
+      <c r="E15">
+        <v>-196.849</v>
+      </c>
+      <c r="F15">
+        <v>64.051</v>
+      </c>
+      <c r="G15">
+        <v>114</v>
+      </c>
+      <c r="H15">
+        <v>231.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>38.6</v>
+      </c>
+      <c r="K15">
+        <v>23.7</v>
+      </c>
+      <c r="L15">
+        <v>14.9</v>
+      </c>
+      <c r="M15">
+        <v>4.035213</v>
+      </c>
+      <c r="N15">
+        <v>10.864787</v>
+      </c>
+      <c r="O15">
+        <v>2.1729574</v>
+      </c>
+      <c r="P15">
+        <v>8.691829600000004</v>
+      </c>
+      <c r="Q15">
+        <v>32.3918296</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09419112160676313</v>
+      </c>
+      <c r="T15">
+        <v>0.8387564070606774</v>
+      </c>
+      <c r="U15">
+        <v>0.063</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.0504</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>3.692494051739029</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08931052245948992</v>
+      </c>
+      <c r="C16">
+        <v>388.4030381327478</v>
+      </c>
+      <c r="D16">
+        <v>343.3810381327478</v>
+      </c>
+      <c r="E16">
+        <v>-191.922</v>
+      </c>
+      <c r="F16">
+        <v>68.97800000000001</v>
+      </c>
+      <c r="G16">
+        <v>114</v>
+      </c>
+      <c r="H16">
+        <v>231.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>38.6</v>
+      </c>
+      <c r="K16">
+        <v>23.7</v>
+      </c>
+      <c r="L16">
+        <v>14.9</v>
+      </c>
+      <c r="M16">
+        <v>4.835357800000001</v>
+      </c>
+      <c r="N16">
+        <v>10.0646422</v>
+      </c>
+      <c r="O16">
+        <v>2.01292844</v>
+      </c>
+      <c r="P16">
+        <v>8.051713760000002</v>
+      </c>
+      <c r="Q16">
+        <v>31.75171376</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09472014239475572</v>
+      </c>
+      <c r="T16">
+        <v>0.8467670694651537</v>
+      </c>
+      <c r="U16">
+        <v>0.0701</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.05608</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>3.081467931907748</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09194036912109591</v>
+      </c>
+      <c r="C17">
+        <v>366.4825642121139</v>
+      </c>
+      <c r="D17">
+        <v>326.3875642121139</v>
+      </c>
+      <c r="E17">
+        <v>-186.995</v>
+      </c>
+      <c r="F17">
+        <v>73.905</v>
+      </c>
+      <c r="G17">
+        <v>114</v>
+      </c>
+      <c r="H17">
+        <v>231.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>38.6</v>
+      </c>
+      <c r="K17">
+        <v>23.7</v>
+      </c>
+      <c r="L17">
+        <v>14.9</v>
+      </c>
+      <c r="M17">
+        <v>6.754917000000001</v>
+      </c>
+      <c r="N17">
+        <v>8.145083000000001</v>
+      </c>
+      <c r="O17">
+        <v>1.6290166</v>
+      </c>
+      <c r="P17">
+        <v>6.516066400000001</v>
+      </c>
+      <c r="Q17">
+        <v>30.2160664</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09526161073070107</v>
+      </c>
+      <c r="T17">
+        <v>0.8549662180438528</v>
+      </c>
+      <c r="U17">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.07312</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>2.205800604211717</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09218461578270189</v>
+      </c>
+      <c r="C18">
+        <v>360.0622674677296</v>
+      </c>
+      <c r="D18">
+        <v>324.8942674677295</v>
+      </c>
+      <c r="E18">
+        <v>-182.068</v>
+      </c>
+      <c r="F18">
+        <v>78.83199999999999</v>
+      </c>
+      <c r="G18">
+        <v>114</v>
+      </c>
+      <c r="H18">
+        <v>231.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>38.6</v>
+      </c>
+      <c r="K18">
+        <v>23.7</v>
+      </c>
+      <c r="L18">
+        <v>14.9</v>
+      </c>
+      <c r="M18">
+        <v>7.2052448</v>
+      </c>
+      <c r="N18">
+        <v>7.694755200000002</v>
+      </c>
+      <c r="O18">
+        <v>1.53895104</v>
+      </c>
+      <c r="P18">
+        <v>6.155804160000002</v>
+      </c>
+      <c r="Q18">
+        <v>29.85580416</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09581597116988319</v>
+      </c>
+      <c r="T18">
+        <v>0.8633605844458542</v>
+      </c>
+      <c r="U18">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.07312</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>2.067938066448485</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09529846244430788</v>
+      </c>
+      <c r="C19">
+        <v>337.229100001198</v>
+      </c>
+      <c r="D19">
+        <v>306.9881000011981</v>
+      </c>
+      <c r="E19">
+        <v>-177.141</v>
+      </c>
+      <c r="F19">
+        <v>83.759</v>
+      </c>
+      <c r="G19">
+        <v>114</v>
+      </c>
+      <c r="H19">
+        <v>231.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>38.6</v>
+      </c>
+      <c r="K19">
+        <v>23.7</v>
+      </c>
+      <c r="L19">
+        <v>14.9</v>
+      </c>
+      <c r="M19">
+        <v>9.4228875</v>
+      </c>
+      <c r="N19">
+        <v>5.477112500000002</v>
+      </c>
+      <c r="O19">
+        <v>1.0954225</v>
+      </c>
+      <c r="P19">
+        <v>4.381690000000003</v>
+      </c>
+      <c r="Q19">
+        <v>28.08169</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0963836896919372</v>
+      </c>
+      <c r="T19">
+        <v>0.8719572247370606</v>
+      </c>
+      <c r="U19">
+        <v>0.1125</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>1.581256276274125</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1091102378039877</v>
+      </c>
+      <c r="C20">
+        <v>271.9972168470269</v>
+      </c>
+      <c r="D20">
+        <v>246.6832168470269</v>
+      </c>
+      <c r="E20">
+        <v>-172.214</v>
+      </c>
+      <c r="F20">
+        <v>88.68599999999999</v>
+      </c>
+      <c r="G20">
+        <v>114</v>
+      </c>
+      <c r="H20">
+        <v>231.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>38.6</v>
+      </c>
+      <c r="K20">
+        <v>23.7</v>
+      </c>
+      <c r="L20">
+        <v>14.9</v>
+      </c>
+      <c r="M20">
+        <v>17.4356676</v>
+      </c>
+      <c r="N20">
+        <v>-2.535667599999996</v>
+      </c>
+      <c r="O20">
+        <v>-0.5071335199999992</v>
+      </c>
+      <c r="P20">
+        <v>-2.028534079999997</v>
+      </c>
+      <c r="Q20">
+        <v>21.67146592</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09728115007406854</v>
+      </c>
+      <c r="T20">
+        <v>0.8855469594050055</v>
+      </c>
+      <c r="U20">
+        <v>0.1966</v>
+      </c>
+      <c r="V20">
+        <v>0.170914017654248</v>
+      </c>
+      <c r="W20">
+        <v>0.1629983041291748</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.8545700882712403</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1106882378039877</v>
+      </c>
+      <c r="C21">
+        <v>261.6553377503103</v>
+      </c>
+      <c r="D21">
+        <v>241.2683377503103</v>
+      </c>
+      <c r="E21">
+        <v>-167.287</v>
+      </c>
+      <c r="F21">
+        <v>93.613</v>
+      </c>
+      <c r="G21">
+        <v>114</v>
+      </c>
+      <c r="H21">
+        <v>231.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>38.6</v>
+      </c>
+      <c r="K21">
+        <v>23.7</v>
+      </c>
+      <c r="L21">
+        <v>14.9</v>
+      </c>
+      <c r="M21">
+        <v>18.4043158</v>
+      </c>
+      <c r="N21">
+        <v>-3.504315799999997</v>
+      </c>
+      <c r="O21">
+        <v>-0.7008631599999993</v>
+      </c>
+      <c r="P21">
+        <v>-2.803452639999998</v>
+      </c>
+      <c r="Q21">
+        <v>20.89654736</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09800313958115581</v>
+      </c>
+      <c r="T21">
+        <v>0.8964796379161784</v>
+      </c>
+      <c r="U21">
+        <v>0.1966</v>
+      </c>
+      <c r="V21">
+        <v>0.1619185430408665</v>
+      </c>
+      <c r="W21">
+        <v>0.1647668144381657</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.8095927152043328</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1158286913565781</v>
+      </c>
+      <c r="C22">
+        <v>240.627471150163</v>
+      </c>
+      <c r="D22">
+        <v>225.1674711501631</v>
+      </c>
+      <c r="E22">
+        <v>-162.36</v>
+      </c>
+      <c r="F22">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="G22">
+        <v>114</v>
+      </c>
+      <c r="H22">
+        <v>231.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>38.6</v>
+      </c>
+      <c r="K22">
+        <v>23.7</v>
+      </c>
+      <c r="L22">
+        <v>14.9</v>
+      </c>
+      <c r="M22">
+        <v>21.067852</v>
+      </c>
+      <c r="N22">
+        <v>-6.167852</v>
+      </c>
+      <c r="O22">
+        <v>-1.2335704</v>
+      </c>
+      <c r="P22">
+        <v>-4.9342816</v>
+      </c>
+      <c r="Q22">
+        <v>18.7657184</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09889624576665834</v>
+      </c>
+      <c r="T22">
+        <v>0.9100034394487386</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.1414477375291985</v>
+      </c>
+      <c r="W22">
+        <v>0.1835584737162574</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.7072386876459926</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1175786913565781</v>
+      </c>
+      <c r="C23">
+        <v>230.698571934432</v>
+      </c>
+      <c r="D23">
+        <v>220.1655719344321</v>
+      </c>
+      <c r="E23">
+        <v>-157.433</v>
+      </c>
+      <c r="F23">
+        <v>103.467</v>
+      </c>
+      <c r="G23">
+        <v>114</v>
+      </c>
+      <c r="H23">
+        <v>231.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>38.6</v>
+      </c>
+      <c r="K23">
+        <v>23.7</v>
+      </c>
+      <c r="L23">
+        <v>14.9</v>
+      </c>
+      <c r="M23">
+        <v>22.1212446</v>
+      </c>
+      <c r="N23">
+        <v>-7.221244599999995</v>
+      </c>
+      <c r="O23">
+        <v>-1.444248919999999</v>
+      </c>
+      <c r="P23">
+        <v>-5.776995679999996</v>
+      </c>
+      <c r="Q23">
+        <v>17.92300432</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09965695773838817</v>
+      </c>
+      <c r="T23">
+        <v>0.9215224703278364</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1347121309801891</v>
+      </c>
+      <c r="W23">
+        <v>0.1849985463964356</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.6735606549009455</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1193286913565781</v>
+      </c>
+      <c r="C24">
+        <v>220.987069114447</v>
+      </c>
+      <c r="D24">
+        <v>215.3810691144469</v>
+      </c>
+      <c r="E24">
+        <v>-152.506</v>
+      </c>
+      <c r="F24">
+        <v>108.394</v>
+      </c>
+      <c r="G24">
+        <v>114</v>
+      </c>
+      <c r="H24">
+        <v>231.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>38.6</v>
+      </c>
+      <c r="K24">
+        <v>23.7</v>
+      </c>
+      <c r="L24">
+        <v>14.9</v>
+      </c>
+      <c r="M24">
+        <v>23.1746372</v>
+      </c>
+      <c r="N24">
+        <v>-8.274637199999994</v>
+      </c>
+      <c r="O24">
+        <v>-1.654927439999998</v>
+      </c>
+      <c r="P24">
+        <v>-6.619709759999996</v>
+      </c>
+      <c r="Q24">
+        <v>17.08029024</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1004371751452906</v>
+      </c>
+      <c r="T24">
+        <v>0.9333368609730652</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1285888522992714</v>
+      </c>
+      <c r="W24">
+        <v>0.1863077033784158</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.6429442614963571</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1210786913565781</v>
+      </c>
+      <c r="C25">
+        <v>211.4790911633417</v>
+      </c>
+      <c r="D25">
+        <v>210.8000911633416</v>
+      </c>
+      <c r="E25">
+        <v>-147.579</v>
+      </c>
+      <c r="F25">
+        <v>113.321</v>
+      </c>
+      <c r="G25">
+        <v>114</v>
+      </c>
+      <c r="H25">
+        <v>231.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>38.6</v>
+      </c>
+      <c r="K25">
+        <v>23.7</v>
+      </c>
+      <c r="L25">
+        <v>14.9</v>
+      </c>
+      <c r="M25">
+        <v>24.2280298</v>
+      </c>
+      <c r="N25">
+        <v>-9.328029799999996</v>
+      </c>
+      <c r="O25">
+        <v>-1.865605959999999</v>
+      </c>
+      <c r="P25">
+        <v>-7.462423839999997</v>
+      </c>
+      <c r="Q25">
+        <v>16.23757616</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1012376579393853</v>
+      </c>
+      <c r="T25">
+        <v>0.9454581189077802</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1229980326340857</v>
+      </c>
+      <c r="W25">
+        <v>0.1875030206228325</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.6149901631704284</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1228286913565781</v>
+      </c>
+      <c r="C26">
+        <v>202.1619221201227</v>
+      </c>
+      <c r="D26">
+        <v>206.4099221201227</v>
+      </c>
+      <c r="E26">
+        <v>-142.652</v>
+      </c>
+      <c r="F26">
+        <v>118.248</v>
+      </c>
+      <c r="G26">
+        <v>114</v>
+      </c>
+      <c r="H26">
+        <v>231.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>38.6</v>
+      </c>
+      <c r="K26">
+        <v>23.7</v>
+      </c>
+      <c r="L26">
+        <v>14.9</v>
+      </c>
+      <c r="M26">
+        <v>25.2814224</v>
+      </c>
+      <c r="N26">
+        <v>-10.38142239999999</v>
+      </c>
+      <c r="O26">
+        <v>-2.076284479999999</v>
+      </c>
+      <c r="P26">
+        <v>-8.305137919999996</v>
+      </c>
+      <c r="Q26">
+        <v>15.39486208</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1020592060701667</v>
+      </c>
+      <c r="T26">
+        <v>0.9578983573144616</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.1178731146076654</v>
+      </c>
+      <c r="W26">
+        <v>0.1885987280968811</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.5893655730383274</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1245786913565781</v>
+      </c>
+      <c r="C27">
+        <v>193.0238837142248</v>
+      </c>
+      <c r="D27">
+        <v>202.1988837142248</v>
+      </c>
+      <c r="E27">
+        <v>-137.725</v>
+      </c>
+      <c r="F27">
+        <v>123.175</v>
+      </c>
+      <c r="G27">
+        <v>114</v>
+      </c>
+      <c r="H27">
+        <v>231.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>38.6</v>
+      </c>
+      <c r="K27">
+        <v>23.7</v>
+      </c>
+      <c r="L27">
+        <v>14.9</v>
+      </c>
+      <c r="M27">
+        <v>26.334815</v>
+      </c>
+      <c r="N27">
+        <v>-11.434815</v>
+      </c>
+      <c r="O27">
+        <v>-2.286962999999999</v>
+      </c>
+      <c r="P27">
+        <v>-9.147851999999999</v>
+      </c>
+      <c r="Q27">
+        <v>14.552148</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1029026621511022</v>
+      </c>
+      <c r="T27">
+        <v>0.9706703354119878</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.1131581900233588</v>
+      </c>
+      <c r="W27">
+        <v>0.1896067789730059</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.5657909501167941</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1263286913565781</v>
+      </c>
+      <c r="C28">
+        <v>184.0542316304826</v>
+      </c>
+      <c r="D28">
+        <v>198.1562316304826</v>
+      </c>
+      <c r="E28">
+        <v>-132.798</v>
+      </c>
+      <c r="F28">
+        <v>128.102</v>
+      </c>
+      <c r="G28">
+        <v>114</v>
+      </c>
+      <c r="H28">
+        <v>231.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>38.6</v>
+      </c>
+      <c r="K28">
+        <v>23.7</v>
+      </c>
+      <c r="L28">
+        <v>14.9</v>
+      </c>
+      <c r="M28">
+        <v>27.3882076</v>
+      </c>
+      <c r="N28">
+        <v>-12.4882076</v>
+      </c>
+      <c r="O28">
+        <v>-2.497641519999999</v>
+      </c>
+      <c r="P28">
+        <v>-9.990566080000001</v>
+      </c>
+      <c r="Q28">
+        <v>13.70943392</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1037689143423333</v>
+      </c>
+      <c r="T28">
+        <v>0.9837875021067444</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.1088059519455373</v>
+      </c>
+      <c r="W28">
+        <v>0.1905372874740441</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.5440297597276866</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1280786913565781</v>
+      </c>
+      <c r="C29">
+        <v>175.2430639743021</v>
+      </c>
+      <c r="D29">
+        <v>194.2720639743021</v>
+      </c>
+      <c r="E29">
+        <v>-127.871</v>
+      </c>
+      <c r="F29">
+        <v>133.029</v>
+      </c>
+      <c r="G29">
+        <v>114</v>
+      </c>
+      <c r="H29">
+        <v>231.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>38.6</v>
+      </c>
+      <c r="K29">
+        <v>23.7</v>
+      </c>
+      <c r="L29">
+        <v>14.9</v>
+      </c>
+      <c r="M29">
+        <v>28.4416002</v>
+      </c>
+      <c r="N29">
+        <v>-13.54160019999999</v>
+      </c>
+      <c r="O29">
+        <v>-2.708320039999998</v>
+      </c>
+      <c r="P29">
+        <v>-10.83328016</v>
+      </c>
+      <c r="Q29">
+        <v>12.86671984</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1046588994703105</v>
+      </c>
+      <c r="T29">
+        <v>0.9972640432314943</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.1047761018734804</v>
+      </c>
+      <c r="W29">
+        <v>0.1913988694194499</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.523880509367402</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1298286913565782</v>
+      </c>
+      <c r="C30">
+        <v>166.5812402952131</v>
+      </c>
+      <c r="D30">
+        <v>190.5372402952131</v>
+      </c>
+      <c r="E30">
+        <v>-122.944</v>
+      </c>
+      <c r="F30">
+        <v>137.956</v>
+      </c>
+      <c r="G30">
+        <v>114</v>
+      </c>
+      <c r="H30">
+        <v>231.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>38.6</v>
+      </c>
+      <c r="K30">
+        <v>23.7</v>
+      </c>
+      <c r="L30">
+        <v>14.9</v>
+      </c>
+      <c r="M30">
+        <v>29.4949928</v>
+      </c>
+      <c r="N30">
+        <v>-14.5949928</v>
+      </c>
+      <c r="O30">
+        <v>-2.918998559999999</v>
+      </c>
+      <c r="P30">
+        <v>-11.67599424</v>
+      </c>
+      <c r="Q30">
+        <v>12.02400576</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1055736064073982</v>
+      </c>
+      <c r="T30">
+        <v>1.011114932720821</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1010340982351418</v>
+      </c>
+      <c r="W30">
+        <v>0.1921989097973267</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.505170491175709</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1389752232434792</v>
+      </c>
+      <c r="C31">
+        <v>144.257174558045</v>
+      </c>
+      <c r="D31">
+        <v>173.140174558045</v>
+      </c>
+      <c r="E31">
+        <v>-118.017</v>
+      </c>
+      <c r="F31">
+        <v>142.883</v>
+      </c>
+      <c r="G31">
+        <v>114</v>
+      </c>
+      <c r="H31">
+        <v>231.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>38.6</v>
+      </c>
+      <c r="K31">
+        <v>23.7</v>
+      </c>
+      <c r="L31">
+        <v>14.9</v>
+      </c>
+      <c r="M31">
+        <v>34.1204604</v>
+      </c>
+      <c r="N31">
+        <v>-19.2204604</v>
+      </c>
+      <c r="O31">
+        <v>-3.844092079999998</v>
+      </c>
+      <c r="P31">
+        <v>-15.37636832</v>
+      </c>
+      <c r="Q31">
+        <v>8.323631680000002</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1067204626763772</v>
+      </c>
+      <c r="T31">
+        <v>1.028481128162987</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.08733762572558956</v>
+      </c>
+      <c r="W31">
+        <v>0.2179437749767292</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.4366881286279479</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1409752232434793</v>
+      </c>
+      <c r="C32">
+        <v>135.9410911959179</v>
+      </c>
+      <c r="D32">
+        <v>169.7510911959179</v>
+      </c>
+      <c r="E32">
+        <v>-113.09</v>
+      </c>
+      <c r="F32">
+        <v>147.81</v>
+      </c>
+      <c r="G32">
+        <v>114</v>
+      </c>
+      <c r="H32">
+        <v>231.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>38.6</v>
+      </c>
+      <c r="K32">
+        <v>23.7</v>
+      </c>
+      <c r="L32">
+        <v>14.9</v>
+      </c>
+      <c r="M32">
+        <v>35.297028</v>
+      </c>
+      <c r="N32">
+        <v>-20.397028</v>
+      </c>
+      <c r="O32">
+        <v>-4.079405599999999</v>
+      </c>
+      <c r="P32">
+        <v>-16.3176224</v>
+      </c>
+      <c r="Q32">
+        <v>7.382377599999995</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1076907550003254</v>
+      </c>
+      <c r="T32">
+        <v>1.043173715708172</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08442637153473656</v>
+      </c>
+      <c r="W32">
+        <v>0.2186389824775049</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.4221318576736829</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1429752232434792</v>
+      </c>
+      <c r="C33">
+        <v>127.7551379456009</v>
+      </c>
+      <c r="D33">
+        <v>166.4921379456009</v>
+      </c>
+      <c r="E33">
+        <v>-108.163</v>
+      </c>
+      <c r="F33">
+        <v>152.737</v>
+      </c>
+      <c r="G33">
+        <v>114</v>
+      </c>
+      <c r="H33">
+        <v>231.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>38.6</v>
+      </c>
+      <c r="K33">
+        <v>23.7</v>
+      </c>
+      <c r="L33">
+        <v>14.9</v>
+      </c>
+      <c r="M33">
+        <v>36.4735956</v>
+      </c>
+      <c r="N33">
+        <v>-21.5735956</v>
+      </c>
+      <c r="O33">
+        <v>-4.314719119999999</v>
+      </c>
+      <c r="P33">
+        <v>-17.25887648</v>
+      </c>
+      <c r="Q33">
+        <v>6.441123519999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1086891717394605</v>
+      </c>
+      <c r="T33">
+        <v>1.058292175356117</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.08170294019490636</v>
+      </c>
+      <c r="W33">
+        <v>0.2192893378814564</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.4085147009745319</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1449752232434793</v>
+      </c>
+      <c r="C34">
+        <v>119.6919611077373</v>
+      </c>
+      <c r="D34">
+        <v>163.3559611077373</v>
+      </c>
+      <c r="E34">
+        <v>-103.236</v>
+      </c>
+      <c r="F34">
+        <v>157.664</v>
+      </c>
+      <c r="G34">
+        <v>114</v>
+      </c>
+      <c r="H34">
+        <v>231.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>38.6</v>
+      </c>
+      <c r="K34">
+        <v>23.7</v>
+      </c>
+      <c r="L34">
+        <v>14.9</v>
+      </c>
+      <c r="M34">
+        <v>37.6501632</v>
+      </c>
+      <c r="N34">
+        <v>-22.7501632</v>
+      </c>
+      <c r="O34">
+        <v>-4.550032639999999</v>
+      </c>
+      <c r="P34">
+        <v>-18.20013056</v>
+      </c>
+      <c r="Q34">
+        <v>5.499869439999998</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1097169536768056</v>
+      </c>
+      <c r="T34">
+        <v>1.073855295581942</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07914972331381553</v>
+      </c>
+      <c r="W34">
+        <v>0.2198990460726609</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3957486165690778</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1469752232434793</v>
+      </c>
+      <c r="C35">
+        <v>111.7447508191011</v>
+      </c>
+      <c r="D35">
+        <v>160.3357508191011</v>
+      </c>
+      <c r="E35">
+        <v>-98.30899999999997</v>
+      </c>
+      <c r="F35">
+        <v>162.591</v>
+      </c>
+      <c r="G35">
+        <v>114</v>
+      </c>
+      <c r="H35">
+        <v>231.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>38.6</v>
+      </c>
+      <c r="K35">
+        <v>23.7</v>
+      </c>
+      <c r="L35">
+        <v>14.9</v>
+      </c>
+      <c r="M35">
+        <v>38.82673080000001</v>
+      </c>
+      <c r="N35">
+        <v>-23.9267308</v>
+      </c>
+      <c r="O35">
+        <v>-4.78534616</v>
+      </c>
+      <c r="P35">
+        <v>-19.14138464000001</v>
+      </c>
+      <c r="Q35">
+        <v>4.558615359999994</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1107754156719818</v>
+      </c>
+      <c r="T35">
+        <v>1.089882986560777</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07675124684976051</v>
+      </c>
+      <c r="W35">
+        <v>0.2204718022522772</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3837562342488026</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1489752232434793</v>
+      </c>
+      <c r="C36">
+        <v>103.907191691578</v>
+      </c>
+      <c r="D36">
+        <v>157.425191691578</v>
+      </c>
+      <c r="E36">
+        <v>-93.38199999999998</v>
+      </c>
+      <c r="F36">
+        <v>167.518</v>
+      </c>
+      <c r="G36">
+        <v>114</v>
+      </c>
+      <c r="H36">
+        <v>231.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>38.6</v>
+      </c>
+      <c r="K36">
+        <v>23.7</v>
+      </c>
+      <c r="L36">
+        <v>14.9</v>
+      </c>
+      <c r="M36">
+        <v>40.00329840000001</v>
+      </c>
+      <c r="N36">
+        <v>-25.1032984</v>
+      </c>
+      <c r="O36">
+        <v>-5.02065968</v>
+      </c>
+      <c r="P36">
+        <v>-20.08263872000001</v>
+      </c>
+      <c r="Q36">
+        <v>3.617361279999994</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1118659522730724</v>
+      </c>
+      <c r="T36">
+        <v>1.106396365145031</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.07449385723653226</v>
+      </c>
+      <c r="W36">
+        <v>0.2210108668919161</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3724692861826614</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1509752232434793</v>
+      </c>
+      <c r="C37">
+        <v>96.17341873156553</v>
+      </c>
+      <c r="D37">
+        <v>154.6184187315656</v>
+      </c>
+      <c r="E37">
+        <v>-88.45499999999996</v>
+      </c>
+      <c r="F37">
+        <v>172.445</v>
+      </c>
+      <c r="G37">
+        <v>114</v>
+      </c>
+      <c r="H37">
+        <v>231.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>38.6</v>
+      </c>
+      <c r="K37">
+        <v>23.7</v>
+      </c>
+      <c r="L37">
+        <v>14.9</v>
+      </c>
+      <c r="M37">
+        <v>41.179866</v>
+      </c>
+      <c r="N37">
+        <v>-26.279866</v>
+      </c>
+      <c r="O37">
+        <v>-5.255973199999999</v>
+      </c>
+      <c r="P37">
+        <v>-21.0238928</v>
+      </c>
+      <c r="Q37">
+        <v>2.676107199999997</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1129900438465043</v>
+      </c>
+      <c r="T37">
+        <v>1.123417847685724</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07236546131548849</v>
+      </c>
+      <c r="W37">
+        <v>0.2215191278378614</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3618273065774424</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1529752232434793</v>
+      </c>
+      <c r="C38">
+        <v>88.53797789231552</v>
+      </c>
+      <c r="D38">
+        <v>151.9099778923155</v>
+      </c>
+      <c r="E38">
+        <v>-83.52799999999999</v>
+      </c>
+      <c r="F38">
+        <v>177.372</v>
+      </c>
+      <c r="G38">
+        <v>114</v>
+      </c>
+      <c r="H38">
+        <v>231.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>38.6</v>
+      </c>
+      <c r="K38">
+        <v>23.7</v>
+      </c>
+      <c r="L38">
+        <v>14.9</v>
+      </c>
+      <c r="M38">
+        <v>42.3564336</v>
+      </c>
+      <c r="N38">
+        <v>-27.45643359999999</v>
+      </c>
+      <c r="O38">
+        <v>-5.491286719999997</v>
+      </c>
+      <c r="P38">
+        <v>-21.96514688</v>
+      </c>
+      <c r="Q38">
+        <v>1.734853120000004</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1141492632816059</v>
+      </c>
+      <c r="T38">
+        <v>1.140971251555814</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07035530961228048</v>
+      </c>
+      <c r="W38">
+        <v>0.2219991520645875</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3517765480614025</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1549752232434793</v>
+      </c>
+      <c r="C39">
+        <v>80.99579070091337</v>
+      </c>
+      <c r="D39">
+        <v>149.2947907009134</v>
+      </c>
+      <c r="E39">
+        <v>-78.60099999999997</v>
+      </c>
+      <c r="F39">
+        <v>182.299</v>
+      </c>
+      <c r="G39">
+        <v>114</v>
+      </c>
+      <c r="H39">
+        <v>231.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>38.6</v>
+      </c>
+      <c r="K39">
+        <v>23.7</v>
+      </c>
+      <c r="L39">
+        <v>14.9</v>
+      </c>
+      <c r="M39">
+        <v>43.5330012</v>
+      </c>
+      <c r="N39">
+        <v>-28.6330012</v>
+      </c>
+      <c r="O39">
+        <v>-5.726600239999999</v>
+      </c>
+      <c r="P39">
+        <v>-22.90640096</v>
+      </c>
+      <c r="Q39">
+        <v>0.7935990400000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1153452833336949</v>
+      </c>
+      <c r="T39">
+        <v>1.159081906342414</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06845381475789451</v>
+      </c>
+      <c r="W39">
+        <v>0.2224532290358148</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3422690737894727</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1569752232434793</v>
+      </c>
+      <c r="C40">
+        <v>73.54212247718056</v>
+      </c>
+      <c r="D40">
+        <v>146.7681224771806</v>
+      </c>
+      <c r="E40">
+        <v>-73.67399999999998</v>
+      </c>
+      <c r="F40">
+        <v>187.226</v>
+      </c>
+      <c r="G40">
+        <v>114</v>
+      </c>
+      <c r="H40">
+        <v>231.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>38.6</v>
+      </c>
+      <c r="K40">
+        <v>23.7</v>
+      </c>
+      <c r="L40">
+        <v>14.9</v>
+      </c>
+      <c r="M40">
+        <v>44.7095688</v>
+      </c>
+      <c r="N40">
+        <v>-29.8095688</v>
+      </c>
+      <c r="O40">
+        <v>-5.961913759999998</v>
+      </c>
+      <c r="P40">
+        <v>-23.84765504</v>
+      </c>
+      <c r="Q40">
+        <v>-0.1476550400000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1165798846777868</v>
+      </c>
+      <c r="T40">
+        <v>1.17777677579955</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06665239858005519</v>
+      </c>
+      <c r="W40">
+        <v>0.2228834072190828</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.333261992900276</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1589752232434793</v>
+      </c>
+      <c r="C41">
+        <v>66.17255372605248</v>
+      </c>
+      <c r="D41">
+        <v>144.3255537260525</v>
+      </c>
+      <c r="E41">
+        <v>-68.74699999999999</v>
+      </c>
+      <c r="F41">
+        <v>192.153</v>
+      </c>
+      <c r="G41">
+        <v>114</v>
+      </c>
+      <c r="H41">
+        <v>231.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>38.6</v>
+      </c>
+      <c r="K41">
+        <v>23.7</v>
+      </c>
+      <c r="L41">
+        <v>14.9</v>
+      </c>
+      <c r="M41">
+        <v>45.8861364</v>
+      </c>
+      <c r="N41">
+        <v>-30.9861364</v>
+      </c>
+      <c r="O41">
+        <v>-6.197227279999998</v>
+      </c>
+      <c r="P41">
+        <v>-24.78890912</v>
+      </c>
+      <c r="Q41">
+        <v>-1.08890912</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1178549647544718</v>
+      </c>
+      <c r="T41">
+        <v>1.197084591796264</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06494336271902813</v>
+      </c>
+      <c r="W41">
+        <v>0.2232915249826961</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3247168135951407</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1609752232434793</v>
+      </c>
+      <c r="C42">
+        <v>58.88295433978527</v>
+      </c>
+      <c r="D42">
+        <v>141.9629543397853</v>
+      </c>
+      <c r="E42">
+        <v>-63.81999999999996</v>
+      </c>
+      <c r="F42">
+        <v>197.08</v>
+      </c>
+      <c r="G42">
+        <v>114</v>
+      </c>
+      <c r="H42">
+        <v>231.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>38.6</v>
+      </c>
+      <c r="K42">
+        <v>23.7</v>
+      </c>
+      <c r="L42">
+        <v>14.9</v>
+      </c>
+      <c r="M42">
+        <v>47.062704</v>
+      </c>
+      <c r="N42">
+        <v>-32.16270400000001</v>
+      </c>
+      <c r="O42">
+        <v>-6.4325408</v>
+      </c>
+      <c r="P42">
+        <v>-25.73016320000001</v>
+      </c>
+      <c r="Q42">
+        <v>-2.030163200000008</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1191725475003796</v>
+      </c>
+      <c r="T42">
+        <v>1.217036001659535</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06331977865105243</v>
+      </c>
+      <c r="W42">
+        <v>0.2236792368581287</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3165988932552621</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1629752232434792</v>
+      </c>
+      <c r="C43">
+        <v>51.66946029320042</v>
+      </c>
+      <c r="D43">
+        <v>139.6764602932004</v>
+      </c>
+      <c r="E43">
+        <v>-58.89299999999997</v>
+      </c>
+      <c r="F43">
+        <v>202.007</v>
+      </c>
+      <c r="G43">
+        <v>114</v>
+      </c>
+      <c r="H43">
+        <v>231.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>38.6</v>
+      </c>
+      <c r="K43">
+        <v>23.7</v>
+      </c>
+      <c r="L43">
+        <v>14.9</v>
+      </c>
+      <c r="M43">
+        <v>48.2392716</v>
+      </c>
+      <c r="N43">
+        <v>-33.3392716</v>
+      </c>
+      <c r="O43">
+        <v>-6.667854319999999</v>
+      </c>
+      <c r="P43">
+        <v>-26.67141728</v>
+      </c>
+      <c r="Q43">
+        <v>-2.971417280000004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1205347940681827</v>
+      </c>
+      <c r="T43">
+        <v>1.237663730501221</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06177539380590481</v>
+      </c>
+      <c r="W43">
+        <v>0.2240480359591499</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.308876969029524</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1649752232434792</v>
+      </c>
+      <c r="C44">
+        <v>44.52845255534731</v>
+      </c>
+      <c r="D44">
+        <v>137.4624525553473</v>
+      </c>
+      <c r="E44">
+        <v>-53.96599999999998</v>
+      </c>
+      <c r="F44">
+        <v>206.934</v>
+      </c>
+      <c r="G44">
+        <v>114</v>
+      </c>
+      <c r="H44">
+        <v>231.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>38.6</v>
+      </c>
+      <c r="K44">
+        <v>23.7</v>
+      </c>
+      <c r="L44">
+        <v>14.9</v>
+      </c>
+      <c r="M44">
+        <v>49.4158392</v>
+      </c>
+      <c r="N44">
+        <v>-34.5158392</v>
+      </c>
+      <c r="O44">
+        <v>-6.903167839999999</v>
+      </c>
+      <c r="P44">
+        <v>-27.61267136</v>
+      </c>
+      <c r="Q44">
+        <v>-3.912671360000004</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1219440146555651</v>
+      </c>
+      <c r="T44">
+        <v>1.259002760337449</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06030455109624041</v>
+      </c>
+      <c r="W44">
+        <v>0.2243992731982178</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.301522755481202</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1669752232434792</v>
+      </c>
+      <c r="C45">
+        <v>37.45653797549556</v>
+      </c>
+      <c r="D45">
+        <v>135.3175379754956</v>
+      </c>
+      <c r="E45">
+        <v>-49.03899999999999</v>
+      </c>
+      <c r="F45">
+        <v>211.861</v>
+      </c>
+      <c r="G45">
+        <v>114</v>
+      </c>
+      <c r="H45">
+        <v>231.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>38.6</v>
+      </c>
+      <c r="K45">
+        <v>23.7</v>
+      </c>
+      <c r="L45">
+        <v>14.9</v>
+      </c>
+      <c r="M45">
+        <v>50.5924068</v>
+      </c>
+      <c r="N45">
+        <v>-35.6924068</v>
+      </c>
+      <c r="O45">
+        <v>-7.138481359999998</v>
+      </c>
+      <c r="P45">
+        <v>-28.55392544</v>
+      </c>
+      <c r="Q45">
+        <v>-4.853925440000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.123402681579347</v>
+      </c>
+      <c r="T45">
+        <v>1.281090528062668</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05890211967539761</v>
+      </c>
+      <c r="W45">
+        <v>0.2247341738215151</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.294510598376988</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1689752232434792</v>
+      </c>
+      <c r="C46">
+        <v>30.45053193112108</v>
+      </c>
+      <c r="D46">
+        <v>133.2385319311211</v>
+      </c>
+      <c r="E46">
+        <v>-44.11199999999999</v>
+      </c>
+      <c r="F46">
+        <v>216.788</v>
+      </c>
+      <c r="G46">
+        <v>114</v>
+      </c>
+      <c r="H46">
+        <v>231.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>38.6</v>
+      </c>
+      <c r="K46">
+        <v>23.7</v>
+      </c>
+      <c r="L46">
+        <v>14.9</v>
+      </c>
+      <c r="M46">
+        <v>51.7689744</v>
+      </c>
+      <c r="N46">
+        <v>-36.8689744</v>
+      </c>
+      <c r="O46">
+        <v>-7.373794879999998</v>
+      </c>
+      <c r="P46">
+        <v>-29.49517952</v>
+      </c>
+      <c r="Q46">
+        <v>-5.795179520000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1249134437504067</v>
+      </c>
+      <c r="T46">
+        <v>1.303967144635215</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05756343513732039</v>
+      </c>
+      <c r="W46">
+        <v>0.2250538516892079</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2878171756866019</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1709752232434792</v>
+      </c>
+      <c r="C47">
+        <v>23.50744255125775</v>
+      </c>
+      <c r="D47">
+        <v>131.2224425512578</v>
+      </c>
+      <c r="E47">
+        <v>-39.18499999999997</v>
+      </c>
+      <c r="F47">
+        <v>221.715</v>
+      </c>
+      <c r="G47">
+        <v>114</v>
+      </c>
+      <c r="H47">
+        <v>231.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>38.6</v>
+      </c>
+      <c r="K47">
+        <v>23.7</v>
+      </c>
+      <c r="L47">
+        <v>14.9</v>
+      </c>
+      <c r="M47">
+        <v>52.945542</v>
+      </c>
+      <c r="N47">
+        <v>-38.045542</v>
+      </c>
+      <c r="O47">
+        <v>-7.609108399999998</v>
+      </c>
+      <c r="P47">
+        <v>-30.4364336</v>
+      </c>
+      <c r="Q47">
+        <v>-6.736433600000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1264791427276869</v>
+      </c>
+      <c r="T47">
+        <v>1.327675638174038</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05628424768982438</v>
+      </c>
+      <c r="W47">
+        <v>0.2253593216516699</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.281421238449122</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1729752232434793</v>
+      </c>
+      <c r="C48">
+        <v>16.62445635083773</v>
+      </c>
+      <c r="D48">
+        <v>129.2664563508377</v>
+      </c>
+      <c r="E48">
+        <v>-34.25799999999998</v>
+      </c>
+      <c r="F48">
+        <v>226.642</v>
+      </c>
+      <c r="G48">
+        <v>114</v>
+      </c>
+      <c r="H48">
+        <v>231.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>38.6</v>
+      </c>
+      <c r="K48">
+        <v>23.7</v>
+      </c>
+      <c r="L48">
+        <v>14.9</v>
+      </c>
+      <c r="M48">
+        <v>54.1221096</v>
+      </c>
+      <c r="N48">
+        <v>-39.2221096</v>
+      </c>
+      <c r="O48">
+        <v>-7.844421919999998</v>
+      </c>
+      <c r="P48">
+        <v>-31.37768768</v>
+      </c>
+      <c r="Q48">
+        <v>-7.677687679999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1281028305559774</v>
+      </c>
+      <c r="T48">
+        <v>1.352262224066149</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05506067708787168</v>
+      </c>
+      <c r="W48">
+        <v>0.2256515103114163</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2753033854393585</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1749752232434792</v>
+      </c>
+      <c r="C49">
+        <v>9.798925130959191</v>
+      </c>
+      <c r="D49">
+        <v>127.3679251309592</v>
+      </c>
+      <c r="E49">
+        <v>-29.33099999999996</v>
+      </c>
+      <c r="F49">
+        <v>231.569</v>
+      </c>
+      <c r="G49">
+        <v>114</v>
+      </c>
+      <c r="H49">
+        <v>231.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>38.6</v>
+      </c>
+      <c r="K49">
+        <v>23.7</v>
+      </c>
+      <c r="L49">
+        <v>14.9</v>
+      </c>
+      <c r="M49">
+        <v>55.29867720000001</v>
+      </c>
+      <c r="N49">
+        <v>-40.39867720000001</v>
+      </c>
+      <c r="O49">
+        <v>-8.07973544</v>
+      </c>
+      <c r="P49">
+        <v>-32.31894176000001</v>
+      </c>
+      <c r="Q49">
+        <v>-8.618941760000009</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1297877896230713</v>
+      </c>
+      <c r="T49">
+        <v>1.377776605652303</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05388917332004461</v>
+      </c>
+      <c r="W49">
+        <v>0.2259312654111734</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2694458666002231</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1769752232434793</v>
+      </c>
+      <c r="C50">
+        <v>3.028354016816365</v>
+      </c>
+      <c r="D50">
+        <v>125.5243540168163</v>
+      </c>
+      <c r="E50">
+        <v>-24.404</v>
+      </c>
+      <c r="F50">
+        <v>236.496</v>
+      </c>
+      <c r="G50">
+        <v>114</v>
+      </c>
+      <c r="H50">
+        <v>231.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>38.6</v>
+      </c>
+      <c r="K50">
+        <v>23.7</v>
+      </c>
+      <c r="L50">
+        <v>14.9</v>
+      </c>
+      <c r="M50">
+        <v>56.4752448</v>
+      </c>
+      <c r="N50">
+        <v>-41.57524479999999</v>
+      </c>
+      <c r="O50">
+        <v>-8.315048959999997</v>
+      </c>
+      <c r="P50">
+        <v>-33.26019583999999</v>
+      </c>
+      <c r="Q50">
+        <v>-9.560195839999995</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1315375548081303</v>
+      </c>
+      <c r="T50">
+        <v>1.404272309607155</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05276648220921036</v>
+      </c>
+      <c r="W50">
+        <v>0.2261993640484406</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2638324110460519</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1789752232434793</v>
+      </c>
+      <c r="C51">
+        <v>-3.689609480331569</v>
+      </c>
+      <c r="D51">
+        <v>123.7333905196684</v>
+      </c>
+      <c r="E51">
+        <v>-19.47699999999998</v>
+      </c>
+      <c r="F51">
+        <v>241.423</v>
+      </c>
+      <c r="G51">
+        <v>114</v>
+      </c>
+      <c r="H51">
+        <v>231.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>38.6</v>
+      </c>
+      <c r="K51">
+        <v>23.7</v>
+      </c>
+      <c r="L51">
+        <v>14.9</v>
+      </c>
+      <c r="M51">
+        <v>57.6518124</v>
+      </c>
+      <c r="N51">
+        <v>-42.75181240000001</v>
+      </c>
+      <c r="O51">
+        <v>-8.550362479999999</v>
+      </c>
+      <c r="P51">
+        <v>-34.20144992000001</v>
+      </c>
+      <c r="Q51">
+        <v>-10.50144992000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1333559382357407</v>
+      </c>
+      <c r="T51">
+        <v>1.431807060775923</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05168961522534891</v>
+      </c>
+      <c r="W51">
+        <v>0.2264565198841867</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2584480761267446</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1809752232434793</v>
+      </c>
+      <c r="C52">
+        <v>-10.35718547799004</v>
+      </c>
+      <c r="D52">
+        <v>121.99281452201</v>
+      </c>
+      <c r="E52">
+        <v>-14.54999999999998</v>
+      </c>
+      <c r="F52">
+        <v>246.35</v>
+      </c>
+      <c r="G52">
+        <v>114</v>
+      </c>
+      <c r="H52">
+        <v>231.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>38.6</v>
+      </c>
+      <c r="K52">
+        <v>23.7</v>
+      </c>
+      <c r="L52">
+        <v>14.9</v>
+      </c>
+      <c r="M52">
+        <v>58.82838</v>
+      </c>
+      <c r="N52">
+        <v>-43.92838</v>
+      </c>
+      <c r="O52">
+        <v>-8.785675999999999</v>
+      </c>
+      <c r="P52">
+        <v>-35.14270400000001</v>
+      </c>
+      <c r="Q52">
+        <v>-11.44270400000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1352470570004556</v>
+      </c>
+      <c r="T52">
+        <v>1.460443201991441</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05065582292084194</v>
+      </c>
+      <c r="W52">
+        <v>0.226703389486503</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2532791146042097</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1829752232434793</v>
+      </c>
+      <c r="C53">
+        <v>-16.97647090370418</v>
+      </c>
+      <c r="D53">
+        <v>120.3005290962958</v>
+      </c>
+      <c r="E53">
+        <v>-9.62299999999999</v>
+      </c>
+      <c r="F53">
+        <v>251.277</v>
+      </c>
+      <c r="G53">
+        <v>114</v>
+      </c>
+      <c r="H53">
+        <v>231.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>38.6</v>
+      </c>
+      <c r="K53">
+        <v>23.7</v>
+      </c>
+      <c r="L53">
+        <v>14.9</v>
+      </c>
+      <c r="M53">
+        <v>60.0049476</v>
+      </c>
+      <c r="N53">
+        <v>-45.1049476</v>
+      </c>
+      <c r="O53">
+        <v>-9.020989519999999</v>
+      </c>
+      <c r="P53">
+        <v>-36.08395808</v>
+      </c>
+      <c r="Q53">
+        <v>-12.38395808</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1372153642861791</v>
+      </c>
+      <c r="T53">
+        <v>1.490248165297389</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04966257149102151</v>
+      </c>
+      <c r="W53">
+        <v>0.2269405779279441</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2483128574551076</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1849752232434793</v>
+      </c>
+      <c r="C54">
+        <v>-23.54944792261273</v>
+      </c>
+      <c r="D54">
+        <v>118.6545520773873</v>
+      </c>
+      <c r="E54">
+        <v>-4.69599999999997</v>
+      </c>
+      <c r="F54">
+        <v>256.204</v>
+      </c>
+      <c r="G54">
+        <v>114</v>
+      </c>
+      <c r="H54">
+        <v>231.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>38.6</v>
+      </c>
+      <c r="K54">
+        <v>23.7</v>
+      </c>
+      <c r="L54">
+        <v>14.9</v>
+      </c>
+      <c r="M54">
+        <v>61.18151520000001</v>
+      </c>
+      <c r="N54">
+        <v>-46.2815152</v>
+      </c>
+      <c r="O54">
+        <v>-9.256303039999999</v>
+      </c>
+      <c r="P54">
+        <v>-37.02521216</v>
+      </c>
+      <c r="Q54">
+        <v>-13.32521216</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1392656843754745</v>
+      </c>
+      <c r="T54">
+        <v>1.521295002074418</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0487075220392711</v>
+      </c>
+      <c r="W54">
+        <v>0.2271686437370221</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2435376101963556</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1869752232434793</v>
+      </c>
+      <c r="C55">
+        <v>-30.07799168249517</v>
+      </c>
+      <c r="D55">
+        <v>117.0530083175049</v>
+      </c>
+      <c r="E55">
+        <v>0.2310000000000514</v>
+      </c>
+      <c r="F55">
+        <v>261.131</v>
+      </c>
+      <c r="G55">
+        <v>114</v>
+      </c>
+      <c r="H55">
+        <v>231.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>38.6</v>
+      </c>
+      <c r="K55">
+        <v>23.7</v>
+      </c>
+      <c r="L55">
+        <v>14.9</v>
+      </c>
+      <c r="M55">
+        <v>62.35808280000001</v>
+      </c>
+      <c r="N55">
+        <v>-47.45808280000001</v>
+      </c>
+      <c r="O55">
+        <v>-9.491616560000001</v>
+      </c>
+      <c r="P55">
+        <v>-37.96646624000002</v>
+      </c>
+      <c r="Q55">
+        <v>-14.26646624000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1414032521281442</v>
+      </c>
+      <c r="T55">
+        <v>1.553662980841959</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04778851218947352</v>
+      </c>
+      <c r="W55">
+        <v>0.2273881032891537</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2389425609473677</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1889752232434793</v>
+      </c>
+      <c r="C56">
+        <v>-36.56387743993761</v>
+      </c>
+      <c r="D56">
+        <v>115.4941225600624</v>
+      </c>
+      <c r="E56">
+        <v>5.158000000000015</v>
+      </c>
+      <c r="F56">
+        <v>266.058</v>
+      </c>
+      <c r="G56">
+        <v>114</v>
+      </c>
+      <c r="H56">
+        <v>231.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>38.6</v>
+      </c>
+      <c r="K56">
+        <v>23.7</v>
+      </c>
+      <c r="L56">
+        <v>14.9</v>
+      </c>
+      <c r="M56">
+        <v>63.5346504</v>
+      </c>
+      <c r="N56">
+        <v>-48.6346504</v>
+      </c>
+      <c r="O56">
+        <v>-9.726930079999997</v>
+      </c>
+      <c r="P56">
+        <v>-38.90772032</v>
+      </c>
+      <c r="Q56">
+        <v>-15.20772032</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1436337576091908</v>
+      </c>
+      <c r="T56">
+        <v>1.587438263034176</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04690353974152032</v>
+      </c>
+      <c r="W56">
+        <v>0.227599434709725</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2345176987076016</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1909752232434793</v>
+      </c>
+      <c r="C57">
+        <v>-43.00878712455525</v>
+      </c>
+      <c r="D57">
+        <v>113.9762128754448</v>
+      </c>
+      <c r="E57">
+        <v>10.08500000000004</v>
+      </c>
+      <c r="F57">
+        <v>270.985</v>
+      </c>
+      <c r="G57">
+        <v>114</v>
+      </c>
+      <c r="H57">
+        <v>231.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>38.6</v>
+      </c>
+      <c r="K57">
+        <v>23.7</v>
+      </c>
+      <c r="L57">
+        <v>14.9</v>
+      </c>
+      <c r="M57">
+        <v>64.711218</v>
+      </c>
+      <c r="N57">
+        <v>-49.811218</v>
+      </c>
+      <c r="O57">
+        <v>-9.962243599999997</v>
+      </c>
+      <c r="P57">
+        <v>-39.8489744</v>
+      </c>
+      <c r="Q57">
+        <v>-16.1489744</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1459633966671729</v>
+      </c>
+      <c r="T57">
+        <v>1.62271466887938</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04605074810985631</v>
+      </c>
+      <c r="W57">
+        <v>0.2278030813513663</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2302537405492816</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1929752232434793</v>
+      </c>
+      <c r="C58">
+        <v>-49.41431539229711</v>
+      </c>
+      <c r="D58">
+        <v>112.4976846077029</v>
+      </c>
+      <c r="E58">
+        <v>15.01200000000006</v>
+      </c>
+      <c r="F58">
+        <v>275.912</v>
+      </c>
+      <c r="G58">
+        <v>114</v>
+      </c>
+      <c r="H58">
+        <v>231.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>38.6</v>
+      </c>
+      <c r="K58">
+        <v>23.7</v>
+      </c>
+      <c r="L58">
+        <v>14.9</v>
+      </c>
+      <c r="M58">
+        <v>65.88778560000002</v>
+      </c>
+      <c r="N58">
+        <v>-50.98778560000001</v>
+      </c>
+      <c r="O58">
+        <v>-10.19755712</v>
+      </c>
+      <c r="P58">
+        <v>-40.79022848000001</v>
+      </c>
+      <c r="Q58">
+        <v>-17.09022848000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1483989284096086</v>
+      </c>
+      <c r="T58">
+        <v>1.659594547717547</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0452284133221803</v>
+      </c>
+      <c r="W58">
+        <v>0.2279994548986634</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2261420666109016</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1949752232434793</v>
+      </c>
+      <c r="C59">
+        <v>-55.78197521363523</v>
+      </c>
+      <c r="D59">
+        <v>111.0570247863647</v>
+      </c>
+      <c r="E59">
+        <v>19.93900000000002</v>
+      </c>
+      <c r="F59">
+        <v>280.839</v>
+      </c>
+      <c r="G59">
+        <v>114</v>
+      </c>
+      <c r="H59">
+        <v>231.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>38.6</v>
+      </c>
+      <c r="K59">
+        <v>23.7</v>
+      </c>
+      <c r="L59">
+        <v>14.9</v>
+      </c>
+      <c r="M59">
+        <v>67.0643532</v>
+      </c>
+      <c r="N59">
+        <v>-52.16435319999999</v>
+      </c>
+      <c r="O59">
+        <v>-10.43287064</v>
+      </c>
+      <c r="P59">
+        <v>-41.73148256</v>
+      </c>
+      <c r="Q59">
+        <v>-18.03148256</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1509477406982042</v>
+      </c>
+      <c r="T59">
+        <v>1.69818976975749</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04443493238670346</v>
+      </c>
+      <c r="W59">
+        <v>0.2281889381460552</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2221746619335174</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1969752232434793</v>
+      </c>
+      <c r="C60">
+        <v>-62.11320303780479</v>
+      </c>
+      <c r="D60">
+        <v>109.6527969621952</v>
+      </c>
+      <c r="E60">
+        <v>24.86599999999999</v>
+      </c>
+      <c r="F60">
+        <v>285.766</v>
+      </c>
+      <c r="G60">
+        <v>114</v>
+      </c>
+      <c r="H60">
+        <v>231.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>38.6</v>
+      </c>
+      <c r="K60">
+        <v>23.7</v>
+      </c>
+      <c r="L60">
+        <v>14.9</v>
+      </c>
+      <c r="M60">
+        <v>68.2409208</v>
+      </c>
+      <c r="N60">
+        <v>-53.34092079999999</v>
+      </c>
+      <c r="O60">
+        <v>-10.66818416</v>
+      </c>
+      <c r="P60">
+        <v>-42.67273664</v>
+      </c>
+      <c r="Q60">
+        <v>-18.97273664</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1536179250005423</v>
+      </c>
+      <c r="T60">
+        <v>1.73862285951362</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04366881286279478</v>
+      </c>
+      <c r="W60">
+        <v>0.2283718874883646</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.218344064313974</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1989752232434793</v>
+      </c>
+      <c r="C61">
+        <v>-68.40936357014903</v>
+      </c>
+      <c r="D61">
+        <v>108.2836364298509</v>
+      </c>
+      <c r="E61">
+        <v>29.79300000000001</v>
+      </c>
+      <c r="F61">
+        <v>290.693</v>
+      </c>
+      <c r="G61">
+        <v>114</v>
+      </c>
+      <c r="H61">
+        <v>231.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>38.6</v>
+      </c>
+      <c r="K61">
+        <v>23.7</v>
+      </c>
+      <c r="L61">
+        <v>14.9</v>
+      </c>
+      <c r="M61">
+        <v>69.4174884</v>
+      </c>
+      <c r="N61">
+        <v>-54.51748839999999</v>
+      </c>
+      <c r="O61">
+        <v>-10.90349768</v>
+      </c>
+      <c r="P61">
+        <v>-43.61399072</v>
+      </c>
+      <c r="Q61">
+        <v>-19.91399072</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1564183621956775</v>
+      </c>
+      <c r="T61">
+        <v>1.781028295111514</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04292866349223894</v>
+      </c>
+      <c r="W61">
+        <v>0.2285486351580534</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2146433174611948</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2009752232434793</v>
+      </c>
+      <c r="C62">
+        <v>-74.67175419596961</v>
+      </c>
+      <c r="D62">
+        <v>106.9482458040304</v>
+      </c>
+      <c r="E62">
+        <v>34.72000000000003</v>
+      </c>
+      <c r="F62">
+        <v>295.62</v>
+      </c>
+      <c r="G62">
+        <v>114</v>
+      </c>
+      <c r="H62">
+        <v>231.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>38.6</v>
+      </c>
+      <c r="K62">
+        <v>23.7</v>
+      </c>
+      <c r="L62">
+        <v>14.9</v>
+      </c>
+      <c r="M62">
+        <v>70.59405600000001</v>
+      </c>
+      <c r="N62">
+        <v>-55.694056</v>
+      </c>
+      <c r="O62">
+        <v>-11.1388112</v>
+      </c>
+      <c r="P62">
+        <v>-44.5552448</v>
+      </c>
+      <c r="Q62">
+        <v>-20.8552448</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1593588212505694</v>
+      </c>
+      <c r="T62">
+        <v>1.825554002489301</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04221318576736828</v>
+      </c>
+      <c r="W62">
+        <v>0.2287194912387525</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2110659288368415</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2029752232434793</v>
+      </c>
+      <c r="C63">
+        <v>-80.90160908102644</v>
+      </c>
+      <c r="D63">
+        <v>105.6453909189735</v>
+      </c>
+      <c r="E63">
+        <v>39.64699999999999</v>
+      </c>
+      <c r="F63">
+        <v>300.547</v>
+      </c>
+      <c r="G63">
+        <v>114</v>
+      </c>
+      <c r="H63">
+        <v>231.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>38.6</v>
+      </c>
+      <c r="K63">
+        <v>23.7</v>
+      </c>
+      <c r="L63">
+        <v>14.9</v>
+      </c>
+      <c r="M63">
+        <v>71.77062359999999</v>
+      </c>
+      <c r="N63">
+        <v>-56.87062359999999</v>
+      </c>
+      <c r="O63">
+        <v>-11.37412472</v>
+      </c>
+      <c r="P63">
+        <v>-45.49649887999999</v>
+      </c>
+      <c r="Q63">
+        <v>-21.79649887999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1624500730775071</v>
+      </c>
+      <c r="T63">
+        <v>1.872363079476207</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04152116632855898</v>
+      </c>
+      <c r="W63">
+        <v>0.2288847454807401</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.207605831642795</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2049752232434792</v>
+      </c>
+      <c r="C64">
+        <v>-87.10010297592771</v>
+      </c>
+      <c r="D64">
+        <v>104.3738970240723</v>
+      </c>
+      <c r="E64">
+        <v>44.57400000000001</v>
+      </c>
+      <c r="F64">
+        <v>305.474</v>
+      </c>
+      <c r="G64">
+        <v>114</v>
+      </c>
+      <c r="H64">
+        <v>231.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>38.6</v>
+      </c>
+      <c r="K64">
+        <v>23.7</v>
+      </c>
+      <c r="L64">
+        <v>14.9</v>
+      </c>
+      <c r="M64">
+        <v>72.94719120000001</v>
+      </c>
+      <c r="N64">
+        <v>-58.0471912</v>
+      </c>
+      <c r="O64">
+        <v>-11.60943824</v>
+      </c>
+      <c r="P64">
+        <v>-46.43775296</v>
+      </c>
+      <c r="Q64">
+        <v>-22.73775296000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1657040223690205</v>
+      </c>
+      <c r="T64">
+        <v>1.921635792094002</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04085147009745318</v>
+      </c>
+      <c r="W64">
+        <v>0.2290446689407282</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.204257350487266</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2069752232434793</v>
+      </c>
+      <c r="C65">
+        <v>-93.26835474906159</v>
+      </c>
+      <c r="D65">
+        <v>103.1326452509384</v>
+      </c>
+      <c r="E65">
+        <v>49.50100000000003</v>
+      </c>
+      <c r="F65">
+        <v>310.401</v>
+      </c>
+      <c r="G65">
+        <v>114</v>
+      </c>
+      <c r="H65">
+        <v>231.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>38.6</v>
+      </c>
+      <c r="K65">
+        <v>23.7</v>
+      </c>
+      <c r="L65">
+        <v>14.9</v>
+      </c>
+      <c r="M65">
+        <v>74.1237588</v>
+      </c>
+      <c r="N65">
+        <v>-59.2237588</v>
+      </c>
+      <c r="O65">
+        <v>-11.84475176</v>
+      </c>
+      <c r="P65">
+        <v>-47.37900704</v>
+      </c>
+      <c r="Q65">
+        <v>-23.67900704000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1691338608114264</v>
+      </c>
+      <c r="T65">
+        <v>1.973571894583029</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04020303406416027</v>
+      </c>
+      <c r="W65">
+        <v>0.2291995154654785</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2010151703208014</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2089752232434792</v>
+      </c>
+      <c r="C66">
+        <v>-99.40743067040032</v>
+      </c>
+      <c r="D66">
+        <v>101.9205693295997</v>
+      </c>
+      <c r="E66">
+        <v>54.428</v>
+      </c>
+      <c r="F66">
+        <v>315.328</v>
+      </c>
+      <c r="G66">
+        <v>114</v>
+      </c>
+      <c r="H66">
+        <v>231.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>38.6</v>
+      </c>
+      <c r="K66">
+        <v>23.7</v>
+      </c>
+      <c r="L66">
+        <v>14.9</v>
+      </c>
+      <c r="M66">
+        <v>75.3003264</v>
+      </c>
+      <c r="N66">
+        <v>-60.4003264</v>
+      </c>
+      <c r="O66">
+        <v>-12.08006528</v>
+      </c>
+      <c r="P66">
+        <v>-48.32026112</v>
+      </c>
+      <c r="Q66">
+        <v>-24.62026112</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.172754245833966</v>
+      </c>
+      <c r="T66">
+        <v>2.028393336099224</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03957486165690777</v>
+      </c>
+      <c r="W66">
+        <v>0.2293495230363304</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1978743082845389</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2109752232434793</v>
+      </c>
+      <c r="C67">
+        <v>-105.5183474664364</v>
+      </c>
+      <c r="D67">
+        <v>100.7366525335636</v>
+      </c>
+      <c r="E67">
+        <v>59.35500000000002</v>
+      </c>
+      <c r="F67">
+        <v>320.255</v>
+      </c>
+      <c r="G67">
+        <v>114</v>
+      </c>
+      <c r="H67">
+        <v>231.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>38.6</v>
+      </c>
+      <c r="K67">
+        <v>23.7</v>
+      </c>
+      <c r="L67">
+        <v>14.9</v>
+      </c>
+      <c r="M67">
+        <v>76.476894</v>
+      </c>
+      <c r="N67">
+        <v>-61.576894</v>
+      </c>
+      <c r="O67">
+        <v>-12.3153788</v>
+      </c>
+      <c r="P67">
+        <v>-49.2615152</v>
+      </c>
+      <c r="Q67">
+        <v>-25.5615152</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1765815100006508</v>
+      </c>
+      <c r="T67">
+        <v>2.086347431416345</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03896601763141688</v>
+      </c>
+      <c r="W67">
+        <v>0.2294949149896177</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1948300881570845</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2129752232434793</v>
+      </c>
+      <c r="C68">
+        <v>-111.6020751646434</v>
+      </c>
+      <c r="D68">
+        <v>99.57992483535659</v>
+      </c>
+      <c r="E68">
+        <v>64.28200000000004</v>
+      </c>
+      <c r="F68">
+        <v>325.182</v>
+      </c>
+      <c r="G68">
+        <v>114</v>
+      </c>
+      <c r="H68">
+        <v>231.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>38.6</v>
+      </c>
+      <c r="K68">
+        <v>23.7</v>
+      </c>
+      <c r="L68">
+        <v>14.9</v>
+      </c>
+      <c r="M68">
+        <v>77.65346160000001</v>
+      </c>
+      <c r="N68">
+        <v>-62.75346160000001</v>
+      </c>
+      <c r="O68">
+        <v>-12.55069232</v>
+      </c>
+      <c r="P68">
+        <v>-50.20276928000001</v>
+      </c>
+      <c r="Q68">
+        <v>-26.50276928000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1806339073536111</v>
+      </c>
+      <c r="T68">
+        <v>2.147710591163885</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03837562342488025</v>
+      </c>
+      <c r="W68">
+        <v>0.2296359011261386</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1918781171244014</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2149752232434793</v>
+      </c>
+      <c r="C69">
+        <v>-117.6595397441914</v>
+      </c>
+      <c r="D69">
+        <v>98.4494602558086</v>
+      </c>
+      <c r="E69">
+        <v>69.20900000000006</v>
+      </c>
+      <c r="F69">
+        <v>330.109</v>
+      </c>
+      <c r="G69">
+        <v>114</v>
+      </c>
+      <c r="H69">
+        <v>231.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>38.6</v>
+      </c>
+      <c r="K69">
+        <v>23.7</v>
+      </c>
+      <c r="L69">
+        <v>14.9</v>
+      </c>
+      <c r="M69">
+        <v>78.83002920000001</v>
+      </c>
+      <c r="N69">
+        <v>-63.93002920000001</v>
+      </c>
+      <c r="O69">
+        <v>-12.78600584</v>
+      </c>
+      <c r="P69">
+        <v>-51.14402336000001</v>
+      </c>
+      <c r="Q69">
+        <v>-27.44402336000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1849319045461448</v>
+      </c>
+      <c r="T69">
+        <v>2.212792730290063</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03780285292600144</v>
+      </c>
+      <c r="W69">
+        <v>0.2297726787212709</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1890142646300073</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2169752232434793</v>
+      </c>
+      <c r="C70">
+        <v>-123.6916256081364</v>
+      </c>
+      <c r="D70">
+        <v>97.34437439186361</v>
+      </c>
+      <c r="E70">
+        <v>74.13600000000002</v>
+      </c>
+      <c r="F70">
+        <v>335.036</v>
+      </c>
+      <c r="G70">
+        <v>114</v>
+      </c>
+      <c r="H70">
+        <v>231.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>38.6</v>
+      </c>
+      <c r="K70">
+        <v>23.7</v>
+      </c>
+      <c r="L70">
+        <v>14.9</v>
+      </c>
+      <c r="M70">
+        <v>80.00659680000001</v>
+      </c>
+      <c r="N70">
+        <v>-65.10659680000001</v>
+      </c>
+      <c r="O70">
+        <v>-13.02131936</v>
+      </c>
+      <c r="P70">
+        <v>-52.08527744000001</v>
+      </c>
+      <c r="Q70">
+        <v>-28.38527744000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1894985265632118</v>
+      </c>
+      <c r="T70">
+        <v>2.281942503111627</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03724692861826613</v>
+      </c>
+      <c r="W70">
+        <v>0.229905433445958</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1862346430913308</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2189752232434793</v>
+      </c>
+      <c r="C71">
+        <v>-129.6991778909586</v>
+      </c>
+      <c r="D71">
+        <v>96.26382210904146</v>
+      </c>
+      <c r="E71">
+        <v>79.06300000000005</v>
+      </c>
+      <c r="F71">
+        <v>339.963</v>
+      </c>
+      <c r="G71">
+        <v>114</v>
+      </c>
+      <c r="H71">
+        <v>231.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>38.6</v>
+      </c>
+      <c r="K71">
+        <v>23.7</v>
+      </c>
+      <c r="L71">
+        <v>14.9</v>
+      </c>
+      <c r="M71">
+        <v>81.18316440000001</v>
+      </c>
+      <c r="N71">
+        <v>-66.2831644</v>
+      </c>
+      <c r="O71">
+        <v>-13.25663288</v>
+      </c>
+      <c r="P71">
+        <v>-53.02653152000001</v>
+      </c>
+      <c r="Q71">
+        <v>-29.32653152000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1943597693555735</v>
+      </c>
+      <c r="T71">
+        <v>2.355553551599099</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03670711805858112</v>
+      </c>
+      <c r="W71">
+        <v>0.2300343402076108</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1835355902929057</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2209752232434793</v>
+      </c>
+      <c r="C72">
+        <v>-135.6830046141007</v>
+      </c>
+      <c r="D72">
+        <v>95.20699538589938</v>
+      </c>
+      <c r="E72">
+        <v>83.99000000000007</v>
+      </c>
+      <c r="F72">
+        <v>344.89</v>
+      </c>
+      <c r="G72">
+        <v>114</v>
+      </c>
+      <c r="H72">
+        <v>231.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>38.6</v>
+      </c>
+      <c r="K72">
+        <v>23.7</v>
+      </c>
+      <c r="L72">
+        <v>14.9</v>
+      </c>
+      <c r="M72">
+        <v>82.35973200000001</v>
+      </c>
+      <c r="N72">
+        <v>-67.459732</v>
+      </c>
+      <c r="O72">
+        <v>-13.4919464</v>
+      </c>
+      <c r="P72">
+        <v>-53.96778560000001</v>
+      </c>
+      <c r="Q72">
+        <v>-30.26778560000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1995450950007593</v>
+      </c>
+      <c r="T72">
+        <v>2.434072003319069</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03618273065774424</v>
+      </c>
+      <c r="W72">
+        <v>0.2301595639189307</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1809136532887213</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2229752232434792</v>
+      </c>
+      <c r="C73">
+        <v>-141.6438787010621</v>
+      </c>
+      <c r="D73">
+        <v>94.17312129893783</v>
+      </c>
+      <c r="E73">
+        <v>88.91699999999997</v>
+      </c>
+      <c r="F73">
+        <v>349.817</v>
+      </c>
+      <c r="G73">
+        <v>114</v>
+      </c>
+      <c r="H73">
+        <v>231.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>38.6</v>
+      </c>
+      <c r="K73">
+        <v>23.7</v>
+      </c>
+      <c r="L73">
+        <v>14.9</v>
+      </c>
+      <c r="M73">
+        <v>83.53629959999999</v>
+      </c>
+      <c r="N73">
+        <v>-68.63629959999999</v>
+      </c>
+      <c r="O73">
+        <v>-13.72725991999999</v>
+      </c>
+      <c r="P73">
+        <v>-54.90903967999999</v>
+      </c>
+      <c r="Q73">
+        <v>-31.20903967999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2050880293111303</v>
+      </c>
+      <c r="T73">
+        <v>2.518005520674899</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03567311473298729</v>
+      </c>
+      <c r="W73">
+        <v>0.2302812602017626</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1783655736649365</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2249752232434792</v>
+      </c>
+      <c r="C74">
+        <v>-147.5825398626097</v>
+      </c>
+      <c r="D74">
+        <v>93.16146013739025</v>
+      </c>
+      <c r="E74">
+        <v>93.84399999999999</v>
+      </c>
+      <c r="F74">
+        <v>354.744</v>
+      </c>
+      <c r="G74">
+        <v>114</v>
+      </c>
+      <c r="H74">
+        <v>231.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>38.6</v>
+      </c>
+      <c r="K74">
+        <v>23.7</v>
+      </c>
+      <c r="L74">
+        <v>14.9</v>
+      </c>
+      <c r="M74">
+        <v>84.71286719999999</v>
+      </c>
+      <c r="N74">
+        <v>-69.81286719999999</v>
+      </c>
+      <c r="O74">
+        <v>-13.96257343999999</v>
+      </c>
+      <c r="P74">
+        <v>-55.85029375999999</v>
+      </c>
+      <c r="Q74">
+        <v>-32.15029376</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2110268875008135</v>
+      </c>
+      <c r="T74">
+        <v>2.607934289270431</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03517765480614024</v>
+      </c>
+      <c r="W74">
+        <v>0.2303995760322937</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1758882740307013</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2269752232434793</v>
+      </c>
+      <c r="C75">
+        <v>-153.4996963617664</v>
+      </c>
+      <c r="D75">
+        <v>92.17130363823361</v>
+      </c>
+      <c r="E75">
+        <v>98.77100000000002</v>
+      </c>
+      <c r="F75">
+        <v>359.671</v>
+      </c>
+      <c r="G75">
+        <v>114</v>
+      </c>
+      <c r="H75">
+        <v>231.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>38.6</v>
+      </c>
+      <c r="K75">
+        <v>23.7</v>
+      </c>
+      <c r="L75">
+        <v>14.9</v>
+      </c>
+      <c r="M75">
+        <v>85.8894348</v>
+      </c>
+      <c r="N75">
+        <v>-70.9894348</v>
+      </c>
+      <c r="O75">
+        <v>-14.19788696</v>
+      </c>
+      <c r="P75">
+        <v>-56.79154784</v>
+      </c>
+      <c r="Q75">
+        <v>-33.09154784</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2174056611119547</v>
+      </c>
+      <c r="T75">
+        <v>2.704524448132299</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03469576912386434</v>
+      </c>
+      <c r="W75">
+        <v>0.2305146503332212</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1734788456193218</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2289752232434792</v>
+      </c>
+      <c r="C76">
+        <v>-159.3960266674312</v>
+      </c>
+      <c r="D76">
+        <v>91.20197333256884</v>
+      </c>
+      <c r="E76">
+        <v>103.698</v>
+      </c>
+      <c r="F76">
+        <v>364.598</v>
+      </c>
+      <c r="G76">
+        <v>114</v>
+      </c>
+      <c r="H76">
+        <v>231.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>38.6</v>
+      </c>
+      <c r="K76">
+        <v>23.7</v>
+      </c>
+      <c r="L76">
+        <v>14.9</v>
+      </c>
+      <c r="M76">
+        <v>87.0660024</v>
+      </c>
+      <c r="N76">
+        <v>-72.1660024</v>
+      </c>
+      <c r="O76">
+        <v>-14.43320048</v>
+      </c>
+      <c r="P76">
+        <v>-57.73280192</v>
+      </c>
+      <c r="Q76">
+        <v>-34.03280192</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2242751096162607</v>
+      </c>
+      <c r="T76">
+        <v>2.80854461921431</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03422690737894726</v>
+      </c>
+      <c r="W76">
+        <v>0.2306266145179074</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1711345368947363</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2309752232434793</v>
+      </c>
+      <c r="C77">
+        <v>-165.2721810047415</v>
+      </c>
+      <c r="D77">
+        <v>90.25281899525848</v>
+      </c>
+      <c r="E77">
+        <v>108.625</v>
+      </c>
+      <c r="F77">
+        <v>369.525</v>
+      </c>
+      <c r="G77">
+        <v>114</v>
+      </c>
+      <c r="H77">
+        <v>231.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>38.6</v>
+      </c>
+      <c r="K77">
+        <v>23.7</v>
+      </c>
+      <c r="L77">
+        <v>14.9</v>
+      </c>
+      <c r="M77">
+        <v>88.24257</v>
+      </c>
+      <c r="N77">
+        <v>-73.34256999999999</v>
+      </c>
+      <c r="O77">
+        <v>-14.668514</v>
+      </c>
+      <c r="P77">
+        <v>-58.674056</v>
+      </c>
+      <c r="Q77">
+        <v>-34.974056</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2316941140009111</v>
+      </c>
+      <c r="T77">
+        <v>2.920886403982883</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03377054861389463</v>
+      </c>
+      <c r="W77">
+        <v>0.230735592991002</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1688527430694732</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2329752232434793</v>
+      </c>
+      <c r="C78">
+        <v>-171.1287828096236</v>
+      </c>
+      <c r="D78">
+        <v>89.32321719037638</v>
+      </c>
+      <c r="E78">
+        <v>113.552</v>
+      </c>
+      <c r="F78">
+        <v>374.452</v>
+      </c>
+      <c r="G78">
+        <v>114</v>
+      </c>
+      <c r="H78">
+        <v>231.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>38.6</v>
+      </c>
+      <c r="K78">
+        <v>23.7</v>
+      </c>
+      <c r="L78">
+        <v>14.9</v>
+      </c>
+      <c r="M78">
+        <v>89.4191376</v>
+      </c>
+      <c r="N78">
+        <v>-74.51913759999999</v>
+      </c>
+      <c r="O78">
+        <v>-14.90382751999999</v>
+      </c>
+      <c r="P78">
+        <v>-59.61531008</v>
+      </c>
+      <c r="Q78">
+        <v>-35.91531008</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2397313687509491</v>
+      </c>
+      <c r="T78">
+        <v>3.042590004148837</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03332619929002759</v>
+      </c>
+      <c r="W78">
+        <v>0.2308417036095414</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.166630996450138</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2349752232434793</v>
+      </c>
+      <c r="C79">
+        <v>-176.9664300943678</v>
+      </c>
+      <c r="D79">
+        <v>88.41256990563224</v>
+      </c>
+      <c r="E79">
+        <v>118.479</v>
+      </c>
+      <c r="F79">
+        <v>379.379</v>
+      </c>
+      <c r="G79">
+        <v>114</v>
+      </c>
+      <c r="H79">
+        <v>231.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>38.6</v>
+      </c>
+      <c r="K79">
+        <v>23.7</v>
+      </c>
+      <c r="L79">
+        <v>14.9</v>
+      </c>
+      <c r="M79">
+        <v>90.59570520000001</v>
+      </c>
+      <c r="N79">
+        <v>-75.69570520000001</v>
+      </c>
+      <c r="O79">
+        <v>-15.13914104</v>
+      </c>
+      <c r="P79">
+        <v>-60.55656416000001</v>
+      </c>
+      <c r="Q79">
+        <v>-36.85656416</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2484675152183817</v>
+      </c>
+      <c r="T79">
+        <v>3.174876526068351</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03289339150704022</v>
+      </c>
+      <c r="W79">
+        <v>0.2309450581081188</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1644669575352011</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2369752232434793</v>
+      </c>
+      <c r="C80">
+        <v>-182.7856967305154</v>
+      </c>
+      <c r="D80">
+        <v>87.52030326948463</v>
+      </c>
+      <c r="E80">
+        <v>123.406</v>
+      </c>
+      <c r="F80">
+        <v>384.306</v>
+      </c>
+      <c r="G80">
+        <v>114</v>
+      </c>
+      <c r="H80">
+        <v>231.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>38.6</v>
+      </c>
+      <c r="K80">
+        <v>23.7</v>
+      </c>
+      <c r="L80">
+        <v>14.9</v>
+      </c>
+      <c r="M80">
+        <v>91.7722728</v>
+      </c>
+      <c r="N80">
+        <v>-76.87227279999999</v>
+      </c>
+      <c r="O80">
+        <v>-15.37445455999999</v>
+      </c>
+      <c r="P80">
+        <v>-61.49781823999999</v>
+      </c>
+      <c r="Q80">
+        <v>-37.79781824</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2579978568192172</v>
+      </c>
+      <c r="T80">
+        <v>3.319189095435094</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03247168135951407</v>
+      </c>
+      <c r="W80">
+        <v>0.2310457624913481</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1623584067975704</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2389752232434793</v>
+      </c>
+      <c r="C81">
+        <v>-188.5871336548397</v>
+      </c>
+      <c r="D81">
+        <v>86.64586634516029</v>
+      </c>
+      <c r="E81">
+        <v>128.333</v>
+      </c>
+      <c r="F81">
+        <v>389.233</v>
+      </c>
+      <c r="G81">
+        <v>114</v>
+      </c>
+      <c r="H81">
+        <v>231.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>38.6</v>
+      </c>
+      <c r="K81">
+        <v>23.7</v>
+      </c>
+      <c r="L81">
+        <v>14.9</v>
+      </c>
+      <c r="M81">
+        <v>92.94884040000001</v>
+      </c>
+      <c r="N81">
+        <v>-78.0488404</v>
+      </c>
+      <c r="O81">
+        <v>-15.60976808</v>
+      </c>
+      <c r="P81">
+        <v>-62.43907232000001</v>
+      </c>
+      <c r="Q81">
+        <v>-38.73907232000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2684358500010847</v>
+      </c>
+      <c r="T81">
+        <v>3.477245719027242</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03206064741825439</v>
+      </c>
+      <c r="W81">
+        <v>0.2311439173965208</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.160303237091272</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2409752232434793</v>
+      </c>
+      <c r="C82">
+        <v>-194.3712700037465</v>
+      </c>
+      <c r="D82">
+        <v>85.78872999625351</v>
+      </c>
+      <c r="E82">
+        <v>133.26</v>
+      </c>
+      <c r="F82">
+        <v>394.16</v>
+      </c>
+      <c r="G82">
+        <v>114</v>
+      </c>
+      <c r="H82">
+        <v>231.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>38.6</v>
+      </c>
+      <c r="K82">
+        <v>23.7</v>
+      </c>
+      <c r="L82">
+        <v>14.9</v>
+      </c>
+      <c r="M82">
+        <v>94.12540800000001</v>
+      </c>
+      <c r="N82">
+        <v>-79.225408</v>
+      </c>
+      <c r="O82">
+        <v>-15.8450816</v>
+      </c>
+      <c r="P82">
+        <v>-63.3803264</v>
+      </c>
+      <c r="Q82">
+        <v>-39.6803264</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2799176425011389</v>
+      </c>
+      <c r="T82">
+        <v>3.651108004978604</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03165988932552621</v>
+      </c>
+      <c r="W82">
+        <v>0.2312396184290643</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1582994466276312</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2429752232434793</v>
+      </c>
+      <c r="C83">
+        <v>-200.138614181002</v>
+      </c>
+      <c r="D83">
+        <v>84.94838581899798</v>
+      </c>
+      <c r="E83">
+        <v>138.187</v>
+      </c>
+      <c r="F83">
+        <v>399.087</v>
+      </c>
+      <c r="G83">
+        <v>114</v>
+      </c>
+      <c r="H83">
+        <v>231.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>38.6</v>
+      </c>
+      <c r="K83">
+        <v>23.7</v>
+      </c>
+      <c r="L83">
+        <v>14.9</v>
+      </c>
+      <c r="M83">
+        <v>95.30197560000001</v>
+      </c>
+      <c r="N83">
+        <v>-80.4019756</v>
+      </c>
+      <c r="O83">
+        <v>-16.08039512</v>
+      </c>
+      <c r="P83">
+        <v>-64.32158048000001</v>
+      </c>
+      <c r="Q83">
+        <v>-40.62158048000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.292608044738041</v>
+      </c>
+      <c r="T83">
+        <v>3.843271584188005</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03126902649434688</v>
+      </c>
+      <c r="W83">
+        <v>0.23133295647315</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1563451324717344</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2449752232434793</v>
+      </c>
+      <c r="C84">
+        <v>-205.889654863317</v>
+      </c>
+      <c r="D84">
+        <v>84.12434513668305</v>
+      </c>
+      <c r="E84">
+        <v>143.114</v>
+      </c>
+      <c r="F84">
+        <v>404.014</v>
+      </c>
+      <c r="G84">
+        <v>114</v>
+      </c>
+      <c r="H84">
+        <v>231.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>38.6</v>
+      </c>
+      <c r="K84">
+        <v>23.7</v>
+      </c>
+      <c r="L84">
+        <v>14.9</v>
+      </c>
+      <c r="M84">
+        <v>96.4785432</v>
+      </c>
+      <c r="N84">
+        <v>-81.5785432</v>
+      </c>
+      <c r="O84">
+        <v>-16.31570864</v>
+      </c>
+      <c r="P84">
+        <v>-65.26283456</v>
+      </c>
+      <c r="Q84">
+        <v>-41.56283456</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3067084916679322</v>
+      </c>
+      <c r="T84">
+        <v>4.05678667219845</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0308876969029524</v>
+      </c>
+      <c r="W84">
+        <v>0.231424017979575</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1544384845147621</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2469752232434793</v>
+      </c>
+      <c r="C85">
+        <v>-211.6248619479641</v>
+      </c>
+      <c r="D85">
+        <v>83.31613805203597</v>
+      </c>
+      <c r="E85">
+        <v>148.0410000000001</v>
+      </c>
+      <c r="F85">
+        <v>408.941</v>
+      </c>
+      <c r="G85">
+        <v>114</v>
+      </c>
+      <c r="H85">
+        <v>231.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>38.6</v>
+      </c>
+      <c r="K85">
+        <v>23.7</v>
+      </c>
+      <c r="L85">
+        <v>14.9</v>
+      </c>
+      <c r="M85">
+        <v>97.65511080000002</v>
+      </c>
+      <c r="N85">
+        <v>-82.75511080000001</v>
+      </c>
+      <c r="O85">
+        <v>-16.55102216</v>
+      </c>
+      <c r="P85">
+        <v>-66.20408864000001</v>
+      </c>
+      <c r="Q85">
+        <v>-42.50408864000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3224678147072223</v>
+      </c>
+      <c r="T85">
+        <v>4.29542118232777</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03051555597641081</v>
+      </c>
+      <c r="W85">
+        <v>0.2315128852328331</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1525777798820541</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2489752232434793</v>
+      </c>
+      <c r="C86">
+        <v>-217.3446874462914</v>
+      </c>
+      <c r="D86">
+        <v>82.52331255370862</v>
+      </c>
+      <c r="E86">
+        <v>152.968</v>
+      </c>
+      <c r="F86">
+        <v>413.868</v>
+      </c>
+      <c r="G86">
+        <v>114</v>
+      </c>
+      <c r="H86">
+        <v>231.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>38.6</v>
+      </c>
+      <c r="K86">
+        <v>23.7</v>
+      </c>
+      <c r="L86">
+        <v>14.9</v>
+      </c>
+      <c r="M86">
+        <v>98.8316784</v>
+      </c>
+      <c r="N86">
+        <v>-83.9316784</v>
+      </c>
+      <c r="O86">
+        <v>-16.78633568</v>
+      </c>
+      <c r="P86">
+        <v>-67.14534272</v>
+      </c>
+      <c r="Q86">
+        <v>-43.44534272</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3401970531264236</v>
+      </c>
+      <c r="T86">
+        <v>4.563885006223253</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0301522755481202</v>
+      </c>
+      <c r="W86">
+        <v>0.2315996365991089</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1507613777406011</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2509752232434793</v>
+      </c>
+      <c r="C87">
+        <v>-223.0495663267015</v>
+      </c>
+      <c r="D87">
+        <v>81.74543367329844</v>
+      </c>
+      <c r="E87">
+        <v>157.895</v>
+      </c>
+      <c r="F87">
+        <v>418.795</v>
+      </c>
+      <c r="G87">
+        <v>114</v>
+      </c>
+      <c r="H87">
+        <v>231.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>38.6</v>
+      </c>
+      <c r="K87">
+        <v>23.7</v>
+      </c>
+      <c r="L87">
+        <v>14.9</v>
+      </c>
+      <c r="M87">
+        <v>100.008246</v>
+      </c>
+      <c r="N87">
+        <v>-85.10824599999999</v>
+      </c>
+      <c r="O87">
+        <v>-17.0216492</v>
+      </c>
+      <c r="P87">
+        <v>-68.0865968</v>
+      </c>
+      <c r="Q87">
+        <v>-44.38659679999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3602901900015185</v>
+      </c>
+      <c r="T87">
+        <v>4.868144006638137</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02979754289461291</v>
+      </c>
+      <c r="W87">
+        <v>0.2316843467567664</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1489877144730646</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2529752232434793</v>
+      </c>
+      <c r="C88">
+        <v>-228.7399173103993</v>
+      </c>
+      <c r="D88">
+        <v>80.98208268960066</v>
+      </c>
+      <c r="E88">
+        <v>162.822</v>
+      </c>
+      <c r="F88">
+        <v>423.722</v>
+      </c>
+      <c r="G88">
+        <v>114</v>
+      </c>
+      <c r="H88">
+        <v>231.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>38.6</v>
+      </c>
+      <c r="K88">
+        <v>23.7</v>
+      </c>
+      <c r="L88">
+        <v>14.9</v>
+      </c>
+      <c r="M88">
+        <v>101.1848136</v>
+      </c>
+      <c r="N88">
+        <v>-86.28481359999999</v>
+      </c>
+      <c r="O88">
+        <v>-17.25696271999999</v>
+      </c>
+      <c r="P88">
+        <v>-69.02785088</v>
+      </c>
+      <c r="Q88">
+        <v>-45.32785088</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.383253775001627</v>
+      </c>
+      <c r="T88">
+        <v>5.215868578540862</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0294510598376988</v>
+      </c>
+      <c r="W88">
+        <v>0.2317670869107575</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1472552991884941</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2549752232434793</v>
+      </c>
+      <c r="C89">
+        <v>-234.416143622967</v>
+      </c>
+      <c r="D89">
+        <v>80.23285637703303</v>
+      </c>
+      <c r="E89">
+        <v>167.749</v>
+      </c>
+      <c r="F89">
+        <v>428.649</v>
+      </c>
+      <c r="G89">
+        <v>114</v>
+      </c>
+      <c r="H89">
+        <v>231.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>38.6</v>
+      </c>
+      <c r="K89">
+        <v>23.7</v>
+      </c>
+      <c r="L89">
+        <v>14.9</v>
+      </c>
+      <c r="M89">
+        <v>102.3613812</v>
+      </c>
+      <c r="N89">
+        <v>-87.46138120000001</v>
+      </c>
+      <c r="O89">
+        <v>-17.49227624</v>
+      </c>
+      <c r="P89">
+        <v>-69.96910496000001</v>
+      </c>
+      <c r="Q89">
+        <v>-46.26910496000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4097502192325214</v>
+      </c>
+      <c r="T89">
+        <v>5.61708923842862</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02911254190852985</v>
+      </c>
+      <c r="W89">
+        <v>0.2318479249922431</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1455627095426493</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2569752232434793</v>
+      </c>
+      <c r="C90">
+        <v>-240.0786337046019</v>
+      </c>
+      <c r="D90">
+        <v>79.49736629539809</v>
+      </c>
+      <c r="E90">
+        <v>172.676</v>
+      </c>
+      <c r="F90">
+        <v>433.576</v>
+      </c>
+      <c r="G90">
+        <v>114</v>
+      </c>
+      <c r="H90">
+        <v>231.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>38.6</v>
+      </c>
+      <c r="K90">
+        <v>23.7</v>
+      </c>
+      <c r="L90">
+        <v>14.9</v>
+      </c>
+      <c r="M90">
+        <v>103.5379488</v>
+      </c>
+      <c r="N90">
+        <v>-88.63794879999999</v>
+      </c>
+      <c r="O90">
+        <v>-17.72758975999999</v>
+      </c>
+      <c r="P90">
+        <v>-70.91035904</v>
+      </c>
+      <c r="Q90">
+        <v>-47.21035904</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4406627375018982</v>
+      </c>
+      <c r="T90">
+        <v>6.085180008297672</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0287817175686602</v>
+      </c>
+      <c r="W90">
+        <v>0.2319269258446039</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1439085878433011</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2589752232434793</v>
+      </c>
+      <c r="C91">
+        <v>-245.7277618816447</v>
+      </c>
+      <c r="D91">
+        <v>78.77523811835533</v>
+      </c>
+      <c r="E91">
+        <v>177.603</v>
+      </c>
+      <c r="F91">
+        <v>438.503</v>
+      </c>
+      <c r="G91">
+        <v>114</v>
+      </c>
+      <c r="H91">
+        <v>231.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>38.6</v>
+      </c>
+      <c r="K91">
+        <v>23.7</v>
+      </c>
+      <c r="L91">
+        <v>14.9</v>
+      </c>
+      <c r="M91">
+        <v>104.7145164</v>
+      </c>
+      <c r="N91">
+        <v>-89.8145164</v>
+      </c>
+      <c r="O91">
+        <v>-17.96290328</v>
+      </c>
+      <c r="P91">
+        <v>-71.85161312000001</v>
+      </c>
+      <c r="Q91">
+        <v>-48.15161312000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4771957136384344</v>
+      </c>
+      <c r="T91">
+        <v>6.638378190870188</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02845832748361907</v>
+      </c>
+      <c r="W91">
+        <v>0.2320041513969118</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1422916374180954</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2609752232434793</v>
+      </c>
+      <c r="C92">
+        <v>-251.3638890018369</v>
+      </c>
+      <c r="D92">
+        <v>78.0661109981631</v>
+      </c>
+      <c r="E92">
+        <v>182.53</v>
+      </c>
+      <c r="F92">
+        <v>443.43</v>
+      </c>
+      <c r="G92">
+        <v>114</v>
+      </c>
+      <c r="H92">
+        <v>231.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>38.6</v>
+      </c>
+      <c r="K92">
+        <v>23.7</v>
+      </c>
+      <c r="L92">
+        <v>14.9</v>
+      </c>
+      <c r="M92">
+        <v>105.891084</v>
+      </c>
+      <c r="N92">
+        <v>-90.991084</v>
+      </c>
+      <c r="O92">
+        <v>-18.1982168</v>
+      </c>
+      <c r="P92">
+        <v>-72.7928672</v>
+      </c>
+      <c r="Q92">
+        <v>-49.0928672</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5210352850022779</v>
+      </c>
+      <c r="T92">
+        <v>7.302216009957208</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02814212384491219</v>
+      </c>
+      <c r="W92">
+        <v>0.232079660825835</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.140710619224561</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2629752232434793</v>
+      </c>
+      <c r="C93">
+        <v>-256.9873630355742</v>
+      </c>
+      <c r="D93">
+        <v>77.36963696442588</v>
+      </c>
+      <c r="E93">
+        <v>187.4570000000001</v>
+      </c>
+      <c r="F93">
+        <v>448.357</v>
+      </c>
+      <c r="G93">
+        <v>114</v>
+      </c>
+      <c r="H93">
+        <v>231.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>38.6</v>
+      </c>
+      <c r="K93">
+        <v>23.7</v>
+      </c>
+      <c r="L93">
+        <v>14.9</v>
+      </c>
+      <c r="M93">
+        <v>107.0676516</v>
+      </c>
+      <c r="N93">
+        <v>-92.16765160000001</v>
+      </c>
+      <c r="O93">
+        <v>-18.43353032</v>
+      </c>
+      <c r="P93">
+        <v>-73.73412128000001</v>
+      </c>
+      <c r="Q93">
+        <v>-50.03412128000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5746169833358643</v>
+      </c>
+      <c r="T93">
+        <v>8.113573344396899</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02783286973672634</v>
+      </c>
+      <c r="W93">
+        <v>0.2321535107068698</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1391643486836317</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2649752232434793</v>
+      </c>
+      <c r="C94">
+        <v>-262.5985196452584</v>
+      </c>
+      <c r="D94">
+        <v>76.68548035474157</v>
+      </c>
+      <c r="E94">
+        <v>192.384</v>
+      </c>
+      <c r="F94">
+        <v>453.284</v>
+      </c>
+      <c r="G94">
+        <v>114</v>
+      </c>
+      <c r="H94">
+        <v>231.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>38.6</v>
+      </c>
+      <c r="K94">
+        <v>23.7</v>
+      </c>
+      <c r="L94">
+        <v>14.9</v>
+      </c>
+      <c r="M94">
+        <v>108.2442192</v>
+      </c>
+      <c r="N94">
+        <v>-93.3442192</v>
+      </c>
+      <c r="O94">
+        <v>-18.66884383999999</v>
+      </c>
+      <c r="P94">
+        <v>-74.67537536</v>
+      </c>
+      <c r="Q94">
+        <v>-50.97537536</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6415941062528476</v>
+      </c>
+      <c r="T94">
+        <v>9.127770012446513</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02753033854393584</v>
+      </c>
+      <c r="W94">
+        <v>0.2322257551557081</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1376516927196793</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2669752232434793</v>
+      </c>
+      <c r="C95">
+        <v>-268.1976827247082</v>
+      </c>
+      <c r="D95">
+        <v>76.01331727529177</v>
+      </c>
+      <c r="E95">
+        <v>197.311</v>
+      </c>
+      <c r="F95">
+        <v>458.211</v>
+      </c>
+      <c r="G95">
+        <v>114</v>
+      </c>
+      <c r="H95">
+        <v>231.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>38.6</v>
+      </c>
+      <c r="K95">
+        <v>23.7</v>
+      </c>
+      <c r="L95">
+        <v>14.9</v>
+      </c>
+      <c r="M95">
+        <v>109.4207868</v>
+      </c>
+      <c r="N95">
+        <v>-94.5207868</v>
+      </c>
+      <c r="O95">
+        <v>-18.90415736</v>
+      </c>
+      <c r="P95">
+        <v>-75.61662944</v>
+      </c>
+      <c r="Q95">
+        <v>-51.91662943999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7277075500032544</v>
+      </c>
+      <c r="T95">
+        <v>10.43173715708173</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02723431339830212</v>
+      </c>
+      <c r="W95">
+        <v>0.2322964459604855</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1361715669915107</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2689752232434793</v>
+      </c>
+      <c r="C96">
+        <v>-273.7851649104463</v>
+      </c>
+      <c r="D96">
+        <v>75.35283508955378</v>
+      </c>
+      <c r="E96">
+        <v>202.2380000000001</v>
+      </c>
+      <c r="F96">
+        <v>463.138</v>
+      </c>
+      <c r="G96">
+        <v>114</v>
+      </c>
+      <c r="H96">
+        <v>231.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>38.6</v>
+      </c>
+      <c r="K96">
+        <v>23.7</v>
+      </c>
+      <c r="L96">
+        <v>14.9</v>
+      </c>
+      <c r="M96">
+        <v>110.5973544</v>
+      </c>
+      <c r="N96">
+        <v>-95.69735440000001</v>
+      </c>
+      <c r="O96">
+        <v>-19.13947088</v>
+      </c>
+      <c r="P96">
+        <v>-76.55788352000002</v>
+      </c>
+      <c r="Q96">
+        <v>-52.85788352000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8425254750037969</v>
+      </c>
+      <c r="T96">
+        <v>12.17036001659535</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02694458666002231</v>
+      </c>
+      <c r="W96">
+        <v>0.2323656327055867</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1347229333001116</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2709752232434793</v>
+      </c>
+      <c r="C97">
+        <v>-279.3612680665615</v>
+      </c>
+      <c r="D97">
+        <v>74.70373193343853</v>
+      </c>
+      <c r="E97">
+        <v>207.165</v>
+      </c>
+      <c r="F97">
+        <v>468.065</v>
+      </c>
+      <c r="G97">
+        <v>114</v>
+      </c>
+      <c r="H97">
+        <v>231.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>38.6</v>
+      </c>
+      <c r="K97">
+        <v>23.7</v>
+      </c>
+      <c r="L97">
+        <v>14.9</v>
+      </c>
+      <c r="M97">
+        <v>111.773922</v>
+      </c>
+      <c r="N97">
+        <v>-96.87392199999999</v>
+      </c>
+      <c r="O97">
+        <v>-19.3747844</v>
+      </c>
+      <c r="P97">
+        <v>-77.4991376</v>
+      </c>
+      <c r="Q97">
+        <v>-53.79913759999999</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.003270570004557</v>
+      </c>
+      <c r="T97">
+        <v>14.60443201991443</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02666095943202207</v>
+      </c>
+      <c r="W97">
+        <v>0.2324333628876331</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1333047971601105</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2729752232434792</v>
+      </c>
+      <c r="C98">
+        <v>-284.9262837447254</v>
+      </c>
+      <c r="D98">
+        <v>74.06571625527459</v>
+      </c>
+      <c r="E98">
+        <v>212.092</v>
+      </c>
+      <c r="F98">
+        <v>472.992</v>
+      </c>
+      <c r="G98">
+        <v>114</v>
+      </c>
+      <c r="H98">
+        <v>231.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>38.6</v>
+      </c>
+      <c r="K98">
+        <v>23.7</v>
+      </c>
+      <c r="L98">
+        <v>14.9</v>
+      </c>
+      <c r="M98">
+        <v>112.9504896</v>
+      </c>
+      <c r="N98">
+        <v>-98.05048959999999</v>
+      </c>
+      <c r="O98">
+        <v>-19.61009791999999</v>
+      </c>
+      <c r="P98">
+        <v>-78.44039168</v>
+      </c>
+      <c r="Q98">
+        <v>-54.74039168</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.244388212505694</v>
+      </c>
+      <c r="T98">
+        <v>18.255540024893</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02638324110460518</v>
+      </c>
+      <c r="W98">
+        <v>0.2324996820242203</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.131916205523026</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2749752232434793</v>
+      </c>
+      <c r="C99">
+        <v>-290.4804936208343</v>
+      </c>
+      <c r="D99">
+        <v>73.43850637916566</v>
+      </c>
+      <c r="E99">
+        <v>217.019</v>
+      </c>
+      <c r="F99">
+        <v>477.919</v>
+      </c>
+      <c r="G99">
+        <v>114</v>
+      </c>
+      <c r="H99">
+        <v>231.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>38.6</v>
+      </c>
+      <c r="K99">
+        <v>23.7</v>
+      </c>
+      <c r="L99">
+        <v>14.9</v>
+      </c>
+      <c r="M99">
+        <v>114.1270572</v>
+      </c>
+      <c r="N99">
+        <v>-99.22705719999999</v>
+      </c>
+      <c r="O99">
+        <v>-19.84541143999999</v>
+      </c>
+      <c r="P99">
+        <v>-79.38164576</v>
+      </c>
+      <c r="Q99">
+        <v>-55.68164575999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.646250950007592</v>
+      </c>
+      <c r="T99">
+        <v>24.34072003319067</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02611124892826904</v>
+      </c>
+      <c r="W99">
+        <v>0.2325646337559294</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1305562446413453</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2769752232434792</v>
+      </c>
+      <c r="C100">
+        <v>-296.0241699096529</v>
+      </c>
+      <c r="D100">
+        <v>72.82183009034706</v>
+      </c>
+      <c r="E100">
+        <v>221.946</v>
+      </c>
+      <c r="F100">
+        <v>482.846</v>
+      </c>
+      <c r="G100">
+        <v>114</v>
+      </c>
+      <c r="H100">
+        <v>231.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>38.6</v>
+      </c>
+      <c r="K100">
+        <v>23.7</v>
+      </c>
+      <c r="L100">
+        <v>14.9</v>
+      </c>
+      <c r="M100">
+        <v>115.3036248</v>
+      </c>
+      <c r="N100">
+        <v>-100.4036248</v>
+      </c>
+      <c r="O100">
+        <v>-20.08072496</v>
+      </c>
+      <c r="P100">
+        <v>-80.32289984000001</v>
+      </c>
+      <c r="Q100">
+        <v>-56.62289984</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.449976425011387</v>
+      </c>
+      <c r="T100">
+        <v>36.511080049786</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02584480761267446</v>
+      </c>
+      <c r="W100">
+        <v>0.2326282599420934</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1292240380633723</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2789752232434792</v>
+      </c>
+      <c r="C101">
+        <v>-301.5575757587402</v>
+      </c>
+      <c r="D101">
+        <v>72.21542424125974</v>
+      </c>
+      <c r="E101">
+        <v>226.873</v>
+      </c>
+      <c r="F101">
+        <v>487.773</v>
+      </c>
+      <c r="G101">
+        <v>114</v>
+      </c>
+      <c r="H101">
+        <v>231.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>38.6</v>
+      </c>
+      <c r="K101">
+        <v>23.7</v>
+      </c>
+      <c r="L101">
+        <v>14.9</v>
+      </c>
+      <c r="M101">
+        <v>116.4801924</v>
+      </c>
+      <c r="N101">
+        <v>-101.5801924</v>
+      </c>
+      <c r="O101">
+        <v>-20.31603847999999</v>
+      </c>
+      <c r="P101">
+        <v>-81.26415392</v>
+      </c>
+      <c r="Q101">
+        <v>-57.56415392</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.861152850022775</v>
+      </c>
+      <c r="T101">
+        <v>73.02216009957201</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02558374894992018</v>
+      </c>
+      <c r="W101">
+        <v>0.2326906007507591</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.127918744749601</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_hotel_gaming.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08218179047585428</v>
+        <v>0.08205342689490255</v>
       </c>
       <c r="C2">
-        <v>540.8882033235129</v>
+        <v>536.31059525944</v>
       </c>
       <c r="D2">
-        <v>472.7882033235129</v>
+        <v>473.70859525944</v>
       </c>
       <c r="E2">
-        <v>-183.1</v>
+        <v>-177.602</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.497999999999999</v>
       </c>
       <c r="G2">
         <v>68.09999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>41.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2765493999999999</v>
       </c>
       <c r="N2">
-        <v>41.775</v>
+        <v>41.4984506</v>
       </c>
       <c r="O2">
-        <v>8.355</v>
+        <v>8.299690119999999</v>
       </c>
       <c r="P2">
-        <v>33.42</v>
+        <v>33.19876048</v>
       </c>
       <c r="Q2">
-        <v>66.52000000000001</v>
+        <v>66.29876048</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08218179047585428</v>
+        <v>0.08247578474232582</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815169</v>
+        <v>0.7540927362344989</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>151.0580026570298</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08205342689490255</v>
+        <v>0.08192506331395084</v>
       </c>
       <c r="C3">
-        <v>536.31059525944</v>
+        <v>531.7365776980259</v>
       </c>
       <c r="D3">
-        <v>473.70859525944</v>
+        <v>474.632577698026</v>
       </c>
       <c r="E3">
-        <v>-177.602</v>
+        <v>-172.104</v>
       </c>
       <c r="F3">
-        <v>5.497999999999999</v>
+        <v>10.996</v>
       </c>
       <c r="G3">
         <v>68.09999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>41.775</v>
       </c>
       <c r="M3">
-        <v>0.2765493999999999</v>
+        <v>0.5530987999999999</v>
       </c>
       <c r="N3">
-        <v>41.4984506</v>
+        <v>41.2219012</v>
       </c>
       <c r="O3">
-        <v>8.299690119999999</v>
+        <v>8.24438024</v>
       </c>
       <c r="P3">
-        <v>33.19876048</v>
+        <v>32.97752096</v>
       </c>
       <c r="Q3">
-        <v>66.29876048</v>
+        <v>66.07752096</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08247578474232582</v>
+        <v>0.08277577889178658</v>
       </c>
       <c r="T3">
-        <v>0.7540927362344989</v>
+        <v>0.7602609316967254</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>151.0580026570298</v>
+        <v>75.52900132851492</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08192506331395084</v>
+        <v>0.08179669973299915</v>
       </c>
       <c r="C4">
-        <v>531.7365776980259</v>
+        <v>527.1661716904722</v>
       </c>
       <c r="D4">
-        <v>474.632577698026</v>
+        <v>475.5601716904723</v>
       </c>
       <c r="E4">
-        <v>-172.104</v>
+        <v>-166.606</v>
       </c>
       <c r="F4">
-        <v>10.996</v>
+        <v>16.494</v>
       </c>
       <c r="G4">
         <v>68.09999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>41.775</v>
       </c>
       <c r="M4">
-        <v>0.5530987999999999</v>
+        <v>0.8296481999999999</v>
       </c>
       <c r="N4">
-        <v>41.2219012</v>
+        <v>40.9453518</v>
       </c>
       <c r="O4">
-        <v>8.24438024</v>
+        <v>8.189070360000001</v>
       </c>
       <c r="P4">
-        <v>32.97752096</v>
+        <v>32.75628144</v>
       </c>
       <c r="Q4">
-        <v>66.07752096</v>
+        <v>65.85628144</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08277577889178658</v>
+        <v>0.08308195848762798</v>
       </c>
       <c r="T4">
-        <v>0.7602609316967254</v>
+        <v>0.7665563064468327</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.52900132851492</v>
+        <v>50.35266755234327</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08179669973299915</v>
+        <v>0.08166833615204744</v>
       </c>
       <c r="C5">
-        <v>527.1661716904722</v>
+        <v>522.5993984528681</v>
       </c>
       <c r="D5">
-        <v>475.5601716904723</v>
+        <v>476.491398452868</v>
       </c>
       <c r="E5">
-        <v>-166.606</v>
+        <v>-161.108</v>
       </c>
       <c r="F5">
-        <v>16.494</v>
+        <v>21.992</v>
       </c>
       <c r="G5">
         <v>68.09999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>41.775</v>
       </c>
       <c r="M5">
-        <v>0.8296481999999999</v>
+        <v>1.1061976</v>
       </c>
       <c r="N5">
-        <v>40.9453518</v>
+        <v>40.6688024</v>
       </c>
       <c r="O5">
-        <v>8.189070360000001</v>
+        <v>8.133760479999999</v>
       </c>
       <c r="P5">
-        <v>32.75628144</v>
+        <v>32.53504192</v>
       </c>
       <c r="Q5">
-        <v>65.85628144</v>
+        <v>65.63504191999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08308195848762798</v>
+        <v>0.08339451682504942</v>
       </c>
       <c r="T5">
-        <v>0.7665563064468327</v>
+        <v>0.7729828348375676</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.35266755234327</v>
+        <v>37.76450066425745</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08166833615204744</v>
+        <v>0.08153997257109573</v>
       </c>
       <c r="C6">
-        <v>522.5993984528681</v>
+        <v>518.0362793678065</v>
       </c>
       <c r="D6">
-        <v>476.491398452868</v>
+        <v>477.4262793678066</v>
       </c>
       <c r="E6">
-        <v>-161.108</v>
+        <v>-155.61</v>
       </c>
       <c r="F6">
-        <v>21.992</v>
+        <v>27.49</v>
       </c>
       <c r="G6">
         <v>68.09999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>41.775</v>
       </c>
       <c r="M6">
-        <v>1.1061976</v>
+        <v>1.382747</v>
       </c>
       <c r="N6">
-        <v>40.6688024</v>
+        <v>40.392253</v>
       </c>
       <c r="O6">
-        <v>8.133760479999999</v>
+        <v>8.0784506</v>
       </c>
       <c r="P6">
-        <v>32.53504192</v>
+        <v>32.3138024</v>
       </c>
       <c r="Q6">
-        <v>65.63504191999999</v>
+        <v>65.41380240000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08339451682504942</v>
+        <v>0.0837136553379955</v>
       </c>
       <c r="T6">
-        <v>0.7729828348375676</v>
+        <v>0.7795446585628439</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.76450066425745</v>
+        <v>30.21160053140596</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08153997257109573</v>
+        <v>0.081411608990144</v>
       </c>
       <c r="C7">
-        <v>518.0362793678065</v>
+        <v>513.4768359860229</v>
       </c>
       <c r="D7">
-        <v>477.4262793678066</v>
+        <v>478.3648359860229</v>
       </c>
       <c r="E7">
-        <v>-155.61</v>
+        <v>-150.112</v>
       </c>
       <c r="F7">
-        <v>27.49</v>
+        <v>32.988</v>
       </c>
       <c r="G7">
         <v>68.09999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>41.775</v>
       </c>
       <c r="M7">
-        <v>1.382747</v>
+        <v>1.6592964</v>
       </c>
       <c r="N7">
-        <v>40.392253</v>
+        <v>40.1157036</v>
       </c>
       <c r="O7">
-        <v>8.0784506</v>
+        <v>8.023140719999999</v>
       </c>
       <c r="P7">
-        <v>32.3138024</v>
+        <v>32.09256288</v>
       </c>
       <c r="Q7">
-        <v>65.41380240000001</v>
+        <v>65.19256288</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0837136553379955</v>
+        <v>0.0840395840320681</v>
       </c>
       <c r="T7">
-        <v>0.7795446585628439</v>
+        <v>0.786246095558871</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.21160053140596</v>
+        <v>25.17633377617164</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.081411608990144</v>
+        <v>0.08128324540919231</v>
       </c>
       <c r="C8">
-        <v>513.4768359860229</v>
+        <v>508.921090028049</v>
       </c>
       <c r="D8">
-        <v>478.3648359860229</v>
+        <v>479.3070900280489</v>
       </c>
       <c r="E8">
-        <v>-150.112</v>
+        <v>-144.614</v>
       </c>
       <c r="F8">
-        <v>32.988</v>
+        <v>38.48599999999999</v>
       </c>
       <c r="G8">
         <v>68.09999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>41.775</v>
       </c>
       <c r="M8">
-        <v>1.6592964</v>
+        <v>1.935845799999999</v>
       </c>
       <c r="N8">
-        <v>40.1157036</v>
+        <v>39.8391542</v>
       </c>
       <c r="O8">
-        <v>8.023140719999999</v>
+        <v>7.96783084</v>
       </c>
       <c r="P8">
-        <v>32.09256288</v>
+        <v>31.87132336</v>
       </c>
       <c r="Q8">
-        <v>65.19256288</v>
+        <v>64.97132336</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0840395840320681</v>
+        <v>0.08437252194536808</v>
       </c>
       <c r="T8">
-        <v>0.786246095558871</v>
+        <v>0.7930916494795438</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.17633377617164</v>
+        <v>21.57971466528998</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08128324540919231</v>
+        <v>0.08115488182824061</v>
       </c>
       <c r="C9">
-        <v>508.921090028049</v>
+        <v>504.3690633858898</v>
       </c>
       <c r="D9">
-        <v>479.3070900280489</v>
+        <v>480.2530633858898</v>
       </c>
       <c r="E9">
-        <v>-144.614</v>
+        <v>-139.116</v>
       </c>
       <c r="F9">
-        <v>38.486</v>
+        <v>43.98399999999999</v>
       </c>
       <c r="G9">
         <v>68.09999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>41.775</v>
       </c>
       <c r="M9">
-        <v>1.9358458</v>
+        <v>2.2123952</v>
       </c>
       <c r="N9">
-        <v>39.8391542</v>
+        <v>39.5626048</v>
       </c>
       <c r="O9">
-        <v>7.96783084</v>
+        <v>7.912520960000001</v>
       </c>
       <c r="P9">
-        <v>31.87132336</v>
+        <v>31.65008384</v>
       </c>
       <c r="Q9">
-        <v>64.97132336</v>
+        <v>64.75008384</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08437252194536808</v>
+        <v>0.08471269763939196</v>
       </c>
       <c r="T9">
-        <v>0.7930916494795438</v>
+        <v>0.8000860197897964</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.57971466528997</v>
+        <v>18.88225033212873</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08115488182824061</v>
+        <v>0.08102651824728889</v>
       </c>
       <c r="C10">
-        <v>504.3690633858898</v>
+        <v>499.8207781247194</v>
       </c>
       <c r="D10">
-        <v>480.2530633858898</v>
+        <v>481.2027781247193</v>
       </c>
       <c r="E10">
-        <v>-139.116</v>
+        <v>-133.618</v>
       </c>
       <c r="F10">
-        <v>43.98399999999999</v>
+        <v>49.48199999999999</v>
       </c>
       <c r="G10">
         <v>68.09999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>41.775</v>
       </c>
       <c r="M10">
-        <v>2.2123952</v>
+        <v>2.4889446</v>
       </c>
       <c r="N10">
-        <v>39.5626048</v>
+        <v>39.2860554</v>
       </c>
       <c r="O10">
-        <v>7.912520960000001</v>
+        <v>7.857211080000001</v>
       </c>
       <c r="P10">
-        <v>31.65008384</v>
+        <v>31.42884432</v>
       </c>
       <c r="Q10">
-        <v>64.75008384</v>
+        <v>64.52884432</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08471269763939196</v>
+        <v>0.08506034972229548</v>
       </c>
       <c r="T10">
-        <v>0.8000860197897964</v>
+        <v>0.8072341125244501</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.88225033212873</v>
+        <v>16.78422251744776</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08102651824728889</v>
+        <v>0.08089815466633718</v>
       </c>
       <c r="C11">
-        <v>499.8207781247194</v>
+        <v>495.2762564845946</v>
       </c>
       <c r="D11">
-        <v>481.2027781247193</v>
+        <v>482.1562564845946</v>
       </c>
       <c r="E11">
-        <v>-133.618</v>
+        <v>-128.12</v>
       </c>
       <c r="F11">
-        <v>49.48199999999999</v>
+        <v>54.97999999999999</v>
       </c>
       <c r="G11">
         <v>68.09999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>41.775</v>
       </c>
       <c r="M11">
-        <v>2.4889446</v>
+        <v>2.765493999999999</v>
       </c>
       <c r="N11">
-        <v>39.2860554</v>
+        <v>39.009506</v>
       </c>
       <c r="O11">
-        <v>7.857211080000001</v>
+        <v>7.801901200000001</v>
       </c>
       <c r="P11">
-        <v>31.42884432</v>
+        <v>31.2076048</v>
       </c>
       <c r="Q11">
-        <v>64.52884432</v>
+        <v>64.30760480000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08506034972229548</v>
+        <v>0.08541572740704131</v>
       </c>
       <c r="T11">
-        <v>0.8072341125244501</v>
+        <v>0.8145410517643183</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.78422251744776</v>
+        <v>15.10580026570299</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08089815466633718</v>
+        <v>0.08076979108538547</v>
       </c>
       <c r="C12">
-        <v>495.2762564845946</v>
+        <v>490.7355208821932</v>
       </c>
       <c r="D12">
-        <v>482.1562564845946</v>
+        <v>483.1135208821931</v>
       </c>
       <c r="E12">
-        <v>-128.12</v>
+        <v>-122.622</v>
       </c>
       <c r="F12">
-        <v>54.98</v>
+        <v>60.47799999999999</v>
       </c>
       <c r="G12">
         <v>68.09999999999999</v>
@@ -2271,28 +2271,28 @@
         <v>41.775</v>
       </c>
       <c r="M12">
-        <v>2.765494</v>
+        <v>3.042043399999999</v>
       </c>
       <c r="N12">
-        <v>39.009506</v>
+        <v>38.7329566</v>
       </c>
       <c r="O12">
-        <v>7.801901200000001</v>
+        <v>7.74659132</v>
       </c>
       <c r="P12">
-        <v>31.2076048</v>
+        <v>30.98636528</v>
       </c>
       <c r="Q12">
-        <v>64.30760480000001</v>
+        <v>64.08636528</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08541572740704131</v>
+        <v>0.08577909110717469</v>
       </c>
       <c r="T12">
-        <v>0.8145410517643186</v>
+        <v>0.8220121918859815</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.10580026570298</v>
+        <v>13.73254569609362</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08076979108538547</v>
+        <v>0.08078542750443378</v>
       </c>
       <c r="C13">
-        <v>490.7355208821932</v>
+        <v>485.1207098801253</v>
       </c>
       <c r="D13">
-        <v>483.1135208821931</v>
+        <v>482.9967098801254</v>
       </c>
       <c r="E13">
-        <v>-122.622</v>
+        <v>-117.124</v>
       </c>
       <c r="F13">
-        <v>60.47799999999999</v>
+        <v>65.976</v>
       </c>
       <c r="G13">
         <v>68.09999999999999</v>
@@ -2353,45 +2353,45 @@
         <v>41.775</v>
       </c>
       <c r="M13">
-        <v>3.042043399999999</v>
+        <v>3.4175568</v>
       </c>
       <c r="N13">
-        <v>38.7329566</v>
+        <v>38.3574432</v>
       </c>
       <c r="O13">
-        <v>7.74659132</v>
+        <v>7.67148864</v>
       </c>
       <c r="P13">
-        <v>30.98636528</v>
+        <v>30.68595456</v>
       </c>
       <c r="Q13">
-        <v>64.08636528</v>
+        <v>63.78595456</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08577909110717469</v>
+        <v>0.0861507130732202</v>
       </c>
       <c r="T13">
-        <v>0.8220121918859815</v>
+        <v>0.8296531306467734</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.73254569609362</v>
+        <v>12.22364468090186</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08078542750443378</v>
+        <v>0.08066906392348205</v>
       </c>
       <c r="C14">
-        <v>485.1207098801253</v>
+        <v>480.493353969241</v>
       </c>
       <c r="D14">
-        <v>482.9967098801254</v>
+        <v>483.867353969241</v>
       </c>
       <c r="E14">
-        <v>-117.124</v>
+        <v>-111.626</v>
       </c>
       <c r="F14">
-        <v>65.976</v>
+        <v>71.47399999999999</v>
       </c>
       <c r="G14">
         <v>68.09999999999999</v>
@@ -2435,28 +2435,28 @@
         <v>41.775</v>
       </c>
       <c r="M14">
-        <v>3.4175568</v>
+        <v>3.702353199999999</v>
       </c>
       <c r="N14">
-        <v>38.3574432</v>
+        <v>38.0726468</v>
       </c>
       <c r="O14">
-        <v>7.67148864</v>
+        <v>7.614529360000001</v>
       </c>
       <c r="P14">
-        <v>30.68595456</v>
+        <v>30.45811744</v>
       </c>
       <c r="Q14">
-        <v>63.78595456</v>
+        <v>63.55811744</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0861507130732202</v>
+        <v>0.08653087807296789</v>
       </c>
       <c r="T14">
-        <v>0.8296531306467734</v>
+        <v>0.8374697231721809</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.22364468090186</v>
+        <v>11.28336432083249</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08066906392348205</v>
+        <v>0.08055270034253034</v>
       </c>
       <c r="C15">
-        <v>480.493353969241</v>
+        <v>475.8691425518145</v>
       </c>
       <c r="D15">
-        <v>483.867353969241</v>
+        <v>484.7411425518146</v>
       </c>
       <c r="E15">
-        <v>-111.626</v>
+        <v>-106.128</v>
       </c>
       <c r="F15">
-        <v>71.47399999999999</v>
+        <v>76.97199999999999</v>
       </c>
       <c r="G15">
         <v>68.09999999999999</v>
@@ -2517,28 +2517,28 @@
         <v>41.775</v>
       </c>
       <c r="M15">
-        <v>3.702353199999999</v>
+        <v>3.9871496</v>
       </c>
       <c r="N15">
-        <v>38.0726468</v>
+        <v>37.7878504</v>
       </c>
       <c r="O15">
-        <v>7.614529360000001</v>
+        <v>7.55757008</v>
       </c>
       <c r="P15">
-        <v>30.45811744</v>
+        <v>30.23028032</v>
       </c>
       <c r="Q15">
-        <v>63.55811744</v>
+        <v>63.33028032</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08653087807296789</v>
+        <v>0.08691988411922133</v>
       </c>
       <c r="T15">
-        <v>0.8374697231721809</v>
+        <v>0.8454680969191098</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.28336432083249</v>
+        <v>10.47740972648731</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08055270034253034</v>
+        <v>0.08064033676157863</v>
       </c>
       <c r="C16">
-        <v>475.8691425518145</v>
+        <v>469.7127768151704</v>
       </c>
       <c r="D16">
-        <v>484.7411425518146</v>
+        <v>484.0827768151704</v>
       </c>
       <c r="E16">
-        <v>-106.128</v>
+        <v>-100.63</v>
       </c>
       <c r="F16">
-        <v>76.97199999999999</v>
+        <v>82.47</v>
       </c>
       <c r="G16">
         <v>68.09999999999999</v>
@@ -2599,45 +2599,45 @@
         <v>41.775</v>
       </c>
       <c r="M16">
-        <v>3.9871496</v>
+        <v>4.412145</v>
       </c>
       <c r="N16">
-        <v>37.7878504</v>
+        <v>37.362855</v>
       </c>
       <c r="O16">
-        <v>7.55757008</v>
+        <v>7.472570999999999</v>
       </c>
       <c r="P16">
-        <v>30.23028032</v>
+        <v>29.890284</v>
       </c>
       <c r="Q16">
-        <v>63.33028032</v>
+        <v>62.990284</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08691988411922133</v>
+        <v>0.08731804324891604</v>
       </c>
       <c r="T16">
-        <v>0.8454680969191098</v>
+        <v>0.8536546676953781</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.47740972648731</v>
+        <v>9.468183842552772</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08064033676157863</v>
+        <v>0.08053757318062693</v>
       </c>
       <c r="C17">
-        <v>469.7127768151705</v>
+        <v>464.9869661393201</v>
       </c>
       <c r="D17">
-        <v>484.0827768151704</v>
+        <v>484.85496613932</v>
       </c>
       <c r="E17">
-        <v>-100.63</v>
+        <v>-95.13200000000001</v>
       </c>
       <c r="F17">
-        <v>82.46999999999998</v>
+        <v>87.96799999999999</v>
       </c>
       <c r="G17">
         <v>68.09999999999999</v>
@@ -2681,28 +2681,28 @@
         <v>41.775</v>
       </c>
       <c r="M17">
-        <v>4.412144999999999</v>
+        <v>4.706287999999999</v>
       </c>
       <c r="N17">
-        <v>37.362855</v>
+        <v>37.068712</v>
       </c>
       <c r="O17">
-        <v>7.472570999999999</v>
+        <v>7.4137424</v>
       </c>
       <c r="P17">
-        <v>29.890284</v>
+        <v>29.6549696</v>
       </c>
       <c r="Q17">
-        <v>62.990284</v>
+        <v>62.7549696</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08731804324891604</v>
+        <v>0.0877256823578892</v>
       </c>
       <c r="T17">
-        <v>0.8536546676953781</v>
+        <v>0.8620361568234624</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.468183842552774</v>
+        <v>8.876422352393224</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08053757318062693</v>
+        <v>0.08043480959967522</v>
       </c>
       <c r="C18">
-        <v>464.9869661393201</v>
+        <v>460.2636229300132</v>
       </c>
       <c r="D18">
-        <v>484.85496613932</v>
+        <v>485.6296229300132</v>
       </c>
       <c r="E18">
-        <v>-95.13200000000001</v>
+        <v>-89.634</v>
       </c>
       <c r="F18">
-        <v>87.96799999999999</v>
+        <v>93.46599999999999</v>
       </c>
       <c r="G18">
         <v>68.09999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>41.775</v>
       </c>
       <c r="M18">
-        <v>4.706287999999999</v>
+        <v>5.000431</v>
       </c>
       <c r="N18">
-        <v>37.068712</v>
+        <v>36.774569</v>
       </c>
       <c r="O18">
-        <v>7.4137424</v>
+        <v>7.3549138</v>
       </c>
       <c r="P18">
-        <v>29.6549696</v>
+        <v>29.4196552</v>
       </c>
       <c r="Q18">
-        <v>62.7549696</v>
+        <v>62.5196552</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0877256823578892</v>
+        <v>0.08814314409599425</v>
       </c>
       <c r="T18">
-        <v>0.8620361568234624</v>
+        <v>0.8706196095449944</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.876422352393224</v>
+        <v>8.354279861075975</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08043480959967522</v>
+        <v>0.08033204601872351</v>
       </c>
       <c r="C19">
-        <v>460.2636229300132</v>
+        <v>455.5427590330508</v>
       </c>
       <c r="D19">
-        <v>485.6296229300132</v>
+        <v>486.4067590330508</v>
       </c>
       <c r="E19">
-        <v>-89.634</v>
+        <v>-84.136</v>
       </c>
       <c r="F19">
-        <v>93.46599999999999</v>
+        <v>98.964</v>
       </c>
       <c r="G19">
         <v>68.09999999999999</v>
@@ -2845,28 +2845,28 @@
         <v>41.775</v>
       </c>
       <c r="M19">
-        <v>5.000431</v>
+        <v>5.294574</v>
       </c>
       <c r="N19">
-        <v>36.774569</v>
+        <v>36.480426</v>
       </c>
       <c r="O19">
-        <v>7.3549138</v>
+        <v>7.2960852</v>
       </c>
       <c r="P19">
-        <v>29.4196552</v>
+        <v>29.1843408</v>
       </c>
       <c r="Q19">
-        <v>62.5196552</v>
+        <v>62.2843408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08814314409599425</v>
+        <v>0.08857078782771161</v>
       </c>
       <c r="T19">
-        <v>0.8706196095449944</v>
+        <v>0.8794124147719298</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.354279861075975</v>
+        <v>7.89015320212731</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08033204601872353</v>
+        <v>0.08035088243777182</v>
       </c>
       <c r="C20">
-        <v>455.5427590330507</v>
+        <v>449.902124968334</v>
       </c>
       <c r="D20">
-        <v>486.4067590330507</v>
+        <v>486.2641249683339</v>
       </c>
       <c r="E20">
-        <v>-84.13600000000001</v>
+        <v>-78.63800000000001</v>
       </c>
       <c r="F20">
-        <v>98.96399999999998</v>
+        <v>104.462</v>
       </c>
       <c r="G20">
         <v>68.09999999999999</v>
@@ -2927,45 +2927,45 @@
         <v>41.775</v>
       </c>
       <c r="M20">
-        <v>5.294573999999999</v>
+        <v>5.6722866</v>
       </c>
       <c r="N20">
-        <v>36.480426</v>
+        <v>36.1027134</v>
       </c>
       <c r="O20">
-        <v>7.2960852</v>
+        <v>7.22054268</v>
       </c>
       <c r="P20">
-        <v>29.1843408</v>
+        <v>28.88217072</v>
       </c>
       <c r="Q20">
-        <v>62.2843408</v>
+        <v>61.98217072</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08857078782771161</v>
+        <v>0.08900899066391582</v>
       </c>
       <c r="T20">
-        <v>0.8794124147719297</v>
+        <v>0.8884223263007647</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.890153202127311</v>
+        <v>7.364754806289231</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08035088243777182</v>
+        <v>0.08025451885682011</v>
       </c>
       <c r="C21">
-        <v>449.902124968334</v>
+        <v>445.1346960469334</v>
       </c>
       <c r="D21">
-        <v>486.2641249683339</v>
+        <v>486.9946960469334</v>
       </c>
       <c r="E21">
-        <v>-78.63800000000001</v>
+        <v>-73.14</v>
       </c>
       <c r="F21">
-        <v>104.462</v>
+        <v>109.96</v>
       </c>
       <c r="G21">
         <v>68.09999999999999</v>
@@ -3009,28 +3009,28 @@
         <v>41.775</v>
       </c>
       <c r="M21">
-        <v>5.6722866</v>
+        <v>5.970828</v>
       </c>
       <c r="N21">
-        <v>36.1027134</v>
+        <v>35.804172</v>
       </c>
       <c r="O21">
-        <v>7.22054268</v>
+        <v>7.160834400000001</v>
       </c>
       <c r="P21">
-        <v>28.88217072</v>
+        <v>28.6433376</v>
       </c>
       <c r="Q21">
-        <v>61.98217072</v>
+        <v>61.7433376</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08900899066391582</v>
+        <v>0.08945814857102513</v>
       </c>
       <c r="T21">
-        <v>0.8884223263007647</v>
+        <v>0.8976574856178203</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.364754806289231</v>
+        <v>6.99651706597477</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08025451885682011</v>
+        <v>0.08015815527586839</v>
       </c>
       <c r="C22">
-        <v>445.1346960469334</v>
+        <v>440.3694656722517</v>
       </c>
       <c r="D22">
-        <v>486.9946960469334</v>
+        <v>487.7274656722517</v>
       </c>
       <c r="E22">
-        <v>-73.14</v>
+        <v>-67.642</v>
       </c>
       <c r="F22">
-        <v>109.96</v>
+        <v>115.458</v>
       </c>
       <c r="G22">
         <v>68.09999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>41.775</v>
       </c>
       <c r="M22">
-        <v>5.970828</v>
+        <v>6.2693694</v>
       </c>
       <c r="N22">
-        <v>35.804172</v>
+        <v>35.5056306</v>
       </c>
       <c r="O22">
-        <v>7.160834400000001</v>
+        <v>7.10112612</v>
       </c>
       <c r="P22">
-        <v>28.6433376</v>
+        <v>28.40450448</v>
       </c>
       <c r="Q22">
-        <v>61.7433376</v>
+        <v>61.50450447999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08945814857102513</v>
+        <v>0.08991867756439037</v>
       </c>
       <c r="T22">
-        <v>0.8976574856178203</v>
+        <v>0.9071264464365737</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.99651706597477</v>
+        <v>6.663349586642637</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08015815527586839</v>
+        <v>0.08006179169491669</v>
       </c>
       <c r="C23">
-        <v>440.3694656722517</v>
+        <v>435.6064437835508</v>
       </c>
       <c r="D23">
-        <v>487.7274656722517</v>
+        <v>488.4624437835508</v>
       </c>
       <c r="E23">
-        <v>-67.64200000000001</v>
+        <v>-62.14400000000001</v>
       </c>
       <c r="F23">
-        <v>115.458</v>
+        <v>120.956</v>
       </c>
       <c r="G23">
         <v>68.09999999999999</v>
@@ -3173,28 +3173,28 @@
         <v>41.775</v>
       </c>
       <c r="M23">
-        <v>6.2693694</v>
+        <v>6.5679108</v>
       </c>
       <c r="N23">
-        <v>35.5056306</v>
+        <v>35.2070892</v>
       </c>
       <c r="O23">
-        <v>7.10112612</v>
+        <v>7.04141784</v>
       </c>
       <c r="P23">
-        <v>28.40450448</v>
+        <v>28.16567136</v>
       </c>
       <c r="Q23">
-        <v>61.50450447999999</v>
+        <v>61.26567136</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08991867756439037</v>
+        <v>0.09039101499348293</v>
       </c>
       <c r="T23">
-        <v>0.9071264464365737</v>
+        <v>0.9168382011224747</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.663349586642637</v>
+        <v>6.360470059977063</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08006179169491669</v>
+        <v>0.08014942811396497</v>
       </c>
       <c r="C24">
-        <v>435.6064437835508</v>
+        <v>429.4399378226703</v>
       </c>
       <c r="D24">
-        <v>488.4624437835508</v>
+        <v>487.7939378226703</v>
       </c>
       <c r="E24">
-        <v>-62.14400000000001</v>
+        <v>-56.646</v>
       </c>
       <c r="F24">
-        <v>120.956</v>
+        <v>126.454</v>
       </c>
       <c r="G24">
         <v>68.09999999999999</v>
@@ -3255,45 +3255,45 @@
         <v>41.775</v>
       </c>
       <c r="M24">
-        <v>6.5679108</v>
+        <v>6.9929062</v>
       </c>
       <c r="N24">
-        <v>35.2070892</v>
+        <v>34.7820938</v>
       </c>
       <c r="O24">
-        <v>7.04141784</v>
+        <v>6.95641876</v>
       </c>
       <c r="P24">
-        <v>28.16567136</v>
+        <v>27.82567504</v>
       </c>
       <c r="Q24">
-        <v>61.26567136</v>
+        <v>60.92567504</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09039101499348293</v>
+        <v>0.09087562092722724</v>
       </c>
       <c r="T24">
-        <v>0.9168382011224747</v>
+        <v>0.9268022091768405</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.360470059977063</v>
+        <v>5.973911104370312</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08014942811396497</v>
+        <v>0.08006106453301327</v>
       </c>
       <c r="C25">
-        <v>429.4399378226703</v>
+        <v>424.615998367007</v>
       </c>
       <c r="D25">
-        <v>487.7939378226703</v>
+        <v>488.4679983670071</v>
       </c>
       <c r="E25">
-        <v>-56.646</v>
+        <v>-51.148</v>
       </c>
       <c r="F25">
-        <v>126.454</v>
+        <v>131.952</v>
       </c>
       <c r="G25">
         <v>68.09999999999999</v>
@@ -3337,28 +3337,28 @@
         <v>41.775</v>
       </c>
       <c r="M25">
-        <v>6.9929062</v>
+        <v>7.2969456</v>
       </c>
       <c r="N25">
-        <v>34.7820938</v>
+        <v>34.4780544</v>
       </c>
       <c r="O25">
-        <v>6.95641876</v>
+        <v>6.89561088</v>
       </c>
       <c r="P25">
-        <v>27.82567504</v>
+        <v>27.58244352</v>
       </c>
       <c r="Q25">
-        <v>60.92567504</v>
+        <v>60.68244352</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09087562092722724</v>
+        <v>0.09137297964870167</v>
       </c>
       <c r="T25">
-        <v>0.9268022091768405</v>
+        <v>0.9370284279694792</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.973911104370312</v>
+        <v>5.724998141688215</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08006106453301327</v>
+        <v>0.07997270095206156</v>
       </c>
       <c r="C26">
-        <v>424.615998367007</v>
+        <v>419.7939243971868</v>
       </c>
       <c r="D26">
-        <v>488.4679983670071</v>
+        <v>489.1439243971868</v>
       </c>
       <c r="E26">
-        <v>-51.148</v>
+        <v>-45.65000000000001</v>
       </c>
       <c r="F26">
-        <v>131.952</v>
+        <v>137.45</v>
       </c>
       <c r="G26">
         <v>68.09999999999999</v>
@@ -3419,28 +3419,28 @@
         <v>41.775</v>
       </c>
       <c r="M26">
-        <v>7.2969456</v>
+        <v>7.600985</v>
       </c>
       <c r="N26">
-        <v>34.4780544</v>
+        <v>34.174015</v>
       </c>
       <c r="O26">
-        <v>6.89561088</v>
+        <v>6.834803</v>
       </c>
       <c r="P26">
-        <v>27.58244352</v>
+        <v>27.339212</v>
       </c>
       <c r="Q26">
-        <v>60.68244352</v>
+        <v>60.439212</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09137297964870167</v>
+        <v>0.09188360126941542</v>
       </c>
       <c r="T26">
-        <v>0.937028427969479</v>
+        <v>0.9475273459299214</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.724998141688215</v>
+        <v>5.495998216020687</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07997270095206156</v>
+        <v>0.07988433737110985</v>
       </c>
       <c r="C27">
-        <v>419.7939243971868</v>
+        <v>414.9737236681352</v>
       </c>
       <c r="D27">
-        <v>489.1439243971868</v>
+        <v>489.8217236681352</v>
       </c>
       <c r="E27">
-        <v>-45.65000000000001</v>
+        <v>-40.15200000000002</v>
       </c>
       <c r="F27">
-        <v>137.45</v>
+        <v>142.948</v>
       </c>
       <c r="G27">
         <v>68.09999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>41.775</v>
       </c>
       <c r="M27">
-        <v>7.600985</v>
+        <v>7.905024399999999</v>
       </c>
       <c r="N27">
-        <v>34.174015</v>
+        <v>33.8699756</v>
       </c>
       <c r="O27">
-        <v>6.834803</v>
+        <v>6.773995119999999</v>
       </c>
       <c r="P27">
-        <v>27.339212</v>
+        <v>27.09598048</v>
       </c>
       <c r="Q27">
-        <v>60.439212</v>
+        <v>60.19598048</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09188360126941542</v>
+        <v>0.09240802347447277</v>
       </c>
       <c r="T27">
-        <v>0.9475273459299214</v>
+        <v>0.9583100184298352</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.495998216020687</v>
+        <v>5.28461366925066</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07988433737110985</v>
+        <v>0.07979597379015815</v>
       </c>
       <c r="C28">
-        <v>414.9737236681352</v>
+        <v>410.1554039778212</v>
       </c>
       <c r="D28">
-        <v>489.8217236681352</v>
+        <v>490.5014039778212</v>
       </c>
       <c r="E28">
-        <v>-40.15200000000002</v>
+        <v>-34.654</v>
       </c>
       <c r="F28">
-        <v>142.948</v>
+        <v>148.446</v>
       </c>
       <c r="G28">
         <v>68.09999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>41.775</v>
       </c>
       <c r="M28">
-        <v>7.905024399999999</v>
+        <v>8.209063800000001</v>
       </c>
       <c r="N28">
-        <v>33.8699756</v>
+        <v>33.5659362</v>
       </c>
       <c r="O28">
-        <v>6.773995119999999</v>
+        <v>6.71318724</v>
       </c>
       <c r="P28">
-        <v>27.09598048</v>
+        <v>26.85274896</v>
       </c>
       <c r="Q28">
-        <v>60.19598048</v>
+        <v>59.95274895999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09240802347447277</v>
+        <v>0.09294681341117554</v>
       </c>
       <c r="T28">
-        <v>0.9583100184298352</v>
+        <v>0.9693881066146782</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.28461366925066</v>
+        <v>5.08888723705619</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07979597379015815</v>
+        <v>0.07970761020920643</v>
       </c>
       <c r="C29">
-        <v>410.1554039778212</v>
+        <v>405.3389731675562</v>
       </c>
       <c r="D29">
-        <v>490.5014039778212</v>
+        <v>491.1829731675562</v>
       </c>
       <c r="E29">
-        <v>-34.654</v>
+        <v>-29.15600000000001</v>
       </c>
       <c r="F29">
-        <v>148.446</v>
+        <v>153.944</v>
       </c>
       <c r="G29">
         <v>68.09999999999999</v>
@@ -3665,28 +3665,28 @@
         <v>41.775</v>
       </c>
       <c r="M29">
-        <v>8.209063800000001</v>
+        <v>8.5131032</v>
       </c>
       <c r="N29">
-        <v>33.5659362</v>
+        <v>33.2618968</v>
       </c>
       <c r="O29">
-        <v>6.71318724</v>
+        <v>6.652379360000001</v>
       </c>
       <c r="P29">
-        <v>26.85274896</v>
+        <v>26.60951744</v>
       </c>
       <c r="Q29">
-        <v>59.95274895999999</v>
+        <v>59.70951744</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09294681341117554</v>
+        <v>0.09350056973500893</v>
       </c>
       <c r="T29">
-        <v>0.9693881066146782</v>
+        <v>0.9807739194713222</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.08888723705619</v>
+        <v>4.907141264304185</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07970761020920643</v>
+        <v>0.07961924662825472</v>
       </c>
       <c r="C30">
-        <v>405.3389731675562</v>
+        <v>400.5244391222949</v>
       </c>
       <c r="D30">
-        <v>491.1829731675562</v>
+        <v>491.8664391222949</v>
       </c>
       <c r="E30">
-        <v>-29.15600000000001</v>
+        <v>-23.65799999999999</v>
       </c>
       <c r="F30">
-        <v>153.944</v>
+        <v>159.442</v>
       </c>
       <c r="G30">
         <v>68.09999999999999</v>
@@ -3747,28 +3747,28 @@
         <v>41.775</v>
       </c>
       <c r="M30">
-        <v>8.5131032</v>
+        <v>8.8171426</v>
       </c>
       <c r="N30">
-        <v>33.2618968</v>
+        <v>32.95785739999999</v>
       </c>
       <c r="O30">
-        <v>6.652379360000001</v>
+        <v>6.591571479999999</v>
       </c>
       <c r="P30">
-        <v>26.60951744</v>
+        <v>26.36628592</v>
       </c>
       <c r="Q30">
-        <v>59.70951744</v>
+        <v>59.46628592</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09350056973500893</v>
+        <v>0.09406992482852777</v>
       </c>
       <c r="T30">
-        <v>0.9807739194713222</v>
+        <v>0.9924804594506886</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.907141264304185</v>
+        <v>4.737929496569556</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07961924662825472</v>
+        <v>0.07953088304730302</v>
       </c>
       <c r="C31">
-        <v>400.5244391222949</v>
+        <v>395.7118097709402</v>
       </c>
       <c r="D31">
-        <v>491.8664391222949</v>
+        <v>492.5518097709402</v>
       </c>
       <c r="E31">
-        <v>-23.65800000000002</v>
+        <v>-18.16000000000003</v>
       </c>
       <c r="F31">
-        <v>159.442</v>
+        <v>164.94</v>
       </c>
       <c r="G31">
         <v>68.09999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>41.775</v>
       </c>
       <c r="M31">
-        <v>8.817142599999999</v>
+        <v>9.121181999999999</v>
       </c>
       <c r="N31">
-        <v>32.9578574</v>
+        <v>32.653818</v>
       </c>
       <c r="O31">
-        <v>6.591571480000001</v>
+        <v>6.5307636</v>
       </c>
       <c r="P31">
-        <v>26.36628592</v>
+        <v>26.1230544</v>
       </c>
       <c r="Q31">
-        <v>59.46628592</v>
+        <v>59.2230544</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09406992482852777</v>
+        <v>0.09465554721043289</v>
       </c>
       <c r="T31">
-        <v>0.9924804594506886</v>
+        <v>1.004521472000894</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.737929496569558</v>
+        <v>4.579998513350573</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07953088304730302</v>
+        <v>0.0800625194663513</v>
       </c>
       <c r="C32">
-        <v>395.7118097709402</v>
+        <v>386.1188846705435</v>
       </c>
       <c r="D32">
-        <v>492.5518097709402</v>
+        <v>488.4568846705435</v>
       </c>
       <c r="E32">
-        <v>-18.16000000000003</v>
+        <v>-12.66200000000001</v>
       </c>
       <c r="F32">
-        <v>164.94</v>
+        <v>170.438</v>
       </c>
       <c r="G32">
         <v>68.09999999999999</v>
@@ -3911,45 +3911,45 @@
         <v>41.775</v>
       </c>
       <c r="M32">
-        <v>9.121181999999999</v>
+        <v>9.8513164</v>
       </c>
       <c r="N32">
-        <v>32.653818</v>
+        <v>31.9236836</v>
       </c>
       <c r="O32">
-        <v>6.5307636</v>
+        <v>6.384736719999999</v>
       </c>
       <c r="P32">
-        <v>26.1230544</v>
+        <v>25.53894688</v>
       </c>
       <c r="Q32">
-        <v>59.2230544</v>
+        <v>58.63894688</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09465554721043289</v>
+        <v>0.09525814415413233</v>
       </c>
       <c r="T32">
-        <v>1.004521472000894</v>
+        <v>1.016911499407627</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.579998513350573</v>
+        <v>4.240550024360196</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0800625194663513</v>
+        <v>0.0799941558853996</v>
       </c>
       <c r="C33">
-        <v>386.1188846705435</v>
+        <v>381.1436356984223</v>
       </c>
       <c r="D33">
-        <v>488.4568846705435</v>
+        <v>488.9796356984223</v>
       </c>
       <c r="E33">
-        <v>-12.66200000000001</v>
+        <v>-7.164000000000016</v>
       </c>
       <c r="F33">
-        <v>170.438</v>
+        <v>175.936</v>
       </c>
       <c r="G33">
         <v>68.09999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>41.775</v>
       </c>
       <c r="M33">
-        <v>9.8513164</v>
+        <v>10.1691008</v>
       </c>
       <c r="N33">
-        <v>31.9236836</v>
+        <v>31.6058992</v>
       </c>
       <c r="O33">
-        <v>6.384736719999999</v>
+        <v>6.32117984</v>
       </c>
       <c r="P33">
-        <v>25.53894688</v>
+        <v>25.28471936</v>
       </c>
       <c r="Q33">
-        <v>58.63894688</v>
+        <v>58.38471936000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09525814415413233</v>
+        <v>0.09587846453735235</v>
       </c>
       <c r="T33">
-        <v>1.016911499407627</v>
+        <v>1.029665939385147</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.240550024360196</v>
+        <v>4.108032836098941</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0799941558853996</v>
+        <v>0.08084979230444789</v>
       </c>
       <c r="C34">
-        <v>381.1436356984223</v>
+        <v>369.182470441066</v>
       </c>
       <c r="D34">
-        <v>488.9796356984223</v>
+        <v>482.516470441066</v>
       </c>
       <c r="E34">
-        <v>-7.164000000000016</v>
+        <v>-1.665999999999997</v>
       </c>
       <c r="F34">
-        <v>175.936</v>
+        <v>181.434</v>
       </c>
       <c r="G34">
         <v>68.09999999999999</v>
@@ -4075,45 +4075,45 @@
         <v>41.775</v>
       </c>
       <c r="M34">
-        <v>10.1691008</v>
+        <v>11.1219042</v>
       </c>
       <c r="N34">
-        <v>31.6058992</v>
+        <v>30.6530958</v>
       </c>
       <c r="O34">
-        <v>6.32117984</v>
+        <v>6.13061916</v>
       </c>
       <c r="P34">
-        <v>25.28471936</v>
+        <v>24.52247664</v>
       </c>
       <c r="Q34">
-        <v>58.38471936000001</v>
+        <v>57.62247664</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09587846453735235</v>
+        <v>0.09651730194693715</v>
       </c>
       <c r="T34">
-        <v>1.029665939385147</v>
+        <v>1.042801108914234</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.108032836098941</v>
+        <v>3.756101405728706</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08084979230444789</v>
+        <v>0.08080942872349617</v>
       </c>
       <c r="C35">
-        <v>369.182470441066</v>
+        <v>363.985519959016</v>
       </c>
       <c r="D35">
-        <v>482.516470441066</v>
+        <v>482.817519959016</v>
       </c>
       <c r="E35">
-        <v>-1.665999999999997</v>
+        <v>3.831999999999994</v>
       </c>
       <c r="F35">
-        <v>181.434</v>
+        <v>186.932</v>
       </c>
       <c r="G35">
         <v>68.09999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>41.775</v>
       </c>
       <c r="M35">
-        <v>11.1219042</v>
+        <v>11.4589316</v>
       </c>
       <c r="N35">
-        <v>30.6530958</v>
+        <v>30.3160684</v>
       </c>
       <c r="O35">
-        <v>6.13061916</v>
+        <v>6.06321368</v>
       </c>
       <c r="P35">
-        <v>24.52247664</v>
+        <v>24.25285472</v>
       </c>
       <c r="Q35">
-        <v>57.62247664</v>
+        <v>57.35285472</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09651730194693715</v>
+        <v>0.0971754980659033</v>
       </c>
       <c r="T35">
-        <v>1.042801108914234</v>
+        <v>1.056334313883597</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.756101405728706</v>
+        <v>3.645627834971979</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08080942872349617</v>
+        <v>0.08076906514254446</v>
       </c>
       <c r="C36">
-        <v>363.985519959016</v>
+        <v>358.7889453704288</v>
       </c>
       <c r="D36">
-        <v>482.817519959016</v>
+        <v>483.1189453704288</v>
       </c>
       <c r="E36">
-        <v>3.831999999999994</v>
+        <v>9.330000000000013</v>
       </c>
       <c r="F36">
-        <v>186.932</v>
+        <v>192.43</v>
       </c>
       <c r="G36">
         <v>68.09999999999999</v>
@@ -4239,28 +4239,28 @@
         <v>41.775</v>
       </c>
       <c r="M36">
-        <v>11.4589316</v>
+        <v>11.795959</v>
       </c>
       <c r="N36">
-        <v>30.3160684</v>
+        <v>29.979041</v>
       </c>
       <c r="O36">
-        <v>6.06321368</v>
+        <v>5.9958082</v>
       </c>
       <c r="P36">
-        <v>24.25285472</v>
+        <v>23.9832328</v>
       </c>
       <c r="Q36">
-        <v>57.35285472</v>
+        <v>57.0832328</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0971754980659033</v>
+        <v>0.09785394637314535</v>
       </c>
       <c r="T36">
-        <v>1.056334313883597</v>
+        <v>1.070283925159709</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.645627834971979</v>
+        <v>3.541467039687066</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08076906514254446</v>
+        <v>0.08153510156159277</v>
       </c>
       <c r="C37">
-        <v>358.7889453704288</v>
+        <v>347.6338275205466</v>
       </c>
       <c r="D37">
-        <v>483.1189453704288</v>
+        <v>477.4618275205465</v>
       </c>
       <c r="E37">
-        <v>9.330000000000013</v>
+        <v>14.828</v>
       </c>
       <c r="F37">
-        <v>192.43</v>
+        <v>197.928</v>
       </c>
       <c r="G37">
         <v>68.09999999999999</v>
@@ -4321,45 +4321,45 @@
         <v>41.775</v>
       </c>
       <c r="M37">
-        <v>11.795959</v>
+        <v>12.6871848</v>
       </c>
       <c r="N37">
-        <v>29.979041</v>
+        <v>29.0878152</v>
       </c>
       <c r="O37">
-        <v>5.9958082</v>
+        <v>5.81756304</v>
       </c>
       <c r="P37">
-        <v>23.9832328</v>
+        <v>23.27025216</v>
       </c>
       <c r="Q37">
-        <v>57.0832328</v>
+        <v>56.37025216</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09785394637314535</v>
+        <v>0.09855359618998871</v>
       </c>
       <c r="T37">
-        <v>1.070283925159709</v>
+        <v>1.0846694617882</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.541467039687066</v>
+        <v>3.292692638953284</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08153510156159276</v>
+        <v>0.08151713798064107</v>
       </c>
       <c r="C38">
-        <v>347.6338275205467</v>
+        <v>342.2669697555362</v>
       </c>
       <c r="D38">
-        <v>477.4618275205466</v>
+        <v>477.5929697555362</v>
       </c>
       <c r="E38">
-        <v>14.82799999999997</v>
+        <v>20.32599999999999</v>
       </c>
       <c r="F38">
-        <v>197.928</v>
+        <v>203.426</v>
       </c>
       <c r="G38">
         <v>68.09999999999999</v>
@@ -4403,28 +4403,28 @@
         <v>41.775</v>
       </c>
       <c r="M38">
-        <v>12.6871848</v>
+        <v>13.0396066</v>
       </c>
       <c r="N38">
-        <v>29.0878152</v>
+        <v>28.7353934</v>
       </c>
       <c r="O38">
-        <v>5.81756304</v>
+        <v>5.74707868</v>
       </c>
       <c r="P38">
-        <v>23.27025216</v>
+        <v>22.98831472</v>
       </c>
       <c r="Q38">
-        <v>56.37025216000001</v>
+        <v>56.08831472</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09855359618998868</v>
+        <v>0.09927545711212866</v>
       </c>
       <c r="T38">
-        <v>1.0846694617882</v>
+        <v>1.099511682119182</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.292692638953285</v>
+        <v>3.203700946008601</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08151713798064107</v>
+        <v>0.08149917439968934</v>
       </c>
       <c r="C39">
-        <v>342.2669697555362</v>
+        <v>336.9001840507826</v>
       </c>
       <c r="D39">
-        <v>477.5929697555362</v>
+        <v>477.7241840507826</v>
       </c>
       <c r="E39">
-        <v>20.32599999999999</v>
+        <v>25.82399999999998</v>
       </c>
       <c r="F39">
-        <v>203.426</v>
+        <v>208.924</v>
       </c>
       <c r="G39">
         <v>68.09999999999999</v>
@@ -4485,28 +4485,28 @@
         <v>41.775</v>
       </c>
       <c r="M39">
-        <v>13.0396066</v>
+        <v>13.3920284</v>
       </c>
       <c r="N39">
-        <v>28.7353934</v>
+        <v>28.3829716</v>
       </c>
       <c r="O39">
-        <v>5.74707868</v>
+        <v>5.67659432</v>
       </c>
       <c r="P39">
-        <v>22.98831472</v>
+        <v>22.70637728</v>
       </c>
       <c r="Q39">
-        <v>56.08831472</v>
+        <v>55.80637728</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09927545711212866</v>
+        <v>0.1000206038704667</v>
       </c>
       <c r="T39">
-        <v>1.099511682119182</v>
+        <v>1.114832683751164</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.203700946008601</v>
+        <v>3.119393026376796</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08149917439968934</v>
+        <v>0.08148121081873763</v>
       </c>
       <c r="C40">
-        <v>336.9001840507826</v>
+        <v>331.5334704656952</v>
       </c>
       <c r="D40">
-        <v>477.7241840507826</v>
+        <v>477.8554704656952</v>
       </c>
       <c r="E40">
-        <v>25.82399999999998</v>
+        <v>31.322</v>
       </c>
       <c r="F40">
-        <v>208.924</v>
+        <v>214.422</v>
       </c>
       <c r="G40">
         <v>68.09999999999999</v>
@@ -4567,28 +4567,28 @@
         <v>41.775</v>
       </c>
       <c r="M40">
-        <v>13.3920284</v>
+        <v>13.7444502</v>
       </c>
       <c r="N40">
-        <v>28.3829716</v>
+        <v>28.0305498</v>
       </c>
       <c r="O40">
-        <v>5.67659432</v>
+        <v>5.60610996</v>
       </c>
       <c r="P40">
-        <v>22.70637728</v>
+        <v>22.42443984</v>
       </c>
       <c r="Q40">
-        <v>55.80637728</v>
+        <v>55.52443984</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1000206038704667</v>
+        <v>0.1007901816700617</v>
       </c>
       <c r="T40">
-        <v>1.114832683751164</v>
+        <v>1.130656013305506</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.119393026376796</v>
+        <v>3.039408589803032</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08148121081873763</v>
+        <v>0.08395924723778593</v>
       </c>
       <c r="C41">
-        <v>331.5334704656952</v>
+        <v>308.5815068059202</v>
       </c>
       <c r="D41">
-        <v>477.8554704656952</v>
+        <v>460.4015068059202</v>
       </c>
       <c r="E41">
-        <v>31.322</v>
+        <v>36.81999999999999</v>
       </c>
       <c r="F41">
-        <v>214.422</v>
+        <v>219.92</v>
       </c>
       <c r="G41">
         <v>68.09999999999999</v>
@@ -4649,45 +4649,45 @@
         <v>41.775</v>
       </c>
       <c r="M41">
-        <v>13.7444502</v>
+        <v>15.812248</v>
       </c>
       <c r="N41">
-        <v>28.0305498</v>
+        <v>25.962752</v>
       </c>
       <c r="O41">
-        <v>5.60610996</v>
+        <v>5.1925504</v>
       </c>
       <c r="P41">
-        <v>22.42443984</v>
+        <v>20.7702016</v>
       </c>
       <c r="Q41">
-        <v>55.52443984</v>
+        <v>53.8702016</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1007901816700617</v>
+        <v>0.1015854120629766</v>
       </c>
       <c r="T41">
-        <v>1.130656013305506</v>
+        <v>1.147006787178326</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.039408589803032</v>
+        <v>2.641939337151808</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08395924723778593</v>
+        <v>0.08400368365683422</v>
       </c>
       <c r="C42">
-        <v>308.5815068059202</v>
+        <v>302.7821498302393</v>
       </c>
       <c r="D42">
-        <v>460.4015068059202</v>
+        <v>460.1001498302393</v>
       </c>
       <c r="E42">
-        <v>36.81999999999999</v>
+        <v>42.31800000000001</v>
       </c>
       <c r="F42">
-        <v>219.92</v>
+        <v>225.418</v>
       </c>
       <c r="G42">
         <v>68.09999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>41.775</v>
       </c>
       <c r="M42">
-        <v>15.812248</v>
+        <v>16.2075542</v>
       </c>
       <c r="N42">
-        <v>25.962752</v>
+        <v>25.5674458</v>
       </c>
       <c r="O42">
-        <v>5.1925504</v>
+        <v>5.11348916</v>
       </c>
       <c r="P42">
-        <v>20.7702016</v>
+        <v>20.45395664</v>
       </c>
       <c r="Q42">
-        <v>53.8702016</v>
+        <v>53.55395664</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1015854120629766</v>
+        <v>0.1024075994183631</v>
       </c>
       <c r="T42">
-        <v>1.147006787178326</v>
+        <v>1.163911824572259</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.641939337151808</v>
+        <v>2.577501792343227</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08400368365683422</v>
+        <v>0.08404812007588251</v>
       </c>
       <c r="C43">
-        <v>302.7821498302393</v>
+        <v>296.983187104449</v>
       </c>
       <c r="D43">
-        <v>460.1001498302393</v>
+        <v>459.7991871044489</v>
       </c>
       <c r="E43">
-        <v>42.31800000000001</v>
+        <v>47.816</v>
       </c>
       <c r="F43">
-        <v>225.418</v>
+        <v>230.916</v>
       </c>
       <c r="G43">
         <v>68.09999999999999</v>
@@ -4813,28 +4813,28 @@
         <v>41.775</v>
       </c>
       <c r="M43">
-        <v>16.2075542</v>
+        <v>16.6028604</v>
       </c>
       <c r="N43">
-        <v>25.5674458</v>
+        <v>25.1721396</v>
       </c>
       <c r="O43">
-        <v>5.11348916</v>
+        <v>5.03442792</v>
       </c>
       <c r="P43">
-        <v>20.45395664</v>
+        <v>20.13771168</v>
       </c>
       <c r="Q43">
-        <v>53.55395664</v>
+        <v>53.23771168</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1024075994183631</v>
+        <v>0.1032581380618664</v>
       </c>
       <c r="T43">
-        <v>1.163911824572259</v>
+        <v>1.18139979429012</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.577501792343227</v>
+        <v>2.516132702049341</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08404812007588253</v>
+        <v>0.08543415649493082</v>
       </c>
       <c r="C44">
-        <v>296.9831871044489</v>
+        <v>282.2914441019901</v>
       </c>
       <c r="D44">
-        <v>459.7991871044488</v>
+        <v>450.6054441019901</v>
       </c>
       <c r="E44">
-        <v>47.81599999999997</v>
+        <v>53.31399999999999</v>
       </c>
       <c r="F44">
-        <v>230.916</v>
+        <v>236.414</v>
       </c>
       <c r="G44">
         <v>68.09999999999999</v>
@@ -4895,45 +4895,45 @@
         <v>41.775</v>
       </c>
       <c r="M44">
-        <v>16.6028604</v>
+        <v>17.9201812</v>
       </c>
       <c r="N44">
-        <v>25.1721396</v>
+        <v>23.8548188</v>
       </c>
       <c r="O44">
-        <v>5.034427920000001</v>
+        <v>4.77096376</v>
       </c>
       <c r="P44">
-        <v>20.13771168</v>
+        <v>19.08385504</v>
       </c>
       <c r="Q44">
-        <v>53.23771168</v>
+        <v>52.18385504</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1032581380618664</v>
+        <v>0.1041385201665453</v>
       </c>
       <c r="T44">
-        <v>1.18139979429012</v>
+        <v>1.199501376980538</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.516132702049341</v>
+        <v>2.331170624547033</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08543415649493082</v>
+        <v>0.0855097929139791</v>
       </c>
       <c r="C45">
-        <v>282.2914441019901</v>
+        <v>276.3023063765343</v>
       </c>
       <c r="D45">
-        <v>450.6054441019901</v>
+        <v>450.1143063765343</v>
       </c>
       <c r="E45">
-        <v>53.31399999999999</v>
+        <v>58.81199999999998</v>
       </c>
       <c r="F45">
-        <v>236.414</v>
+        <v>241.912</v>
       </c>
       <c r="G45">
         <v>68.09999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>41.775</v>
       </c>
       <c r="M45">
-        <v>17.9201812</v>
+        <v>18.3369296</v>
       </c>
       <c r="N45">
-        <v>23.8548188</v>
+        <v>23.4380704</v>
       </c>
       <c r="O45">
-        <v>4.77096376</v>
+        <v>4.687614079999999</v>
       </c>
       <c r="P45">
-        <v>19.08385504</v>
+        <v>18.75045632</v>
       </c>
       <c r="Q45">
-        <v>52.18385504</v>
+        <v>51.85045632</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1041385201665453</v>
+        <v>0.1050503444892484</v>
       </c>
       <c r="T45">
-        <v>1.199501376980538</v>
+        <v>1.218249444767042</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.331170624547033</v>
+        <v>2.278189473989146</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0855097929139791</v>
+        <v>0.0855854293330274</v>
       </c>
       <c r="C46">
-        <v>276.3023063765343</v>
+        <v>270.314238117242</v>
       </c>
       <c r="D46">
-        <v>450.1143063765343</v>
+        <v>449.6242381172419</v>
       </c>
       <c r="E46">
-        <v>58.81199999999998</v>
+        <v>64.31</v>
       </c>
       <c r="F46">
-        <v>241.912</v>
+        <v>247.41</v>
       </c>
       <c r="G46">
         <v>68.09999999999999</v>
@@ -5059,28 +5059,28 @@
         <v>41.775</v>
       </c>
       <c r="M46">
-        <v>18.3369296</v>
+        <v>18.753678</v>
       </c>
       <c r="N46">
-        <v>23.4380704</v>
+        <v>23.021322</v>
       </c>
       <c r="O46">
-        <v>4.687614079999999</v>
+        <v>4.6042644</v>
       </c>
       <c r="P46">
-        <v>18.75045632</v>
+        <v>18.4170576</v>
       </c>
       <c r="Q46">
-        <v>51.85045632</v>
+        <v>51.5170576</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1050503444892484</v>
+        <v>0.1059953260600498</v>
       </c>
       <c r="T46">
-        <v>1.218249444767042</v>
+        <v>1.237679260473055</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.278189473989146</v>
+        <v>2.227563041233831</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0855854293330274</v>
+        <v>0.08566106575207569</v>
       </c>
       <c r="C47">
-        <v>270.314238117242</v>
+        <v>264.3272358347234</v>
       </c>
       <c r="D47">
-        <v>449.6242381172419</v>
+        <v>449.1352358347235</v>
       </c>
       <c r="E47">
-        <v>64.31</v>
+        <v>69.80799999999999</v>
       </c>
       <c r="F47">
-        <v>247.41</v>
+        <v>252.908</v>
       </c>
       <c r="G47">
         <v>68.09999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>41.775</v>
       </c>
       <c r="M47">
-        <v>18.753678</v>
+        <v>19.1704264</v>
       </c>
       <c r="N47">
-        <v>23.021322</v>
+        <v>22.6045736</v>
       </c>
       <c r="O47">
-        <v>4.6042644</v>
+        <v>4.520914719999999</v>
       </c>
       <c r="P47">
-        <v>18.4170576</v>
+        <v>18.08365888</v>
       </c>
       <c r="Q47">
-        <v>51.5170576</v>
+        <v>51.18365888</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1059953260600498</v>
+        <v>0.1069753069482883</v>
       </c>
       <c r="T47">
-        <v>1.237679260473055</v>
+        <v>1.257828698982995</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.227563041233831</v>
+        <v>2.179137757728748</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08566106575207569</v>
+        <v>0.08573670217112397</v>
       </c>
       <c r="C48">
-        <v>264.3272358347234</v>
+        <v>258.3412960547526</v>
       </c>
       <c r="D48">
-        <v>449.1352358347235</v>
+        <v>448.6472960547526</v>
       </c>
       <c r="E48">
-        <v>69.80799999999999</v>
+        <v>75.30600000000001</v>
       </c>
       <c r="F48">
-        <v>252.908</v>
+        <v>258.406</v>
       </c>
       <c r="G48">
         <v>68.09999999999999</v>
@@ -5223,28 +5223,28 @@
         <v>41.775</v>
       </c>
       <c r="M48">
-        <v>19.1704264</v>
+        <v>19.5871748</v>
       </c>
       <c r="N48">
-        <v>22.6045736</v>
+        <v>22.1878252</v>
       </c>
       <c r="O48">
-        <v>4.520914719999999</v>
+        <v>4.437565039999999</v>
       </c>
       <c r="P48">
-        <v>18.08365888</v>
+        <v>17.75026016</v>
       </c>
       <c r="Q48">
-        <v>51.18365888</v>
+        <v>50.85026016</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1069753069482883</v>
+        <v>0.1079922682474037</v>
       </c>
       <c r="T48">
-        <v>1.257828698982995</v>
+        <v>1.278738493663121</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.179137757728748</v>
+        <v>2.132773124585583</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08573670217112397</v>
+        <v>0.08581233859017227</v>
       </c>
       <c r="C49">
-        <v>258.3412960547526</v>
+        <v>252.3564153181841</v>
       </c>
       <c r="D49">
-        <v>448.6472960547526</v>
+        <v>448.1604153181841</v>
       </c>
       <c r="E49">
-        <v>75.30600000000001</v>
+        <v>80.804</v>
       </c>
       <c r="F49">
-        <v>258.406</v>
+        <v>263.904</v>
       </c>
       <c r="G49">
         <v>68.09999999999999</v>
@@ -5305,28 +5305,28 @@
         <v>41.775</v>
       </c>
       <c r="M49">
-        <v>19.5871748</v>
+        <v>20.0039232</v>
       </c>
       <c r="N49">
-        <v>22.1878252</v>
+        <v>21.7710768</v>
       </c>
       <c r="O49">
-        <v>4.437565039999999</v>
+        <v>4.35421536</v>
       </c>
       <c r="P49">
-        <v>17.75026016</v>
+        <v>17.41686144</v>
       </c>
       <c r="Q49">
-        <v>50.85026016</v>
+        <v>50.51686144</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1079922682474037</v>
+        <v>0.109048343442639</v>
       </c>
       <c r="T49">
-        <v>1.278738493663121</v>
+        <v>1.30045251121556</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.132773124585583</v>
+        <v>2.088340351156717</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08581233859017227</v>
+        <v>0.08588797500922056</v>
       </c>
       <c r="C50">
-        <v>252.3564153181841</v>
+        <v>246.3725901808727</v>
       </c>
       <c r="D50">
-        <v>448.1604153181841</v>
+        <v>447.6745901808727</v>
       </c>
       <c r="E50">
-        <v>80.804</v>
+        <v>86.30199999999999</v>
       </c>
       <c r="F50">
-        <v>263.904</v>
+        <v>269.402</v>
       </c>
       <c r="G50">
         <v>68.09999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>41.775</v>
       </c>
       <c r="M50">
-        <v>20.0039232</v>
+        <v>20.4206716</v>
       </c>
       <c r="N50">
-        <v>21.7710768</v>
+        <v>21.3543284</v>
       </c>
       <c r="O50">
-        <v>4.35421536</v>
+        <v>4.270865679999999</v>
       </c>
       <c r="P50">
-        <v>17.41686144</v>
+        <v>17.08346272</v>
       </c>
       <c r="Q50">
-        <v>50.51686144</v>
+        <v>50.18346271999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.109048343442639</v>
+        <v>0.1101458333514128</v>
       </c>
       <c r="T50">
-        <v>1.30045251121556</v>
+        <v>1.323018058868095</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.088340351156717</v>
+        <v>2.045721160316784</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08588797500922056</v>
+        <v>0.08596361142826885</v>
       </c>
       <c r="C51">
-        <v>246.3725901808727</v>
+        <v>240.3898172135908</v>
       </c>
       <c r="D51">
-        <v>447.6745901808727</v>
+        <v>447.1898172135908</v>
       </c>
       <c r="E51">
-        <v>86.30199999999999</v>
+        <v>91.79999999999998</v>
       </c>
       <c r="F51">
-        <v>269.402</v>
+        <v>274.9</v>
       </c>
       <c r="G51">
         <v>68.09999999999999</v>
@@ -5469,28 +5469,28 @@
         <v>41.775</v>
       </c>
       <c r="M51">
-        <v>20.4206716</v>
+        <v>20.83742</v>
       </c>
       <c r="N51">
-        <v>21.3543284</v>
+        <v>20.93758</v>
       </c>
       <c r="O51">
-        <v>4.270865679999999</v>
+        <v>4.187516</v>
       </c>
       <c r="P51">
-        <v>17.08346272</v>
+        <v>16.750064</v>
       </c>
       <c r="Q51">
-        <v>50.18346271999999</v>
+        <v>49.850064</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1101458333514128</v>
+        <v>0.1112872228565377</v>
       </c>
       <c r="T51">
-        <v>1.323018058868095</v>
+        <v>1.34648622842673</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.045721160316784</v>
+        <v>2.004806737110448</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08596361142826885</v>
+        <v>0.09183284784731713</v>
       </c>
       <c r="C52">
-        <v>240.3898172135908</v>
+        <v>200.2278870917589</v>
       </c>
       <c r="D52">
-        <v>447.1898172135908</v>
+        <v>412.5258870917589</v>
       </c>
       <c r="E52">
-        <v>91.79999999999998</v>
+        <v>97.29799999999997</v>
       </c>
       <c r="F52">
-        <v>274.9</v>
+        <v>280.398</v>
       </c>
       <c r="G52">
         <v>68.09999999999999</v>
@@ -5551,45 +5551,45 @@
         <v>41.775</v>
       </c>
       <c r="M52">
-        <v>20.83742</v>
+        <v>25.23582</v>
       </c>
       <c r="N52">
-        <v>20.93758</v>
+        <v>16.53918</v>
       </c>
       <c r="O52">
-        <v>4.187516</v>
+        <v>3.307836</v>
       </c>
       <c r="P52">
-        <v>16.750064</v>
+        <v>13.231344</v>
       </c>
       <c r="Q52">
-        <v>49.850064</v>
+        <v>46.331344</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1112872228565377</v>
+        <v>0.1124751996884023</v>
       </c>
       <c r="T52">
-        <v>1.34648622842673</v>
+        <v>1.370912282457148</v>
       </c>
       <c r="U52">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
         <v>0.2</v>
       </c>
       <c r="W52">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.004806737110448</v>
+        <v>1.655385083583573</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09183284784731713</v>
+        <v>0.09202208426636543</v>
       </c>
       <c r="C53">
-        <v>200.2278870917589</v>
+        <v>193.7014537111066</v>
       </c>
       <c r="D53">
-        <v>412.5258870917589</v>
+        <v>411.4974537111066</v>
       </c>
       <c r="E53">
-        <v>97.29799999999997</v>
+        <v>102.796</v>
       </c>
       <c r="F53">
-        <v>280.398</v>
+        <v>285.896</v>
       </c>
       <c r="G53">
         <v>68.09999999999999</v>
@@ -5633,28 +5633,28 @@
         <v>41.775</v>
       </c>
       <c r="M53">
-        <v>25.23582</v>
+        <v>25.73063999999999</v>
       </c>
       <c r="N53">
-        <v>16.53918</v>
+        <v>16.04436</v>
       </c>
       <c r="O53">
-        <v>3.307836</v>
+        <v>3.208872000000001</v>
       </c>
       <c r="P53">
-        <v>13.231344</v>
+        <v>12.835488</v>
       </c>
       <c r="Q53">
-        <v>46.331344</v>
+        <v>45.93548800000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1124751996884023</v>
+        <v>0.113712675554928</v>
       </c>
       <c r="T53">
-        <v>1.370912282457148</v>
+        <v>1.396356088738832</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.655385083583573</v>
+        <v>1.62355075505312</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09202208426636543</v>
+        <v>0.09221132068541371</v>
       </c>
       <c r="C54">
-        <v>193.7014537111066</v>
+        <v>187.1801353790277</v>
       </c>
       <c r="D54">
-        <v>411.4974537111066</v>
+        <v>410.4741353790277</v>
       </c>
       <c r="E54">
-        <v>102.796</v>
+        <v>108.294</v>
       </c>
       <c r="F54">
-        <v>285.896</v>
+        <v>291.394</v>
       </c>
       <c r="G54">
         <v>68.09999999999999</v>
@@ -5715,28 +5715,28 @@
         <v>41.775</v>
       </c>
       <c r="M54">
-        <v>25.73063999999999</v>
+        <v>26.22546</v>
       </c>
       <c r="N54">
-        <v>16.04436</v>
+        <v>15.54954</v>
       </c>
       <c r="O54">
-        <v>3.208872000000001</v>
+        <v>3.109908</v>
       </c>
       <c r="P54">
-        <v>12.835488</v>
+        <v>12.439632</v>
       </c>
       <c r="Q54">
-        <v>45.93548800000001</v>
+        <v>45.539632</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.113712675554928</v>
+        <v>0.1150028099689654</v>
       </c>
       <c r="T54">
-        <v>1.396356088738832</v>
+        <v>1.422882610181439</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.62355075505312</v>
+        <v>1.59291772193891</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09221132068541371</v>
+        <v>0.092400557104462</v>
       </c>
       <c r="C55">
-        <v>187.1801353790277</v>
+        <v>180.6638940296353</v>
       </c>
       <c r="D55">
-        <v>410.4741353790277</v>
+        <v>409.4558940296353</v>
       </c>
       <c r="E55">
-        <v>108.294</v>
+        <v>113.792</v>
       </c>
       <c r="F55">
-        <v>291.394</v>
+        <v>296.892</v>
       </c>
       <c r="G55">
         <v>68.09999999999999</v>
@@ -5797,28 +5797,28 @@
         <v>41.775</v>
       </c>
       <c r="M55">
-        <v>26.22546</v>
+        <v>26.72028</v>
       </c>
       <c r="N55">
-        <v>15.54954</v>
+        <v>15.05472</v>
       </c>
       <c r="O55">
-        <v>3.109908</v>
+        <v>3.010944</v>
       </c>
       <c r="P55">
-        <v>12.439632</v>
+        <v>12.043776</v>
       </c>
       <c r="Q55">
-        <v>45.539632</v>
+        <v>45.143776</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1150028099689654</v>
+        <v>0.1163490371836131</v>
       </c>
       <c r="T55">
-        <v>1.422882610181439</v>
+        <v>1.450562458643289</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.59291772193891</v>
+        <v>1.563419245606708</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.092400557104462</v>
+        <v>0.09258979352351031</v>
       </c>
       <c r="C56">
-        <v>180.6638940296353</v>
+        <v>174.1526919738204</v>
       </c>
       <c r="D56">
-        <v>409.4558940296353</v>
+        <v>408.4426919738204</v>
       </c>
       <c r="E56">
-        <v>113.792</v>
+        <v>119.29</v>
       </c>
       <c r="F56">
-        <v>296.892</v>
+        <v>302.39</v>
       </c>
       <c r="G56">
         <v>68.09999999999999</v>
@@ -5879,28 +5879,28 @@
         <v>41.775</v>
       </c>
       <c r="M56">
-        <v>26.72028</v>
+        <v>27.2151</v>
       </c>
       <c r="N56">
-        <v>15.05472</v>
+        <v>14.5599</v>
       </c>
       <c r="O56">
-        <v>3.010944</v>
+        <v>2.911980000000001</v>
       </c>
       <c r="P56">
-        <v>12.043776</v>
+        <v>11.64792</v>
       </c>
       <c r="Q56">
-        <v>45.143776</v>
+        <v>44.74792000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1163490371836131</v>
+        <v>0.1177550967189118</v>
       </c>
       <c r="T56">
-        <v>1.450562458643289</v>
+        <v>1.479472522592334</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.563419245606708</v>
+        <v>1.534993441141131</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09258979352351031</v>
+        <v>0.0927790299425586</v>
       </c>
       <c r="C57">
-        <v>174.1526919738204</v>
+        <v>167.6464918946011</v>
       </c>
       <c r="D57">
-        <v>408.4426919738204</v>
+        <v>407.434491894601</v>
       </c>
       <c r="E57">
-        <v>119.29</v>
+        <v>124.788</v>
       </c>
       <c r="F57">
-        <v>302.39</v>
+        <v>307.888</v>
       </c>
       <c r="G57">
         <v>68.09999999999999</v>
@@ -5961,28 +5961,28 @@
         <v>41.775</v>
       </c>
       <c r="M57">
-        <v>27.2151</v>
+        <v>27.70992</v>
       </c>
       <c r="N57">
-        <v>14.5599</v>
+        <v>14.06508</v>
       </c>
       <c r="O57">
-        <v>2.911980000000001</v>
+        <v>2.813016000000001</v>
       </c>
       <c r="P57">
-        <v>11.64792</v>
+        <v>11.252064</v>
       </c>
       <c r="Q57">
-        <v>44.74792000000001</v>
+        <v>44.352064</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1177550967189118</v>
+        <v>0.1192250680512695</v>
       </c>
       <c r="T57">
-        <v>1.479472522592334</v>
+        <v>1.509696680357244</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.534993441141131</v>
+        <v>1.507582843977897</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0927790299425586</v>
+        <v>0.1207891870393586</v>
       </c>
       <c r="C58">
-        <v>167.6464918946011</v>
+        <v>53.12110926810948</v>
       </c>
       <c r="D58">
-        <v>407.434491894601</v>
+        <v>298.4071092681095</v>
       </c>
       <c r="E58">
-        <v>124.788</v>
+        <v>130.286</v>
       </c>
       <c r="F58">
-        <v>307.888</v>
+        <v>313.386</v>
       </c>
       <c r="G58">
         <v>68.09999999999999</v>
@@ -6043,45 +6043,45 @@
         <v>41.775</v>
       </c>
       <c r="M58">
-        <v>27.70992</v>
+        <v>46.00506480000001</v>
       </c>
       <c r="N58">
-        <v>14.06508</v>
+        <v>-4.230064800000008</v>
       </c>
       <c r="O58">
-        <v>2.813016000000001</v>
+        <v>-0.8460129600000017</v>
       </c>
       <c r="P58">
-        <v>11.252064</v>
+        <v>-3.384051840000006</v>
       </c>
       <c r="Q58">
-        <v>44.352064</v>
+        <v>29.71594816</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1192250680512695</v>
+        <v>0.121650283968967</v>
       </c>
       <c r="T58">
-        <v>1.509696680357244</v>
+        <v>1.559561672209085</v>
       </c>
       <c r="U58">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2</v>
+        <v>0.181610438683699</v>
       </c>
       <c r="W58">
-        <v>0.07199999999999999</v>
+        <v>0.120139587601233</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.507582843977897</v>
+        <v>0.908052193418495</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1207891870393586</v>
+        <v>0.1217991870393586</v>
       </c>
       <c r="C59">
-        <v>53.12110926810948</v>
+        <v>44.77128764885447</v>
       </c>
       <c r="D59">
-        <v>298.4071092681095</v>
+        <v>295.5552876488545</v>
       </c>
       <c r="E59">
-        <v>130.286</v>
+        <v>135.784</v>
       </c>
       <c r="F59">
-        <v>313.386</v>
+        <v>318.884</v>
       </c>
       <c r="G59">
         <v>68.09999999999999</v>
@@ -6125,37 +6125,37 @@
         <v>41.775</v>
       </c>
       <c r="M59">
-        <v>46.00506480000001</v>
+        <v>46.81217120000001</v>
       </c>
       <c r="N59">
-        <v>-4.230064800000008</v>
+        <v>-5.03717120000001</v>
       </c>
       <c r="O59">
-        <v>-0.8460129600000017</v>
+        <v>-1.007434240000002</v>
       </c>
       <c r="P59">
-        <v>-3.384051840000006</v>
+        <v>-4.029736960000008</v>
       </c>
       <c r="Q59">
-        <v>29.71594816</v>
+        <v>29.07026303999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.121650283968967</v>
+        <v>0.1234562431110853</v>
       </c>
       <c r="T59">
-        <v>1.559561672209085</v>
+        <v>1.596694092975968</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.181610438683699</v>
+        <v>0.1784792242236352</v>
       </c>
       <c r="W59">
-        <v>0.120139587601233</v>
+        <v>0.1205992498839703</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.908052193418495</v>
+        <v>0.892396121118176</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1217991870393586</v>
+        <v>0.1228091870393586</v>
       </c>
       <c r="C60">
-        <v>44.77128764885452</v>
+        <v>36.47545869646649</v>
       </c>
       <c r="D60">
-        <v>295.5552876488545</v>
+        <v>292.7574586964665</v>
       </c>
       <c r="E60">
-        <v>135.784</v>
+        <v>141.282</v>
       </c>
       <c r="F60">
-        <v>318.884</v>
+        <v>324.3819999999999</v>
       </c>
       <c r="G60">
         <v>68.09999999999999</v>
@@ -6207,37 +6207,37 @@
         <v>41.775</v>
       </c>
       <c r="M60">
-        <v>46.8121712</v>
+        <v>47.6192776</v>
       </c>
       <c r="N60">
-        <v>-5.037171200000003</v>
+        <v>-5.844277599999998</v>
       </c>
       <c r="O60">
-        <v>-1.007434240000001</v>
+        <v>-1.16885552</v>
       </c>
       <c r="P60">
-        <v>-4.029736960000003</v>
+        <v>-4.675422079999999</v>
       </c>
       <c r="Q60">
-        <v>29.07026304</v>
+        <v>28.42457792</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1234562431110853</v>
+        <v>0.1253502978211118</v>
       </c>
       <c r="T60">
-        <v>1.596694092975968</v>
+        <v>1.635637851341236</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1784792242236352</v>
+        <v>0.1754541526266245</v>
       </c>
       <c r="W60">
-        <v>0.1205992498839703</v>
+        <v>0.1210433303944115</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8923961211181761</v>
+        <v>0.8772707631331225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1228091870393586</v>
+        <v>0.1238191870393587</v>
       </c>
       <c r="C61">
-        <v>36.47545869646649</v>
+        <v>28.2321034499742</v>
       </c>
       <c r="D61">
-        <v>292.7574586964665</v>
+        <v>290.0121034499742</v>
       </c>
       <c r="E61">
-        <v>141.282</v>
+        <v>146.7799999999999</v>
       </c>
       <c r="F61">
-        <v>324.3819999999999</v>
+        <v>329.8799999999999</v>
       </c>
       <c r="G61">
         <v>68.09999999999999</v>
@@ -6289,37 +6289,37 @@
         <v>41.775</v>
       </c>
       <c r="M61">
-        <v>47.6192776</v>
+        <v>48.426384</v>
       </c>
       <c r="N61">
-        <v>-5.844277599999998</v>
+        <v>-6.651384</v>
       </c>
       <c r="O61">
-        <v>-1.16885552</v>
+        <v>-1.3302768</v>
       </c>
       <c r="P61">
-        <v>-4.675422079999999</v>
+        <v>-5.3211072</v>
       </c>
       <c r="Q61">
-        <v>28.42457792</v>
+        <v>27.7788928</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1253502978211118</v>
+        <v>0.1273390552666396</v>
       </c>
       <c r="T61">
-        <v>1.635637851341236</v>
+        <v>1.676528797624766</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1754541526266245</v>
+        <v>0.1725299167495141</v>
       </c>
       <c r="W61">
-        <v>0.1210433303944115</v>
+        <v>0.1214726082211714</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8772707631331225</v>
+        <v>0.8626495837475703</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1238191870393587</v>
+        <v>0.1248291870393586</v>
       </c>
       <c r="C62">
-        <v>28.2321034499742</v>
+        <v>20.03975939575383</v>
       </c>
       <c r="D62">
-        <v>290.0121034499742</v>
+        <v>287.3177593957538</v>
       </c>
       <c r="E62">
-        <v>146.7799999999999</v>
+        <v>152.278</v>
       </c>
       <c r="F62">
-        <v>329.8799999999999</v>
+        <v>335.378</v>
       </c>
       <c r="G62">
         <v>68.09999999999999</v>
@@ -6371,37 +6371,37 @@
         <v>41.775</v>
       </c>
       <c r="M62">
-        <v>48.426384</v>
+        <v>49.2334904</v>
       </c>
       <c r="N62">
-        <v>-6.651384</v>
+        <v>-7.458490400000002</v>
       </c>
       <c r="O62">
-        <v>-1.3302768</v>
+        <v>-1.491698080000001</v>
       </c>
       <c r="P62">
-        <v>-5.3211072</v>
+        <v>-5.966792320000001</v>
       </c>
       <c r="Q62">
-        <v>27.7788928</v>
+        <v>27.13320768</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1273390552666396</v>
+        <v>0.1294298002734765</v>
       </c>
       <c r="T62">
-        <v>1.676528797624766</v>
+        <v>1.719516715512581</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1725299167495141</v>
+        <v>0.1697015574585384</v>
       </c>
       <c r="W62">
-        <v>0.1214726082211714</v>
+        <v>0.1218878113650866</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8626495837475703</v>
+        <v>0.8485077872926921</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1248291870393586</v>
+        <v>0.1258391870393586</v>
       </c>
       <c r="C63">
-        <v>20.03975939575383</v>
+        <v>11.89701786955686</v>
       </c>
       <c r="D63">
-        <v>287.3177593957538</v>
+        <v>284.6730178695569</v>
       </c>
       <c r="E63">
-        <v>152.278</v>
+        <v>157.776</v>
       </c>
       <c r="F63">
-        <v>335.378</v>
+        <v>340.876</v>
       </c>
       <c r="G63">
         <v>68.09999999999999</v>
@@ -6453,37 +6453,37 @@
         <v>41.775</v>
       </c>
       <c r="M63">
-        <v>49.2334904</v>
+        <v>50.0405968</v>
       </c>
       <c r="N63">
-        <v>-7.458490400000002</v>
+        <v>-8.265596800000004</v>
       </c>
       <c r="O63">
-        <v>-1.491698080000001</v>
+        <v>-1.653119360000001</v>
       </c>
       <c r="P63">
-        <v>-5.966792320000001</v>
+        <v>-6.612477440000004</v>
       </c>
       <c r="Q63">
-        <v>27.13320768</v>
+        <v>26.48752256</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1294298002734765</v>
+        <v>0.1316305844911995</v>
       </c>
       <c r="T63">
-        <v>1.719516715512581</v>
+        <v>1.764767155394491</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1697015574585384</v>
+        <v>0.1669644355640459</v>
       </c>
       <c r="W63">
-        <v>0.1218878113650866</v>
+        <v>0.1222896208591981</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8485077872926921</v>
+        <v>0.8348221778202293</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1258391870393586</v>
+        <v>0.1268491870393586</v>
       </c>
       <c r="C64">
-        <v>11.89701786955686</v>
+        <v>3.802521600716943</v>
       </c>
       <c r="D64">
-        <v>284.6730178695569</v>
+        <v>282.0765216007169</v>
       </c>
       <c r="E64">
-        <v>157.776</v>
+        <v>163.274</v>
       </c>
       <c r="F64">
-        <v>340.876</v>
+        <v>346.374</v>
       </c>
       <c r="G64">
         <v>68.09999999999999</v>
@@ -6535,37 +6535,37 @@
         <v>41.775</v>
       </c>
       <c r="M64">
-        <v>50.0405968</v>
+        <v>50.8477032</v>
       </c>
       <c r="N64">
-        <v>-8.265596800000004</v>
+        <v>-9.072703199999999</v>
       </c>
       <c r="O64">
-        <v>-1.653119360000001</v>
+        <v>-1.81454064</v>
       </c>
       <c r="P64">
-        <v>-6.612477440000004</v>
+        <v>-7.25816256</v>
       </c>
       <c r="Q64">
-        <v>26.48752256</v>
+        <v>25.84183744</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1316305844911995</v>
+        <v>0.1339503300179887</v>
       </c>
       <c r="T64">
-        <v>1.764767155394491</v>
+        <v>1.812463564999748</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1669644355640459</v>
+        <v>0.1643142064281087</v>
       </c>
       <c r="W64">
-        <v>0.1222896208591981</v>
+        <v>0.1226786744963537</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8348221778202293</v>
+        <v>0.8215710321405432</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1268491870393586</v>
+        <v>0.1278591870393586</v>
       </c>
       <c r="C65">
-        <v>3.802521600716943</v>
+        <v>-4.245037610466284</v>
       </c>
       <c r="D65">
-        <v>282.0765216007169</v>
+        <v>279.5269623895337</v>
       </c>
       <c r="E65">
-        <v>163.274</v>
+        <v>168.772</v>
       </c>
       <c r="F65">
-        <v>346.374</v>
+        <v>351.872</v>
       </c>
       <c r="G65">
         <v>68.09999999999999</v>
@@ -6617,37 +6617,37 @@
         <v>41.775</v>
       </c>
       <c r="M65">
-        <v>50.8477032</v>
+        <v>51.6548096</v>
       </c>
       <c r="N65">
-        <v>-9.072703199999999</v>
+        <v>-9.879809600000002</v>
       </c>
       <c r="O65">
-        <v>-1.81454064</v>
+        <v>-1.97596192</v>
       </c>
       <c r="P65">
-        <v>-7.25816256</v>
+        <v>-7.903847680000001</v>
       </c>
       <c r="Q65">
-        <v>25.84183744</v>
+        <v>25.19615232</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1339503300179887</v>
+        <v>0.1363989502962662</v>
       </c>
       <c r="T65">
-        <v>1.812463564999748</v>
+        <v>1.862809775138629</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1643142064281087</v>
+        <v>0.1617467969526694</v>
       </c>
       <c r="W65">
-        <v>0.1226786744963537</v>
+        <v>0.1230555702073481</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8215710321405432</v>
+        <v>0.8087339847633471</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1278591870393586</v>
+        <v>0.1649820012422307</v>
       </c>
       <c r="C66">
-        <v>-4.245037610466284</v>
+        <v>-79.44860312627452</v>
       </c>
       <c r="D66">
-        <v>279.5269623895337</v>
+        <v>209.8213968737255</v>
       </c>
       <c r="E66">
-        <v>168.772</v>
+        <v>174.27</v>
       </c>
       <c r="F66">
-        <v>351.872</v>
+        <v>357.37</v>
       </c>
       <c r="G66">
         <v>68.09999999999999</v>
@@ -6699,45 +6699,45 @@
         <v>41.775</v>
       </c>
       <c r="M66">
-        <v>51.6548096</v>
+        <v>71.759896</v>
       </c>
       <c r="N66">
-        <v>-9.879809600000002</v>
+        <v>-29.984896</v>
       </c>
       <c r="O66">
-        <v>-1.97596192</v>
+        <v>-5.9969792</v>
       </c>
       <c r="P66">
-        <v>-7.903847680000001</v>
+        <v>-23.9879168</v>
       </c>
       <c r="Q66">
-        <v>25.19615232</v>
+        <v>9.112083200000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1363989502962662</v>
+        <v>0.1418812465986512</v>
       </c>
       <c r="T66">
-        <v>1.862809775138629</v>
+        <v>1.975531557332502</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1617467969526694</v>
+        <v>0.1164299346253233</v>
       </c>
       <c r="W66">
-        <v>0.1230555702073481</v>
+        <v>0.1774208691272351</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8087339847633471</v>
+        <v>0.5821496731266166</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1649820012422307</v>
+        <v>0.1665320012422307</v>
       </c>
       <c r="C67">
-        <v>-79.44860312627452</v>
+        <v>-87.10875317991332</v>
       </c>
       <c r="D67">
-        <v>209.8213968737255</v>
+        <v>207.6592468200867</v>
       </c>
       <c r="E67">
-        <v>174.27</v>
+        <v>179.768</v>
       </c>
       <c r="F67">
-        <v>357.37</v>
+        <v>362.868</v>
       </c>
       <c r="G67">
         <v>68.09999999999999</v>
@@ -6781,37 +6781,37 @@
         <v>41.775</v>
       </c>
       <c r="M67">
-        <v>71.759896</v>
+        <v>72.86389440000001</v>
       </c>
       <c r="N67">
-        <v>-29.984896</v>
+        <v>-31.08889440000001</v>
       </c>
       <c r="O67">
-        <v>-5.9969792</v>
+        <v>-6.217778880000002</v>
       </c>
       <c r="P67">
-        <v>-23.9879168</v>
+        <v>-24.87111552000001</v>
       </c>
       <c r="Q67">
-        <v>9.112083200000001</v>
+        <v>8.228884479999994</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1418812465986512</v>
+        <v>0.1447071656162586</v>
       </c>
       <c r="T67">
-        <v>1.975531557332502</v>
+        <v>2.033635426665811</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1164299346253233</v>
+        <v>0.1146658447067578</v>
       </c>
       <c r="W67">
-        <v>0.1774208691272351</v>
+        <v>0.1777750983828831</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5821496731266166</v>
+        <v>0.573329223533789</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1665320012422307</v>
+        <v>0.1680820012422307</v>
       </c>
       <c r="C68">
-        <v>-87.10875317991332</v>
+        <v>-94.7247970477448</v>
       </c>
       <c r="D68">
-        <v>207.6592468200867</v>
+        <v>205.5412029522552</v>
       </c>
       <c r="E68">
-        <v>179.768</v>
+        <v>185.266</v>
       </c>
       <c r="F68">
-        <v>362.868</v>
+        <v>368.366</v>
       </c>
       <c r="G68">
         <v>68.09999999999999</v>
@@ -6863,37 +6863,37 @@
         <v>41.775</v>
       </c>
       <c r="M68">
-        <v>72.86389440000001</v>
+        <v>73.9678928</v>
       </c>
       <c r="N68">
-        <v>-31.08889440000001</v>
+        <v>-32.1928928</v>
       </c>
       <c r="O68">
-        <v>-6.217778880000002</v>
+        <v>-6.438578560000001</v>
       </c>
       <c r="P68">
-        <v>-24.87111552000001</v>
+        <v>-25.75431424</v>
       </c>
       <c r="Q68">
-        <v>8.228884479999994</v>
+        <v>7.345685759999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1447071656162586</v>
+        <v>0.1477043524531149</v>
       </c>
       <c r="T68">
-        <v>2.033635426665811</v>
+        <v>2.09526074262538</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1146658447067578</v>
+        <v>0.1129544141887465</v>
       </c>
       <c r="W68">
-        <v>0.1777750983828831</v>
+        <v>0.1781187536308997</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.573329223533789</v>
+        <v>0.5647720709437325</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1680820012422307</v>
+        <v>0.1696320012422307</v>
       </c>
       <c r="C69">
-        <v>-94.7247970477448</v>
+        <v>-102.2980707013996</v>
       </c>
       <c r="D69">
-        <v>205.5412029522552</v>
+        <v>203.4659292986004</v>
       </c>
       <c r="E69">
-        <v>185.266</v>
+        <v>190.764</v>
       </c>
       <c r="F69">
-        <v>368.366</v>
+        <v>373.864</v>
       </c>
       <c r="G69">
         <v>68.09999999999999</v>
@@ -6945,37 +6945,37 @@
         <v>41.775</v>
       </c>
       <c r="M69">
-        <v>73.9678928</v>
+        <v>75.0718912</v>
       </c>
       <c r="N69">
-        <v>-32.1928928</v>
+        <v>-33.2968912</v>
       </c>
       <c r="O69">
-        <v>-6.438578560000001</v>
+        <v>-6.65937824</v>
       </c>
       <c r="P69">
-        <v>-25.75431424</v>
+        <v>-26.63751296</v>
       </c>
       <c r="Q69">
-        <v>7.345685759999999</v>
+        <v>6.462487040000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1477043524531149</v>
+        <v>0.1508888634672748</v>
       </c>
       <c r="T69">
-        <v>2.09526074262538</v>
+        <v>2.160737640832424</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1129544141887465</v>
+        <v>0.1112933198624414</v>
       </c>
       <c r="W69">
-        <v>0.1781187536308997</v>
+        <v>0.1784523013716218</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5647720709437325</v>
+        <v>0.5564665993122071</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1696320012422307</v>
+        <v>0.1711820012422307</v>
       </c>
       <c r="C70">
-        <v>-102.2980707013996</v>
+        <v>-109.82985669658</v>
       </c>
       <c r="D70">
-        <v>203.4659292986004</v>
+        <v>201.4321433034201</v>
       </c>
       <c r="E70">
-        <v>190.764</v>
+        <v>196.262</v>
       </c>
       <c r="F70">
-        <v>373.864</v>
+        <v>379.362</v>
       </c>
       <c r="G70">
         <v>68.09999999999999</v>
@@ -7027,37 +7027,37 @@
         <v>41.775</v>
       </c>
       <c r="M70">
-        <v>75.0718912</v>
+        <v>76.1758896</v>
       </c>
       <c r="N70">
-        <v>-33.2968912</v>
+        <v>-34.40088960000001</v>
       </c>
       <c r="O70">
-        <v>-6.65937824</v>
+        <v>-6.880177920000001</v>
       </c>
       <c r="P70">
-        <v>-26.63751296</v>
+        <v>-27.52071168000001</v>
       </c>
       <c r="Q70">
-        <v>6.462487040000003</v>
+        <v>5.579288319999996</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1508888634672748</v>
+        <v>0.1542788268049288</v>
       </c>
       <c r="T70">
-        <v>2.160737640832424</v>
+        <v>2.230438855052824</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1112933198624414</v>
+        <v>0.1096803731977683</v>
       </c>
       <c r="W70">
-        <v>0.1784523013716218</v>
+        <v>0.1787761810618881</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5564665993122071</v>
+        <v>0.5484018659888417</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1711820012422307</v>
+        <v>0.1727320012422307</v>
       </c>
       <c r="C71">
-        <v>-109.82985669658</v>
+        <v>-117.3213868162883</v>
       </c>
       <c r="D71">
-        <v>201.4321433034201</v>
+        <v>199.4386131837117</v>
       </c>
       <c r="E71">
-        <v>196.262</v>
+        <v>201.76</v>
       </c>
       <c r="F71">
-        <v>379.362</v>
+        <v>384.86</v>
       </c>
       <c r="G71">
         <v>68.09999999999999</v>
@@ -7109,37 +7109,37 @@
         <v>41.775</v>
       </c>
       <c r="M71">
-        <v>76.1758896</v>
+        <v>77.279888</v>
       </c>
       <c r="N71">
-        <v>-34.40088960000001</v>
+        <v>-35.504888</v>
       </c>
       <c r="O71">
-        <v>-6.880177920000001</v>
+        <v>-7.1009776</v>
       </c>
       <c r="P71">
-        <v>-27.52071168000001</v>
+        <v>-28.4039104</v>
       </c>
       <c r="Q71">
-        <v>5.579288319999996</v>
+        <v>4.696089600000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1542788268049288</v>
+        <v>0.1578947876984264</v>
       </c>
       <c r="T71">
-        <v>2.230438855052824</v>
+        <v>2.304786816887919</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1096803731977683</v>
+        <v>0.1081135107235145</v>
       </c>
       <c r="W71">
-        <v>0.1787761810618881</v>
+        <v>0.1790908070467183</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5484018659888417</v>
+        <v>0.5405675536175725</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1727320012422307</v>
+        <v>0.1742820012422307</v>
       </c>
       <c r="C72">
-        <v>-117.3213868162883</v>
+        <v>-124.7738445586382</v>
       </c>
       <c r="D72">
-        <v>199.4386131837117</v>
+        <v>197.4841554413618</v>
       </c>
       <c r="E72">
-        <v>201.76</v>
+        <v>207.258</v>
       </c>
       <c r="F72">
-        <v>384.86</v>
+        <v>390.358</v>
       </c>
       <c r="G72">
         <v>68.09999999999999</v>
@@ -7191,37 +7191,37 @@
         <v>41.775</v>
       </c>
       <c r="M72">
-        <v>77.279888</v>
+        <v>78.38388640000001</v>
       </c>
       <c r="N72">
-        <v>-35.504888</v>
+        <v>-36.60888640000001</v>
       </c>
       <c r="O72">
-        <v>-7.1009776</v>
+        <v>-7.321777280000003</v>
       </c>
       <c r="P72">
-        <v>-28.4039104</v>
+        <v>-29.28710912000001</v>
       </c>
       <c r="Q72">
-        <v>4.696089600000001</v>
+        <v>3.812890879999994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1578947876984264</v>
+        <v>0.1617601252052687</v>
       </c>
       <c r="T72">
-        <v>2.304786816887919</v>
+        <v>2.384262224366813</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1081135107235145</v>
+        <v>0.1065907852203664</v>
       </c>
       <c r="W72">
-        <v>0.1790908070467183</v>
+        <v>0.1793965703277504</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5405675536175725</v>
+        <v>0.532953926101832</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1742820012422307</v>
+        <v>0.1758320012422307</v>
       </c>
       <c r="C73">
-        <v>-124.7738445586382</v>
+        <v>-132.1883674798042</v>
       </c>
       <c r="D73">
-        <v>197.4841554413618</v>
+        <v>195.5676325201957</v>
       </c>
       <c r="E73">
-        <v>207.258</v>
+        <v>212.7559999999999</v>
       </c>
       <c r="F73">
-        <v>390.3579999999999</v>
+        <v>395.8559999999999</v>
       </c>
       <c r="G73">
         <v>68.09999999999999</v>
@@ -7273,37 +7273,37 @@
         <v>41.775</v>
       </c>
       <c r="M73">
-        <v>78.38388639999999</v>
+        <v>79.48788479999999</v>
       </c>
       <c r="N73">
-        <v>-36.6088864</v>
+        <v>-37.71288479999999</v>
       </c>
       <c r="O73">
-        <v>-7.321777279999999</v>
+        <v>-7.542576959999998</v>
       </c>
       <c r="P73">
-        <v>-29.28710912</v>
+        <v>-30.17030783999999</v>
       </c>
       <c r="Q73">
-        <v>3.812890880000005</v>
+        <v>2.929692160000009</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1617601252052687</v>
+        <v>0.165901558248314</v>
       </c>
       <c r="T73">
-        <v>2.384262224366812</v>
+        <v>2.469414446665627</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1065907852203664</v>
+        <v>0.1051103576478613</v>
       </c>
       <c r="W73">
-        <v>0.1793965703277504</v>
+        <v>0.1796938401843095</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5329539261018321</v>
+        <v>0.5255517882393067</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1758320012422307</v>
+        <v>0.1773820012422307</v>
       </c>
       <c r="C74">
-        <v>-132.1883674798042</v>
+        <v>-139.5660494018573</v>
       </c>
       <c r="D74">
-        <v>195.5676325201957</v>
+        <v>193.6879505981427</v>
       </c>
       <c r="E74">
-        <v>212.7559999999999</v>
+        <v>218.254</v>
       </c>
       <c r="F74">
-        <v>395.8559999999999</v>
+        <v>401.354</v>
       </c>
       <c r="G74">
         <v>68.09999999999999</v>
@@ -7355,37 +7355,37 @@
         <v>41.775</v>
       </c>
       <c r="M74">
-        <v>79.48788479999999</v>
+        <v>80.5918832</v>
       </c>
       <c r="N74">
-        <v>-37.71288479999999</v>
+        <v>-38.8168832</v>
       </c>
       <c r="O74">
-        <v>-7.542576959999998</v>
+        <v>-7.763376640000001</v>
       </c>
       <c r="P74">
-        <v>-30.17030783999999</v>
+        <v>-31.05350656</v>
       </c>
       <c r="Q74">
-        <v>2.929692160000009</v>
+        <v>2.046493440000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.165901558248314</v>
+        <v>0.1703497641093626</v>
       </c>
       <c r="T74">
-        <v>2.469414446665627</v>
+        <v>2.560874240986576</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1051103576478613</v>
+        <v>0.1036704897348769</v>
       </c>
       <c r="W74">
-        <v>0.1796938401843095</v>
+        <v>0.1799829656612367</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5255517882393067</v>
+        <v>0.5183524486743847</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1773820012422307</v>
+        <v>0.1789320012422307</v>
       </c>
       <c r="C75">
-        <v>-139.5660494018573</v>
+        <v>-146.9079424944893</v>
       </c>
       <c r="D75">
-        <v>193.6879505981427</v>
+        <v>191.8440575055107</v>
       </c>
       <c r="E75">
-        <v>218.254</v>
+        <v>223.752</v>
       </c>
       <c r="F75">
-        <v>401.354</v>
+        <v>406.852</v>
       </c>
       <c r="G75">
         <v>68.09999999999999</v>
@@ -7437,37 +7437,37 @@
         <v>41.775</v>
       </c>
       <c r="M75">
-        <v>80.5918832</v>
+        <v>81.69588159999999</v>
       </c>
       <c r="N75">
-        <v>-38.8168832</v>
+        <v>-39.92088159999999</v>
       </c>
       <c r="O75">
-        <v>-7.763376640000001</v>
+        <v>-7.98417632</v>
       </c>
       <c r="P75">
-        <v>-31.05350656</v>
+        <v>-31.93670527999999</v>
       </c>
       <c r="Q75">
-        <v>2.046493440000003</v>
+        <v>1.163294720000007</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1703497641093626</v>
+        <v>0.1751401396520304</v>
       </c>
       <c r="T75">
-        <v>2.560874240986576</v>
+        <v>2.659369404101444</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1036704897348769</v>
+        <v>0.1022695371708921</v>
       </c>
       <c r="W75">
-        <v>0.1799829656612367</v>
+        <v>0.1802642769360848</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5183524486743847</v>
+        <v>0.5113476858544606</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1789320012422307</v>
+        <v>0.1804820012422307</v>
       </c>
       <c r="C76">
-        <v>-146.9079424944893</v>
+        <v>-154.2150592389534</v>
       </c>
       <c r="D76">
-        <v>191.8440575055107</v>
+        <v>190.0349407610466</v>
       </c>
       <c r="E76">
-        <v>223.752</v>
+        <v>229.25</v>
       </c>
       <c r="F76">
-        <v>406.852</v>
+        <v>412.35</v>
       </c>
       <c r="G76">
         <v>68.09999999999999</v>
@@ -7519,37 +7519,37 @@
         <v>41.775</v>
       </c>
       <c r="M76">
-        <v>81.69588159999999</v>
+        <v>82.79988</v>
       </c>
       <c r="N76">
-        <v>-39.92088159999999</v>
+        <v>-41.02488</v>
       </c>
       <c r="O76">
-        <v>-7.98417632</v>
+        <v>-8.204976</v>
       </c>
       <c r="P76">
-        <v>-31.93670527999999</v>
+        <v>-32.819904</v>
       </c>
       <c r="Q76">
-        <v>1.163294720000007</v>
+        <v>0.2800960000000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1751401396520304</v>
+        <v>0.1803137452381117</v>
       </c>
       <c r="T76">
-        <v>2.659369404101444</v>
+        <v>2.765744180265502</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1022695371708921</v>
+        <v>0.1009059433419469</v>
       </c>
       <c r="W76">
-        <v>0.1802642769360848</v>
+        <v>0.1805380865769371</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5113476858544606</v>
+        <v>0.5045297167097343</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1804820012422307</v>
+        <v>0.2090406840065286</v>
       </c>
       <c r="C77">
-        <v>-154.2150592389534</v>
+        <v>-187.8438917582417</v>
       </c>
       <c r="D77">
-        <v>190.0349407610466</v>
+        <v>161.9041082417582</v>
       </c>
       <c r="E77">
-        <v>229.25</v>
+        <v>234.748</v>
       </c>
       <c r="F77">
-        <v>412.35</v>
+        <v>417.848</v>
       </c>
       <c r="G77">
         <v>68.09999999999999</v>
@@ -7601,45 +7601,45 @@
         <v>41.775</v>
       </c>
       <c r="M77">
-        <v>82.79988</v>
+        <v>98.52855839999999</v>
       </c>
       <c r="N77">
-        <v>-41.02488</v>
+        <v>-56.7535584</v>
       </c>
       <c r="O77">
-        <v>-8.204976</v>
+        <v>-11.35071168</v>
       </c>
       <c r="P77">
-        <v>-32.819904</v>
+        <v>-45.40284672</v>
       </c>
       <c r="Q77">
-        <v>0.2800960000000003</v>
+        <v>-12.30284672</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1803137452381117</v>
+        <v>0.1876213294742739</v>
       </c>
       <c r="T77">
-        <v>2.765744180265502</v>
+        <v>2.91599580352667</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1009059433419469</v>
+        <v>0.084797749359946</v>
       </c>
       <c r="W77">
-        <v>0.1805380865769371</v>
+        <v>0.2158046907009248</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5045297167097343</v>
+        <v>0.4239887467997299</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2090406840065286</v>
+        <v>0.2109406840065285</v>
       </c>
       <c r="C78">
-        <v>-187.8438917582417</v>
+        <v>-194.9208340309313</v>
       </c>
       <c r="D78">
-        <v>161.9041082417582</v>
+        <v>160.3251659690686</v>
       </c>
       <c r="E78">
-        <v>234.748</v>
+        <v>240.246</v>
       </c>
       <c r="F78">
-        <v>417.848</v>
+        <v>423.3459999999999</v>
       </c>
       <c r="G78">
         <v>68.09999999999999</v>
@@ -7683,37 +7683,37 @@
         <v>41.775</v>
       </c>
       <c r="M78">
-        <v>98.52855839999999</v>
+        <v>99.82498679999999</v>
       </c>
       <c r="N78">
-        <v>-56.7535584</v>
+        <v>-58.04998679999999</v>
       </c>
       <c r="O78">
-        <v>-11.35071168</v>
+        <v>-11.60999736</v>
       </c>
       <c r="P78">
-        <v>-45.40284672</v>
+        <v>-46.43998943999999</v>
       </c>
       <c r="Q78">
-        <v>-12.30284672</v>
+        <v>-13.33998943999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1876213294742739</v>
+        <v>0.1937874742340249</v>
       </c>
       <c r="T78">
-        <v>2.91599580352667</v>
+        <v>3.04277822976696</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.084797749359946</v>
+        <v>0.0836964798877389</v>
       </c>
       <c r="W78">
-        <v>0.2158046907009248</v>
+        <v>0.2160643700424712</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4239887467997299</v>
+        <v>0.4184823994386945</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2109406840065285</v>
+        <v>0.2128406840065286</v>
       </c>
       <c r="C79">
-        <v>-194.9208340309313</v>
+        <v>-201.9672770109708</v>
       </c>
       <c r="D79">
-        <v>160.3251659690686</v>
+        <v>158.7767229890292</v>
       </c>
       <c r="E79">
-        <v>240.246</v>
+        <v>245.744</v>
       </c>
       <c r="F79">
-        <v>423.3459999999999</v>
+        <v>428.844</v>
       </c>
       <c r="G79">
         <v>68.09999999999999</v>
@@ -7765,37 +7765,37 @@
         <v>41.775</v>
       </c>
       <c r="M79">
-        <v>99.82498679999999</v>
+        <v>101.1214152</v>
       </c>
       <c r="N79">
-        <v>-58.04998679999999</v>
+        <v>-59.3464152</v>
       </c>
       <c r="O79">
-        <v>-11.60999736</v>
+        <v>-11.86928304</v>
       </c>
       <c r="P79">
-        <v>-46.43998943999999</v>
+        <v>-47.47713216</v>
       </c>
       <c r="Q79">
-        <v>-13.33998943999999</v>
+        <v>-14.37713216</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1937874742340249</v>
+        <v>0.2005141776082988</v>
       </c>
       <c r="T79">
-        <v>3.04277822976696</v>
+        <v>3.181086331120003</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0836964798877389</v>
+        <v>0.08262344809430634</v>
       </c>
       <c r="W79">
-        <v>0.2160643700424712</v>
+        <v>0.2163173909393626</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4184823994386945</v>
+        <v>0.4131172404715316</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2128406840065286</v>
+        <v>0.2147406840065285</v>
       </c>
       <c r="C80">
-        <v>-201.9672770109708</v>
+        <v>-208.9840959444718</v>
       </c>
       <c r="D80">
-        <v>158.7767229890292</v>
+        <v>157.2579040555282</v>
       </c>
       <c r="E80">
-        <v>245.744</v>
+        <v>251.242</v>
       </c>
       <c r="F80">
-        <v>428.844</v>
+        <v>434.342</v>
       </c>
       <c r="G80">
         <v>68.09999999999999</v>
@@ -7847,37 +7847,37 @@
         <v>41.775</v>
       </c>
       <c r="M80">
-        <v>101.1214152</v>
+        <v>102.4178436</v>
       </c>
       <c r="N80">
-        <v>-59.3464152</v>
+        <v>-60.6428436</v>
       </c>
       <c r="O80">
-        <v>-11.86928304</v>
+        <v>-12.12856872</v>
       </c>
       <c r="P80">
-        <v>-47.47713216</v>
+        <v>-48.51427488</v>
       </c>
       <c r="Q80">
-        <v>-14.37713216</v>
+        <v>-15.41427488</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2005141776082988</v>
+        <v>0.2078815193991702</v>
       </c>
       <c r="T80">
-        <v>3.181086331120003</v>
+        <v>3.332566632601909</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08262344809430634</v>
+        <v>0.08157758166273284</v>
       </c>
       <c r="W80">
-        <v>0.2163173909393626</v>
+        <v>0.2165640062439276</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4131172404715316</v>
+        <v>0.4078879083136642</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2147406840065285</v>
+        <v>0.2166406840065286</v>
       </c>
       <c r="C81">
-        <v>-208.9840959444718</v>
+        <v>-215.9721329053103</v>
       </c>
       <c r="D81">
-        <v>157.2579040555282</v>
+        <v>155.7678670946896</v>
       </c>
       <c r="E81">
-        <v>251.242</v>
+        <v>256.74</v>
       </c>
       <c r="F81">
-        <v>434.342</v>
+        <v>439.84</v>
       </c>
       <c r="G81">
         <v>68.09999999999999</v>
@@ -7929,37 +7929,37 @@
         <v>41.775</v>
       </c>
       <c r="M81">
-        <v>102.4178436</v>
+        <v>103.714272</v>
       </c>
       <c r="N81">
-        <v>-60.6428436</v>
+        <v>-61.939272</v>
       </c>
       <c r="O81">
-        <v>-12.12856872</v>
+        <v>-12.3878544</v>
       </c>
       <c r="P81">
-        <v>-48.51427488</v>
+        <v>-49.55141759999999</v>
       </c>
       <c r="Q81">
-        <v>-15.41427488</v>
+        <v>-16.45141759999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2078815193991702</v>
+        <v>0.2159855953691287</v>
       </c>
       <c r="T81">
-        <v>3.332566632601909</v>
+        <v>3.499194964232005</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08157758166273284</v>
+        <v>0.08055786189194869</v>
       </c>
       <c r="W81">
-        <v>0.2165640062439276</v>
+        <v>0.2168044561658785</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4078879083136642</v>
+        <v>0.4027893094597434</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2166406840065286</v>
+        <v>0.2185406840065285</v>
       </c>
       <c r="C82">
-        <v>-215.9721329053103</v>
+        <v>-222.9321983519301</v>
       </c>
       <c r="D82">
-        <v>155.7678670946896</v>
+        <v>154.3058016480698</v>
       </c>
       <c r="E82">
-        <v>256.74</v>
+        <v>262.2379999999999</v>
       </c>
       <c r="F82">
-        <v>439.84</v>
+        <v>445.338</v>
       </c>
       <c r="G82">
         <v>68.09999999999999</v>
@@ -8011,37 +8011,37 @@
         <v>41.775</v>
       </c>
       <c r="M82">
-        <v>103.714272</v>
+        <v>105.0107004</v>
       </c>
       <c r="N82">
-        <v>-61.939272</v>
+        <v>-63.23570039999999</v>
       </c>
       <c r="O82">
-        <v>-12.3878544</v>
+        <v>-12.64714008</v>
       </c>
       <c r="P82">
-        <v>-49.55141759999999</v>
+        <v>-50.58856031999999</v>
       </c>
       <c r="Q82">
-        <v>-16.45141759999999</v>
+        <v>-17.48856031999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2159855953691287</v>
+        <v>0.2249427319675039</v>
       </c>
       <c r="T82">
-        <v>3.499194964232005</v>
+        <v>3.683363120244216</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08055786189194869</v>
+        <v>0.07956332038710982</v>
       </c>
       <c r="W82">
-        <v>0.2168044561658785</v>
+        <v>0.2170389690527195</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4027893094597434</v>
+        <v>0.397816601935549</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2185406840065285</v>
+        <v>0.2204406840065286</v>
       </c>
       <c r="C83">
-        <v>-222.9321983519301</v>
+        <v>-229.8650725972863</v>
       </c>
       <c r="D83">
-        <v>154.3058016480698</v>
+        <v>152.8709274027137</v>
       </c>
       <c r="E83">
-        <v>262.2379999999999</v>
+        <v>267.736</v>
       </c>
       <c r="F83">
-        <v>445.338</v>
+        <v>450.836</v>
       </c>
       <c r="G83">
         <v>68.09999999999999</v>
@@ -8093,37 +8093,37 @@
         <v>41.775</v>
       </c>
       <c r="M83">
-        <v>105.0107004</v>
+        <v>106.3071288</v>
       </c>
       <c r="N83">
-        <v>-63.23570039999999</v>
+        <v>-64.53212880000001</v>
       </c>
       <c r="O83">
-        <v>-12.64714008</v>
+        <v>-12.90642576</v>
       </c>
       <c r="P83">
-        <v>-50.58856031999999</v>
+        <v>-51.62570304</v>
       </c>
       <c r="Q83">
-        <v>-17.48856031999999</v>
+        <v>-18.52570304</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2249427319675039</v>
+        <v>0.2348951059656985</v>
       </c>
       <c r="T83">
-        <v>3.683363120244216</v>
+        <v>3.887994404702227</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07956332038710982</v>
+        <v>0.07859303599214507</v>
       </c>
       <c r="W83">
-        <v>0.2170389690527195</v>
+        <v>0.2172677621130522</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.397816601935549</v>
+        <v>0.3929651799607252</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2204406840065286</v>
+        <v>0.2223406840065286</v>
       </c>
       <c r="C84">
-        <v>-229.8650725972863</v>
+        <v>-236.7715071975315</v>
       </c>
       <c r="D84">
-        <v>152.8709274027137</v>
+        <v>151.4624928024685</v>
       </c>
       <c r="E84">
-        <v>267.736</v>
+        <v>273.234</v>
       </c>
       <c r="F84">
-        <v>450.836</v>
+        <v>456.334</v>
       </c>
       <c r="G84">
         <v>68.09999999999999</v>
@@ -8175,37 +8175,37 @@
         <v>41.775</v>
       </c>
       <c r="M84">
-        <v>106.3071288</v>
+        <v>107.6035572</v>
       </c>
       <c r="N84">
-        <v>-64.53212880000001</v>
+        <v>-65.82855720000001</v>
       </c>
       <c r="O84">
-        <v>-12.90642576</v>
+        <v>-13.16571144</v>
       </c>
       <c r="P84">
-        <v>-51.62570304</v>
+        <v>-52.66284576</v>
       </c>
       <c r="Q84">
-        <v>-18.52570304</v>
+        <v>-19.56284576</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2348951059656985</v>
+        <v>0.2460183474930926</v>
       </c>
       <c r="T84">
-        <v>3.887994404702227</v>
+        <v>4.116699957920006</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07859303599214507</v>
+        <v>0.07764613194404692</v>
       </c>
       <c r="W84">
-        <v>0.2172677621130522</v>
+        <v>0.2174910420875938</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3929651799607252</v>
+        <v>0.3882306597202346</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2223406840065286</v>
+        <v>0.2242406840065286</v>
       </c>
       <c r="C85">
-        <v>-236.7715071975315</v>
+        <v>-243.6522262646371</v>
       </c>
       <c r="D85">
-        <v>151.4624928024685</v>
+        <v>150.0797737353629</v>
       </c>
       <c r="E85">
-        <v>273.234</v>
+        <v>278.732</v>
       </c>
       <c r="F85">
-        <v>456.334</v>
+        <v>461.832</v>
       </c>
       <c r="G85">
         <v>68.09999999999999</v>
@@ -8257,37 +8257,37 @@
         <v>41.775</v>
       </c>
       <c r="M85">
-        <v>107.6035572</v>
+        <v>108.8999856</v>
       </c>
       <c r="N85">
-        <v>-65.82855720000001</v>
+        <v>-67.1249856</v>
       </c>
       <c r="O85">
-        <v>-13.16571144</v>
+        <v>-13.42499712</v>
       </c>
       <c r="P85">
-        <v>-52.66284576</v>
+        <v>-53.69998848</v>
       </c>
       <c r="Q85">
-        <v>-19.56284576</v>
+        <v>-20.59998848</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2460183474930926</v>
+        <v>0.2585319942114109</v>
       </c>
       <c r="T85">
-        <v>4.116699957920006</v>
+        <v>4.373993705290007</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07764613194404692</v>
+        <v>0.07672177323042731</v>
       </c>
       <c r="W85">
-        <v>0.2174910420875938</v>
+        <v>0.2177090058722652</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3882306597202346</v>
+        <v>0.3836088661521366</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2242406840065285</v>
+        <v>0.2261406840065285</v>
       </c>
       <c r="C86">
-        <v>-243.652226264637</v>
+        <v>-250.5079277077667</v>
       </c>
       <c r="D86">
-        <v>150.0797737353629</v>
+        <v>148.7220722922332</v>
       </c>
       <c r="E86">
-        <v>278.732</v>
+        <v>284.2299999999999</v>
       </c>
       <c r="F86">
-        <v>461.8319999999999</v>
+        <v>467.3299999999999</v>
       </c>
       <c r="G86">
         <v>68.09999999999999</v>
@@ -8339,37 +8339,37 @@
         <v>41.775</v>
       </c>
       <c r="M86">
-        <v>108.8999856</v>
+        <v>110.196414</v>
       </c>
       <c r="N86">
-        <v>-67.1249856</v>
+        <v>-68.421414</v>
       </c>
       <c r="O86">
-        <v>-13.42499712</v>
+        <v>-13.6842828</v>
       </c>
       <c r="P86">
-        <v>-53.69998848</v>
+        <v>-54.7371312</v>
       </c>
       <c r="Q86">
-        <v>-20.59998848</v>
+        <v>-21.6371312</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2585319942114107</v>
+        <v>0.2727141271588381</v>
       </c>
       <c r="T86">
-        <v>4.373993705290004</v>
+        <v>4.665593285642671</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07672177323042732</v>
+        <v>0.07581916413359877</v>
       </c>
       <c r="W86">
-        <v>0.2177090058722652</v>
+        <v>0.2179218410972974</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3836088661521365</v>
+        <v>0.3790958206679937</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2261406840065285</v>
+        <v>0.2280406840065285</v>
       </c>
       <c r="C87">
-        <v>-250.5079277077667</v>
+        <v>-257.3392844078729</v>
       </c>
       <c r="D87">
-        <v>148.7220722922332</v>
+        <v>147.3887155921271</v>
       </c>
       <c r="E87">
-        <v>284.2299999999999</v>
+        <v>289.728</v>
       </c>
       <c r="F87">
-        <v>467.3299999999999</v>
+        <v>472.828</v>
       </c>
       <c r="G87">
         <v>68.09999999999999</v>
@@ -8421,37 +8421,37 @@
         <v>41.775</v>
       </c>
       <c r="M87">
-        <v>110.196414</v>
+        <v>111.4928424</v>
       </c>
       <c r="N87">
-        <v>-68.421414</v>
+        <v>-69.71784239999999</v>
       </c>
       <c r="O87">
-        <v>-13.6842828</v>
+        <v>-13.94356848</v>
       </c>
       <c r="P87">
-        <v>-54.7371312</v>
+        <v>-55.77427392</v>
       </c>
       <c r="Q87">
-        <v>-21.6371312</v>
+        <v>-22.67427392</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2727141271588381</v>
+        <v>0.2889222790987551</v>
       </c>
       <c r="T87">
-        <v>4.665593285642671</v>
+        <v>4.998849948902862</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07581916413359877</v>
+        <v>0.07493754594599877</v>
       </c>
       <c r="W87">
-        <v>0.2179218410972974</v>
+        <v>0.2181297266659335</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3790958206679937</v>
+        <v>0.3746877297299939</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2280406840065285</v>
+        <v>0.2299406840065286</v>
       </c>
       <c r="C88">
-        <v>-257.3392844078729</v>
+        <v>-264.1469453296703</v>
       </c>
       <c r="D88">
-        <v>147.3887155921271</v>
+        <v>146.0790546703297</v>
       </c>
       <c r="E88">
-        <v>289.728</v>
+        <v>295.226</v>
       </c>
       <c r="F88">
-        <v>472.828</v>
+        <v>478.326</v>
       </c>
       <c r="G88">
         <v>68.09999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>41.775</v>
       </c>
       <c r="M88">
-        <v>111.4928424</v>
+        <v>112.7892708</v>
       </c>
       <c r="N88">
-        <v>-69.71784239999999</v>
+        <v>-71.01427079999999</v>
       </c>
       <c r="O88">
-        <v>-13.94356848</v>
+        <v>-14.20285416</v>
       </c>
       <c r="P88">
-        <v>-55.77427392</v>
+        <v>-56.81141663999999</v>
       </c>
       <c r="Q88">
-        <v>-22.67427392</v>
+        <v>-23.71141663999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2889222790987551</v>
+        <v>0.3076239928755825</v>
       </c>
       <c r="T88">
-        <v>4.998849948902862</v>
+        <v>5.383376868049236</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07493754594599877</v>
+        <v>0.0740761948431712</v>
       </c>
       <c r="W88">
-        <v>0.2181297266659335</v>
+        <v>0.2183328332559802</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3746877297299939</v>
+        <v>0.370380974215856</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2299406840065286</v>
+        <v>0.2318406840065285</v>
       </c>
       <c r="C89">
-        <v>-264.1469453296703</v>
+        <v>-270.9315365748471</v>
       </c>
       <c r="D89">
-        <v>146.0790546703297</v>
+        <v>144.7924634251528</v>
       </c>
       <c r="E89">
-        <v>295.226</v>
+        <v>300.7239999999999</v>
       </c>
       <c r="F89">
-        <v>478.326</v>
+        <v>483.824</v>
       </c>
       <c r="G89">
         <v>68.09999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>41.775</v>
       </c>
       <c r="M89">
-        <v>112.7892708</v>
+        <v>114.0856992</v>
       </c>
       <c r="N89">
-        <v>-71.01427079999999</v>
+        <v>-72.31069919999999</v>
       </c>
       <c r="O89">
-        <v>-14.20285416</v>
+        <v>-14.46213984</v>
       </c>
       <c r="P89">
-        <v>-56.81141663999999</v>
+        <v>-57.84855935999999</v>
       </c>
       <c r="Q89">
-        <v>-23.71141663999999</v>
+        <v>-24.74855935999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3076239928755825</v>
+        <v>0.3294426589485477</v>
       </c>
       <c r="T89">
-        <v>5.383376868049236</v>
+        <v>5.83199160705334</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0740761948431712</v>
+        <v>0.07323441990177153</v>
       </c>
       <c r="W89">
-        <v>0.2183328332559802</v>
+        <v>0.2185313237871623</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.370380974215856</v>
+        <v>0.3661720995088578</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2318406840065285</v>
+        <v>0.2337406840065285</v>
       </c>
       <c r="C90">
-        <v>-270.9315365748471</v>
+        <v>-277.6936623801057</v>
       </c>
       <c r="D90">
-        <v>144.7924634251528</v>
+        <v>143.5283376198942</v>
       </c>
       <c r="E90">
-        <v>300.7239999999999</v>
+        <v>306.222</v>
       </c>
       <c r="F90">
-        <v>483.824</v>
+        <v>489.3219999999999</v>
       </c>
       <c r="G90">
         <v>68.09999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>41.775</v>
       </c>
       <c r="M90">
-        <v>114.0856992</v>
+        <v>115.3821276</v>
       </c>
       <c r="N90">
-        <v>-72.31069919999999</v>
+        <v>-73.60712759999998</v>
       </c>
       <c r="O90">
-        <v>-14.46213984</v>
+        <v>-14.72142552</v>
       </c>
       <c r="P90">
-        <v>-57.84855935999999</v>
+        <v>-58.88570207999999</v>
       </c>
       <c r="Q90">
-        <v>-24.74855935999999</v>
+        <v>-25.78570207999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3294426589485477</v>
+        <v>0.3552283552165975</v>
       </c>
       <c r="T90">
-        <v>5.83199160705334</v>
+        <v>6.362172662240007</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07323441990177153</v>
+        <v>0.07241156125118983</v>
       </c>
       <c r="W90">
-        <v>0.2185313237871623</v>
+        <v>0.2187253538569695</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3661720995088578</v>
+        <v>0.3620578062559492</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2337406840065285</v>
+        <v>0.2356406840065285</v>
       </c>
       <c r="C91">
-        <v>-277.6936623801057</v>
+        <v>-284.4339060633739</v>
       </c>
       <c r="D91">
-        <v>143.5283376198942</v>
+        <v>142.2860939366261</v>
       </c>
       <c r="E91">
-        <v>306.222</v>
+        <v>311.72</v>
       </c>
       <c r="F91">
-        <v>489.3219999999999</v>
+        <v>494.82</v>
       </c>
       <c r="G91">
         <v>68.09999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>41.775</v>
       </c>
       <c r="M91">
-        <v>115.3821276</v>
+        <v>116.678556</v>
       </c>
       <c r="N91">
-        <v>-73.60712759999998</v>
+        <v>-74.90355600000001</v>
       </c>
       <c r="O91">
-        <v>-14.72142552</v>
+        <v>-14.9807112</v>
       </c>
       <c r="P91">
-        <v>-58.88570207999999</v>
+        <v>-59.92284480000001</v>
       </c>
       <c r="Q91">
-        <v>-25.78570207999999</v>
+        <v>-26.82284480000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3552283552165975</v>
+        <v>0.3861711907382573</v>
       </c>
       <c r="T91">
-        <v>6.362172662240007</v>
+        <v>6.998389928464009</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07241156125118983</v>
+        <v>0.07160698834839883</v>
       </c>
       <c r="W91">
-        <v>0.2187253538569695</v>
+        <v>0.2189150721474476</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3620578062559492</v>
+        <v>0.358034941741994</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2356406840065285</v>
+        <v>0.2375406840065285</v>
       </c>
       <c r="C92">
-        <v>-284.4339060633739</v>
+        <v>-291.1528309213016</v>
       </c>
       <c r="D92">
-        <v>142.2860939366261</v>
+        <v>141.0651690786983</v>
       </c>
       <c r="E92">
-        <v>311.72</v>
+        <v>317.218</v>
       </c>
       <c r="F92">
-        <v>494.82</v>
+        <v>500.318</v>
       </c>
       <c r="G92">
         <v>68.09999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>41.775</v>
       </c>
       <c r="M92">
-        <v>116.678556</v>
+        <v>117.9749844</v>
       </c>
       <c r="N92">
-        <v>-74.90355600000001</v>
+        <v>-76.19998440000001</v>
       </c>
       <c r="O92">
-        <v>-14.9807112</v>
+        <v>-15.23999688</v>
       </c>
       <c r="P92">
-        <v>-59.92284480000001</v>
+        <v>-60.95998752000001</v>
       </c>
       <c r="Q92">
-        <v>-26.82284480000001</v>
+        <v>-27.85998752</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3861711907382573</v>
+        <v>0.423990211931397</v>
       </c>
       <c r="T92">
-        <v>6.998389928464009</v>
+        <v>7.775988809404454</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07160698834839883</v>
+        <v>0.07082009836654829</v>
       </c>
       <c r="W92">
-        <v>0.2189150721474476</v>
+        <v>0.2191006208051679</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.358034941741994</v>
+        <v>0.3541004918327414</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2375406840065285</v>
+        <v>0.2394406840065285</v>
       </c>
       <c r="C93">
-        <v>-291.1528309213016</v>
+        <v>-297.8509810809431</v>
       </c>
       <c r="D93">
-        <v>141.0651690786983</v>
+        <v>139.8650189190568</v>
       </c>
       <c r="E93">
-        <v>317.218</v>
+        <v>322.716</v>
       </c>
       <c r="F93">
-        <v>500.318</v>
+        <v>505.816</v>
       </c>
       <c r="G93">
         <v>68.09999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>41.775</v>
       </c>
       <c r="M93">
-        <v>117.9749844</v>
+        <v>119.2714128</v>
       </c>
       <c r="N93">
-        <v>-76.19998440000001</v>
+        <v>-77.4964128</v>
       </c>
       <c r="O93">
-        <v>-15.23999688</v>
+        <v>-15.49928256</v>
       </c>
       <c r="P93">
-        <v>-60.95998752000001</v>
+        <v>-61.99713024</v>
       </c>
       <c r="Q93">
-        <v>-27.85998752</v>
+        <v>-28.89713024</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.423990211931397</v>
+        <v>0.4712639884228217</v>
       </c>
       <c r="T93">
-        <v>7.775988809404454</v>
+        <v>8.747987410580013</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07082009836654829</v>
+        <v>0.07005031468865103</v>
       </c>
       <c r="W93">
-        <v>0.2191006208051679</v>
+        <v>0.2192821357964161</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3541004918327414</v>
+        <v>0.3502515734432551</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2394406840065285</v>
+        <v>0.2413406840065285</v>
       </c>
       <c r="C94">
-        <v>-297.8509810809431</v>
+        <v>-304.5288823083305</v>
       </c>
       <c r="D94">
-        <v>139.8650189190568</v>
+        <v>138.6851176916695</v>
       </c>
       <c r="E94">
-        <v>322.716</v>
+        <v>328.2139999999999</v>
       </c>
       <c r="F94">
-        <v>505.816</v>
+        <v>511.314</v>
       </c>
       <c r="G94">
         <v>68.09999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>41.775</v>
       </c>
       <c r="M94">
-        <v>119.2714128</v>
+        <v>120.5678412</v>
       </c>
       <c r="N94">
-        <v>-77.4964128</v>
+        <v>-78.7928412</v>
       </c>
       <c r="O94">
-        <v>-15.49928256</v>
+        <v>-15.75856824</v>
       </c>
       <c r="P94">
-        <v>-61.99713024</v>
+        <v>-63.03427296</v>
       </c>
       <c r="Q94">
-        <v>-28.89713024</v>
+        <v>-29.93427295999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4712639884228217</v>
+        <v>0.5320445581975106</v>
       </c>
       <c r="T94">
-        <v>8.747987410580013</v>
+        <v>9.997699897805731</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07005031468865103</v>
+        <v>0.06929708549845048</v>
       </c>
       <c r="W94">
-        <v>0.2192821357964161</v>
+        <v>0.2194597472394654</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3502515734432551</v>
+        <v>0.3464854274922523</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2413406840065285</v>
+        <v>0.2432406840065285</v>
       </c>
       <c r="C95">
-        <v>-304.5288823083305</v>
+        <v>-311.1870427764627</v>
       </c>
       <c r="D95">
-        <v>138.6851176916695</v>
+        <v>137.5249572235373</v>
       </c>
       <c r="E95">
-        <v>328.2139999999999</v>
+        <v>333.712</v>
       </c>
       <c r="F95">
-        <v>511.314</v>
+        <v>516.812</v>
       </c>
       <c r="G95">
         <v>68.09999999999999</v>
@@ -9077,37 +9077,37 @@
         <v>41.775</v>
       </c>
       <c r="M95">
-        <v>120.5678412</v>
+        <v>121.8642696</v>
       </c>
       <c r="N95">
-        <v>-78.7928412</v>
+        <v>-80.08926960000002</v>
       </c>
       <c r="O95">
-        <v>-15.75856824</v>
+        <v>-16.01785392</v>
       </c>
       <c r="P95">
-        <v>-63.03427296</v>
+        <v>-64.07141568000002</v>
       </c>
       <c r="Q95">
-        <v>-29.93427295999999</v>
+        <v>-30.97141568000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5320445581975106</v>
+        <v>0.6130853178970959</v>
       </c>
       <c r="T95">
-        <v>9.997699897805731</v>
+        <v>11.66398321410669</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06929708549845048</v>
+        <v>0.06855988246123292</v>
       </c>
       <c r="W95">
-        <v>0.2194597472394654</v>
+        <v>0.2196335797156413</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3464854274922523</v>
+        <v>0.3427994123061645</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2432406840065285</v>
+        <v>0.2451406840065286</v>
       </c>
       <c r="C96">
-        <v>-311.1870427764627</v>
+        <v>-317.825953795067</v>
       </c>
       <c r="D96">
-        <v>137.5249572235373</v>
+        <v>136.384046204933</v>
       </c>
       <c r="E96">
-        <v>333.712</v>
+        <v>339.2099999999999</v>
       </c>
       <c r="F96">
-        <v>516.812</v>
+        <v>522.3099999999999</v>
       </c>
       <c r="G96">
         <v>68.09999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>41.775</v>
       </c>
       <c r="M96">
-        <v>121.8642696</v>
+        <v>123.160698</v>
       </c>
       <c r="N96">
-        <v>-80.08926960000002</v>
+        <v>-81.38569799999999</v>
       </c>
       <c r="O96">
-        <v>-16.01785392</v>
+        <v>-16.2771396</v>
       </c>
       <c r="P96">
-        <v>-64.07141568000002</v>
+        <v>-65.10855839999999</v>
       </c>
       <c r="Q96">
-        <v>-30.97141568000001</v>
+        <v>-32.00855839999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6130853178970959</v>
+        <v>0.7265423814765155</v>
       </c>
       <c r="T96">
-        <v>11.66398321410669</v>
+        <v>13.99677985692804</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06855988246123292</v>
+        <v>0.06783819948795679</v>
       </c>
       <c r="W96">
-        <v>0.2196335797156413</v>
+        <v>0.2198037525607398</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3427994123061645</v>
+        <v>0.339190997439784</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2451406840065286</v>
+        <v>0.2470406840065286</v>
       </c>
       <c r="C97">
-        <v>-317.825953795067</v>
+        <v>-324.4460905043353</v>
       </c>
       <c r="D97">
-        <v>136.384046204933</v>
+        <v>135.2619094956647</v>
       </c>
       <c r="E97">
-        <v>339.2099999999999</v>
+        <v>344.708</v>
       </c>
       <c r="F97">
-        <v>522.3099999999999</v>
+        <v>527.808</v>
       </c>
       <c r="G97">
         <v>68.09999999999999</v>
@@ -9241,37 +9241,37 @@
         <v>41.775</v>
       </c>
       <c r="M97">
-        <v>123.160698</v>
+        <v>124.4571264</v>
       </c>
       <c r="N97">
-        <v>-81.38569799999999</v>
+        <v>-82.68212640000002</v>
       </c>
       <c r="O97">
-        <v>-16.2771396</v>
+        <v>-16.53642528</v>
       </c>
       <c r="P97">
-        <v>-65.10855839999999</v>
+        <v>-66.14570112000001</v>
       </c>
       <c r="Q97">
-        <v>-32.00855839999999</v>
+        <v>-33.04570112000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7265423814765155</v>
+        <v>0.8967279768456446</v>
       </c>
       <c r="T97">
-        <v>13.99677985692804</v>
+        <v>17.49597482116005</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06783819948795679</v>
+        <v>0.0671315515766239</v>
       </c>
       <c r="W97">
-        <v>0.2198037525607398</v>
+        <v>0.2199703801382321</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.339190997439784</v>
+        <v>0.3356577578831195</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2470406840065285</v>
+        <v>0.2489406840065286</v>
       </c>
       <c r="C98">
-        <v>-324.4460905043353</v>
+        <v>-331.0479125346908</v>
       </c>
       <c r="D98">
-        <v>135.2619094956647</v>
+        <v>134.1580874653091</v>
       </c>
       <c r="E98">
-        <v>344.708</v>
+        <v>350.2059999999999</v>
       </c>
       <c r="F98">
-        <v>527.808</v>
+        <v>533.3059999999999</v>
       </c>
       <c r="G98">
         <v>68.09999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>41.775</v>
       </c>
       <c r="M98">
-        <v>124.4571264</v>
+        <v>125.7535548</v>
       </c>
       <c r="N98">
-        <v>-82.68212640000002</v>
+        <v>-83.97855479999998</v>
       </c>
       <c r="O98">
-        <v>-16.53642528</v>
+        <v>-16.79571096</v>
       </c>
       <c r="P98">
-        <v>-66.14570112000001</v>
+        <v>-67.18284383999999</v>
       </c>
       <c r="Q98">
-        <v>-33.04570112000001</v>
+        <v>-34.08284383999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8967279768456423</v>
+        <v>1.18037063579419</v>
       </c>
       <c r="T98">
-        <v>17.49597482116</v>
+        <v>23.32796642821334</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0671315515766239</v>
+        <v>0.0664394737253185</v>
       </c>
       <c r="W98">
-        <v>0.2199703801382321</v>
+        <v>0.2201335720955699</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3356577578831195</v>
+        <v>0.3321973686265925</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2489406840065286</v>
+        <v>0.2508406840065286</v>
       </c>
       <c r="C99">
-        <v>-331.0479125346908</v>
+        <v>-337.6318646345139</v>
       </c>
       <c r="D99">
-        <v>134.1580874653091</v>
+        <v>133.0721353654861</v>
       </c>
       <c r="E99">
-        <v>350.2059999999999</v>
+        <v>355.704</v>
       </c>
       <c r="F99">
-        <v>533.3059999999999</v>
+        <v>538.804</v>
       </c>
       <c r="G99">
         <v>68.09999999999999</v>
@@ -9405,37 +9405,37 @@
         <v>41.775</v>
       </c>
       <c r="M99">
-        <v>125.7535548</v>
+        <v>127.0499832</v>
       </c>
       <c r="N99">
-        <v>-83.97855479999998</v>
+        <v>-85.27498320000001</v>
       </c>
       <c r="O99">
-        <v>-16.79571096</v>
+        <v>-17.05499664</v>
       </c>
       <c r="P99">
-        <v>-67.18284383999999</v>
+        <v>-68.21998656000001</v>
       </c>
       <c r="Q99">
-        <v>-34.08284383999999</v>
+        <v>-35.11998656000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.18037063579419</v>
+        <v>1.747655953691285</v>
       </c>
       <c r="T99">
-        <v>23.32796642821334</v>
+        <v>34.99194964232001</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0664394737253185</v>
+        <v>0.06576151991179484</v>
       </c>
       <c r="W99">
-        <v>0.2201335720955699</v>
+        <v>0.2202934336047988</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3321973686265925</v>
+        <v>0.3288075995589741</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2508406840065286</v>
+        <v>0.2527406840065285</v>
       </c>
       <c r="C100">
-        <v>-337.6318646345139</v>
+        <v>-344.198377267623</v>
       </c>
       <c r="D100">
-        <v>133.0721353654861</v>
+        <v>132.0036227323769</v>
       </c>
       <c r="E100">
-        <v>355.704</v>
+        <v>361.2019999999999</v>
       </c>
       <c r="F100">
-        <v>538.804</v>
+        <v>544.3019999999999</v>
       </c>
       <c r="G100">
         <v>68.09999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>41.775</v>
       </c>
       <c r="M100">
-        <v>127.0499832</v>
+        <v>128.3464116</v>
       </c>
       <c r="N100">
-        <v>-85.27498320000001</v>
+        <v>-86.57141159999998</v>
       </c>
       <c r="O100">
-        <v>-17.05499664</v>
+        <v>-17.31428232</v>
       </c>
       <c r="P100">
-        <v>-68.21998656000001</v>
+        <v>-69.25712927999999</v>
       </c>
       <c r="Q100">
-        <v>-35.11998656000001</v>
+        <v>-36.15712927999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.747655953691285</v>
+        <v>3.449511907382569</v>
       </c>
       <c r="T100">
-        <v>34.99194964232001</v>
+        <v>69.98389928464002</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06576151991179484</v>
+        <v>0.06509726213490803</v>
       </c>
       <c r="W100">
-        <v>0.2202934336047988</v>
+        <v>0.2204500655885887</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3288075995589741</v>
+        <v>0.3254863106745403</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2527406840065285</v>
-      </c>
-      <c r="C101">
-        <v>-344.198377267623</v>
-      </c>
-      <c r="D101">
-        <v>132.0036227323769</v>
-      </c>
-      <c r="E101">
-        <v>361.2019999999999</v>
-      </c>
-      <c r="F101">
-        <v>544.3019999999999</v>
-      </c>
-      <c r="G101">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>366.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>74.875</v>
-      </c>
-      <c r="K101">
-        <v>33.1</v>
-      </c>
-      <c r="L101">
-        <v>41.775</v>
-      </c>
-      <c r="M101">
-        <v>128.3464116</v>
-      </c>
-      <c r="N101">
-        <v>-86.57141159999998</v>
-      </c>
-      <c r="O101">
-        <v>-17.31428232</v>
-      </c>
-      <c r="P101">
-        <v>-69.25712927999999</v>
-      </c>
-      <c r="Q101">
-        <v>-36.15712927999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.449511907382569</v>
-      </c>
-      <c r="T101">
-        <v>69.98389928464002</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06509726213490803</v>
-      </c>
-      <c r="W101">
-        <v>0.2204500655885887</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3254863106745403</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
